--- a/NPS - matriz-saojoaodemeriti.xlsx
+++ b/NPS - matriz-saojoaodemeriti.xlsx
@@ -6,14 +6,14 @@
     <sheet state="visible" name="CSAT 1" sheetId="1" r:id="rId5"/>
   </sheets>
   <definedNames>
-    <definedName hidden="1" localSheetId="0" name="_xlnm._FilterDatabase">'CSAT 1'!$A$1:$Z$57</definedName>
+    <definedName hidden="1" localSheetId="0" name="_xlnm._FilterDatabase">'CSAT 1'!$A$1:$Z$76</definedName>
   </definedNames>
   <calcPr/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="933" uniqueCount="343">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1296" uniqueCount="448">
   <si>
     <t>userId</t>
   </si>
@@ -33,6 +33,9 @@
     <t>userEmail</t>
   </si>
   <si>
+    <t>tipoRespondente</t>
+  </si>
+  <si>
     <t>answeredAt</t>
   </si>
   <si>
@@ -90,21 +93,370 @@
     <t>AÇÃO</t>
   </si>
   <si>
-    <t>Última atualização: 22/03/2026 16:31</t>
+    <t>Última atualização: 25/03/2026 18:30</t>
+  </si>
+  <si>
+    <t>677bc2d45316892336c5d39e</t>
+  </si>
+  <si>
+    <t>69b86abb3648364cda618a5d</t>
+  </si>
+  <si>
+    <t>Queremos ouvir a sua opinião</t>
+  </si>
+  <si>
+    <t>matriz-saojoaodemeriti</t>
+  </si>
+  <si>
+    <t>CRISTIANE NOVAES CANDIDO SCHUENCK</t>
+  </si>
+  <si>
+    <t>crisliviaschuenck@gmail.com</t>
+  </si>
+  <si>
+    <t>responsavel</t>
+  </si>
+  <si>
+    <t>2026-03-25T21:15:42.108Z</t>
+  </si>
+  <si>
+    <t>10 - Extremamente provável</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Minha filha entrou em 2025 e até o momento não tenho nenhuma reclamação </t>
+  </si>
+  <si>
+    <t>Responsável</t>
+  </si>
+  <si>
+    <t>Promotor</t>
+  </si>
+  <si>
+    <t>65aa9e22611c74921eb70328</t>
+  </si>
+  <si>
+    <t>69b898ede32111b0684fb44a</t>
+  </si>
+  <si>
+    <t>MIGUEL BORGES DE CARVALHO</t>
+  </si>
+  <si>
+    <t>miguelmt23119951@matrizeducacao.com.br</t>
+  </si>
+  <si>
+    <t>estudante</t>
+  </si>
+  <si>
+    <t>2026-03-25T20:54:49.392Z</t>
+  </si>
+  <si>
+    <t>Acho o ensino muito bom</t>
+  </si>
+  <si>
+    <t>6 - Muito Satisfeito</t>
+  </si>
+  <si>
+    <t>Aluno</t>
+  </si>
+  <si>
+    <t>65aa9e26611c7404bdb70f1e</t>
+  </si>
+  <si>
+    <t>ESTHER SOARES MENDES RODRIGUES</t>
+  </si>
+  <si>
+    <t>esthermt23130347@matrizeducacao.com.br</t>
+  </si>
+  <si>
+    <t>2026-03-25T20:39:52.207Z</t>
+  </si>
+  <si>
+    <t>a escola é boa, mas ainda tem pontos ruins</t>
+  </si>
+  <si>
+    <t>1 - Muito Insatisfeito</t>
+  </si>
+  <si>
+    <t xml:space="preserve">a cantina está horrorosa! decaiu muito, as coisas estão caras, com poucas qualidades, lanches pequenos, sem recheio, má higienização, produtos de baixa qualidade para preços altos. o Guaravita totalmente de baixa qualidade, 5 reais em nuggsts pra vim nuggsts minúsculos e pouquíssimos. a mesma coisa com a batata. outro dia tinha uma mosca nos salgados. sem variedade nenhuma, e vários alunos reclamando </t>
+  </si>
+  <si>
+    <t>Neutro</t>
+  </si>
+  <si>
+    <t>60368552bff8bc73b402749b</t>
+  </si>
+  <si>
+    <t>JOÃO PEDRO DE OLIVEIRA PEREIRA</t>
+  </si>
+  <si>
+    <t>joaomt21036728@matrizeducacao.com.br</t>
+  </si>
+  <si>
+    <t>2026-03-25T20:39:12.247Z</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5 pois o colégio é realmente bom mas deixa a desejar no quesito de material didático, principalmente os online q deveria ser para todos os alunos </t>
+  </si>
+  <si>
+    <t>Detrator</t>
+  </si>
+  <si>
+    <t>66ba24bc26275a3f0664c348</t>
+  </si>
+  <si>
+    <t>ROSENI ORTEGA DO NASCIMENTO</t>
+  </si>
+  <si>
+    <t>roseortegan@gmail.com</t>
+  </si>
+  <si>
+    <t>2026-03-25T20:38:03.008Z</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bom ensino </t>
+  </si>
+  <si>
+    <t>693dffea6c53690cd4213027</t>
+  </si>
+  <si>
+    <t>ANDRE LUIZ MACHADO AMARAL</t>
+  </si>
+  <si>
+    <t>amaral.andrezinho@gmail.com</t>
+  </si>
+  <si>
+    <t>2026-03-25T20:16:05.775Z</t>
+  </si>
+  <si>
+    <t>muitos nn viriam</t>
+  </si>
+  <si>
+    <t>60368544bf1dfc5f2bfc7922</t>
+  </si>
+  <si>
+    <t>ELIZABETH MARTINS PAES</t>
+  </si>
+  <si>
+    <t>bethepaes@gmail.com</t>
+  </si>
+  <si>
+    <t>2026-03-25T19:52:52.312Z</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Xxx </t>
+  </si>
+  <si>
+    <t>60368549bff8bc03450273c6</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Katia Soares </t>
+  </si>
+  <si>
+    <t>katiacsoares@gmail.com</t>
+  </si>
+  <si>
+    <t>2026-03-25T19:49:26.62Z</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A escola me tende perfeitamente. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">A satisfação. </t>
+  </si>
+  <si>
+    <t>6036853e954f720c6c1b27b3</t>
+  </si>
+  <si>
+    <t>ANDREZA DE OLIVEIRA CORRÊA</t>
+  </si>
+  <si>
+    <t>andreza_o.c@hotmail.com</t>
+  </si>
+  <si>
+    <t>2026-03-25T19:42:33.341Z</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pois gosto muito de escola , graças a Deus não tive nenhum problema . </t>
+  </si>
+  <si>
+    <t>67892f3ef22cc8e1683af335</t>
+  </si>
+  <si>
+    <t>EVELYN LIMA DA SILVA</t>
+  </si>
+  <si>
+    <t>eveynlima97@gmail.com</t>
+  </si>
+  <si>
+    <t>2026-03-25T18:01:46.832Z</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Alguns casos de insatisfação 
+</t>
+  </si>
+  <si>
+    <t>WhatsApp da coordenação precisa está mais atendo.
+Escola precisa ter telefone 
+Caso de emergência eu prefiro ligar ao invés de mandar mensagem.
+Obs: Atenção ao meu com o meu filho que tem TDHA também é preciso ficar atento.</t>
+  </si>
+  <si>
+    <t>620596ff7d273a001c4a70a1</t>
+  </si>
+  <si>
+    <t>SAMARA RUIZ DA SILVA</t>
+  </si>
+  <si>
+    <t>vi12sa05@gmail.com</t>
+  </si>
+  <si>
+    <t>2026-03-25T16:19:33.608Z</t>
+  </si>
+  <si>
+    <t>O colégio é bem bom em geral</t>
+  </si>
+  <si>
+    <t>O lanche está muito caro comparado ao ano passado e os banheiros são horríveis de usar</t>
+  </si>
+  <si>
+    <t>6410c41b25080500173f16f3</t>
+  </si>
+  <si>
+    <t>LUIZ FELIPE DO NASCIMENTO BARROS</t>
+  </si>
+  <si>
+    <t>felipebarros.lg@gmail.com</t>
+  </si>
+  <si>
+    <t>2026-03-25T10:26:35.959Z</t>
+  </si>
+  <si>
+    <t>Gosto do método de ensino da escola.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Respostas das últimas 3 perguntas, eu coloquei nota 1, pois, não tenho acesso a esses lugares. Acho que precisamos de reuniões todos os meses para saber sobre o desenvolvimento pedagógico de nossos filhos e as novas idéias da administração da escola.
+</t>
+  </si>
+  <si>
+    <t>697bbfe38087918bacf16594</t>
+  </si>
+  <si>
+    <t>PAULO CESAR BARROS DA SILVA</t>
+  </si>
+  <si>
+    <t>pauloesinara51@gmail.com</t>
+  </si>
+  <si>
+    <t>2026-03-24T23:03:33.706Z</t>
+  </si>
+  <si>
+    <t>Até momento nada a declarar,a escola está atendendo até momento os requisitos falado em reunião.</t>
+  </si>
+  <si>
+    <t>Somente a questão que o aluno usem o celular somente no recreio.
+Fora disso a escola está de nota 10</t>
+  </si>
+  <si>
+    <t>6274561b4fd6d6001c7b9732</t>
+  </si>
+  <si>
+    <t>SONIA MEDEIROS CAMARA</t>
+  </si>
+  <si>
+    <t>luana_sjm@hotmail.com</t>
+  </si>
+  <si>
+    <t>2026-03-24T20:55:14.008Z</t>
+  </si>
+  <si>
+    <t>Minha filha completou o ensino médio nesta escola, fiquei satisfeita e por isso matriculei meu filho.</t>
+  </si>
+  <si>
+    <t>677bc2d45316892d0ec5d3b1</t>
+  </si>
+  <si>
+    <t>JEFFERSON BARROS GONZAGA</t>
+  </si>
+  <si>
+    <t>jeffersonbarros163@gmail.com</t>
+  </si>
+  <si>
+    <t>2026-03-23T23:22:06.222Z</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ensino e estrutura de boa qualidade. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ter uma resposta mais rápida quando precisamos dos serviços do pessoal de TI da escola. </t>
+  </si>
+  <si>
+    <t>64122cf9f16a6c0017853803</t>
+  </si>
+  <si>
+    <t>KAREM PEÇANHA MELLO</t>
+  </si>
+  <si>
+    <t>karem.mello@hotmail.com</t>
+  </si>
+  <si>
+    <t>2026-03-23T20:14:08.542Z</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Boa estrutura, embora so tenha 1 banheiro n o térreo o que faz com que o aluno tenha que descer e subir para utilizar o banheiro  e tem muita falha na comunicação. </t>
+  </si>
+  <si>
+    <t>67a2d5dea94cf6692661c11b</t>
+  </si>
+  <si>
+    <t>KAYKE ANDRADE ARAUJO FERNANDES</t>
+  </si>
+  <si>
+    <t>kaykemt25170119@matrizeducacao.com.br</t>
+  </si>
+  <si>
+    <t>2026-03-23T20:12:44.181Z</t>
+  </si>
+  <si>
+    <t>.</t>
+  </si>
+  <si>
+    <t>698530dcff5a35c2f2054ff9</t>
+  </si>
+  <si>
+    <t>DENISE PINHO FRANÇA DOS SANTOS</t>
+  </si>
+  <si>
+    <t>denise-pf@hotmail.com</t>
+  </si>
+  <si>
+    <t>2026-03-23T19:43:08.82Z</t>
+  </si>
+  <si>
+    <t xml:space="preserve">É muito bom o colégio 
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A escola é ótima </t>
+  </si>
+  <si>
+    <t>64122cf9f16a6c00178537c3</t>
+  </si>
+  <si>
+    <t>LEANDRO FERREIRA DOS SANTOS SILVA</t>
+  </si>
+  <si>
+    <t>lferreira.sjm@gmail.com</t>
+  </si>
+  <si>
+    <t>2026-03-23T17:22:04.282Z</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Não ter ensino fundamental na parte da manhã. </t>
   </si>
   <si>
     <t>677bc2d45316893d21c5d5fe</t>
   </si>
   <si>
-    <t>69b898ede32111b0684fb44a</t>
-  </si>
-  <si>
-    <t>Queremos ouvir a sua opinião</t>
-  </si>
-  <si>
-    <t>matriz-saojoaodemeriti</t>
-  </si>
-  <si>
     <t>MANUELA NOGUEIRA BAUER CARVALHO</t>
   </si>
   <si>
@@ -114,27 +466,12 @@
     <t>2026-03-21T14:35:57.677Z</t>
   </si>
   <si>
-    <t>10 - Extremamente provável</t>
-  </si>
-  <si>
     <t xml:space="preserve">Por que o matriz educação e o melhor colégio de São João de Meriti </t>
   </si>
   <si>
-    <t>6 - Muito Satisfeito</t>
-  </si>
-  <si>
-    <t>Aluno</t>
-  </si>
-  <si>
-    <t>Promotor</t>
-  </si>
-  <si>
     <t>65a99b971c199e3ba40b3812</t>
   </si>
   <si>
-    <t>69b86abb3648364cda618a5d</t>
-  </si>
-  <si>
     <t>VANESSA SOUZA SA COSTA</t>
   </si>
   <si>
@@ -145,9 +482,6 @@
   </si>
   <si>
     <t xml:space="preserve">Gosto muito do método de ensino, e meus filhos gostam bastante da escola. </t>
-  </si>
-  <si>
-    <t>Responsável</t>
   </si>
   <si>
     <t>6983df16880d49c218829371</t>
@@ -185,9 +519,6 @@
     <t>Gosto da escola, ensino bom. Porém as vezes deixar desejar em um atendimento rápido quando solicitamos via zap. E este ano teve algumas mudanças na plataforma que não foi satisfatório pra mim.</t>
   </si>
   <si>
-    <t>Neutro</t>
-  </si>
-  <si>
     <t>677bc2d4531689f27fc5d4ec</t>
   </si>
   <si>
@@ -218,9 +549,6 @@
     <t>Alguns pontos deixa a desejar. Como a comunicação.</t>
   </si>
   <si>
-    <t>1 - Muito Insatisfeito</t>
-  </si>
-  <si>
     <t>Melhorar a comunicação pelo app. O tempo de espera é muito demorado.</t>
   </si>
   <si>
@@ -315,9 +643,6 @@
   </si>
   <si>
     <t xml:space="preserve">Troca de professores com frequência, professores bons inclusive! Comunicação aparentemente fácil, porém não resolvem. </t>
-  </si>
-  <si>
-    <t>Detrator</t>
   </si>
   <si>
     <t>69813c644410ff251cf6601b</t>
@@ -801,9 +1126,6 @@
   </si>
   <si>
     <t>2026-03-16T23:30:35.817Z</t>
-  </si>
-  <si>
-    <t>.</t>
   </si>
   <si>
     <t>677bc2d353168935c7c5d281</t>
@@ -1079,7 +1401,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1090,6 +1412,12 @@
       <patternFill patternType="solid">
         <fgColor rgb="FFF3F3F3"/>
         <bgColor rgb="FFF3F3F3"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor rgb="FFFFFFFF"/>
       </patternFill>
     </fill>
   </fills>
@@ -1113,7 +1441,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="7">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -1124,6 +1452,13 @@
       <alignment readingOrder="0"/>
     </xf>
     <xf borderId="1" fillId="0" fontId="2" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
+    <xf borderId="1" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="right" readingOrder="0"/>
+    </xf>
+    <xf borderId="1" fillId="3" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment readingOrder="0"/>
+    </xf>
+    <xf borderId="1" fillId="3" fontId="2" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle xfId="0" name="Normal" builtinId="0"/>
@@ -1346,26 +1681,27 @@
     <col customWidth="1" min="4" max="4" width="17.63"/>
     <col customWidth="1" min="5" max="5" width="41.75"/>
     <col customWidth="1" min="6" max="6" width="35.88"/>
-    <col customWidth="1" min="7" max="7" width="20.5"/>
-    <col customWidth="1" min="8" max="8" width="70.5"/>
-    <col customWidth="1" min="9" max="9" width="357.0"/>
-    <col customWidth="1" min="10" max="10" width="70.13"/>
-    <col customWidth="1" min="11" max="11" width="74.13"/>
-    <col customWidth="1" min="12" max="12" width="76.63"/>
-    <col customWidth="1" min="13" max="13" width="51.75"/>
-    <col customWidth="1" min="14" max="14" width="72.38"/>
-    <col customWidth="1" min="15" max="15" width="38.13"/>
-    <col customWidth="1" min="16" max="16" width="52.75"/>
-    <col customWidth="1" min="17" max="17" width="71.88"/>
-    <col customWidth="1" min="18" max="18" width="64.5"/>
-    <col customWidth="1" min="19" max="19" width="242.0"/>
-    <col customWidth="1" min="20" max="20" width="16.75"/>
-    <col customWidth="1" min="21" max="21" width="7.75"/>
-    <col customWidth="1" min="22" max="22" width="15.25"/>
-    <col customWidth="1" min="23" max="23" width="26.63"/>
-    <col customWidth="1" min="24" max="24" width="18.88"/>
-    <col customWidth="1" min="25" max="25" width="7.75"/>
-    <col customWidth="1" min="26" max="26" width="31.13"/>
+    <col customWidth="1" min="7" max="7" width="15.88"/>
+    <col customWidth="1" min="8" max="8" width="20.5"/>
+    <col customWidth="1" min="9" max="9" width="70.5"/>
+    <col customWidth="1" min="10" max="10" width="357.0"/>
+    <col customWidth="1" min="11" max="11" width="70.13"/>
+    <col customWidth="1" min="12" max="12" width="74.13"/>
+    <col customWidth="1" min="13" max="13" width="76.63"/>
+    <col customWidth="1" min="14" max="14" width="51.75"/>
+    <col customWidth="1" min="15" max="15" width="72.38"/>
+    <col customWidth="1" min="16" max="16" width="38.13"/>
+    <col customWidth="1" min="17" max="17" width="52.75"/>
+    <col customWidth="1" min="18" max="18" width="71.88"/>
+    <col customWidth="1" min="19" max="19" width="64.5"/>
+    <col customWidth="1" min="20" max="20" width="302.75"/>
+    <col customWidth="1" min="21" max="21" width="16.75"/>
+    <col customWidth="1" min="22" max="22" width="7.75"/>
+    <col customWidth="1" min="23" max="23" width="15.25"/>
+    <col customWidth="1" min="24" max="24" width="26.63"/>
+    <col customWidth="1" min="25" max="25" width="18.88"/>
+    <col customWidth="1" min="26" max="26" width="7.75"/>
+    <col customWidth="1" min="27" max="27" width="28.63"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1447,320 +1783,335 @@
       <c r="Z1" s="1" t="s">
         <v>25</v>
       </c>
+      <c r="AA1" s="1" t="s">
+        <v>26</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="J2" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="K2" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="L2" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="M2" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="N2" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="O2" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="P2" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="Q2" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="R2" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="S2" s="2"/>
-      <c r="T2" s="2" t="s">
         <v>36</v>
       </c>
+      <c r="K2" s="2">
+        <v>5.0</v>
+      </c>
+      <c r="L2" s="2">
+        <v>5.0</v>
+      </c>
+      <c r="M2" s="2">
+        <v>5.0</v>
+      </c>
+      <c r="N2" s="2">
+        <v>5.0</v>
+      </c>
+      <c r="O2" s="2">
+        <v>4.0</v>
+      </c>
+      <c r="P2" s="2">
+        <v>5.0</v>
+      </c>
+      <c r="Q2" s="2">
+        <v>5.0</v>
+      </c>
+      <c r="R2" s="2">
+        <v>4.0</v>
+      </c>
+      <c r="S2" s="2">
+        <v>5.0</v>
+      </c>
+      <c r="T2" s="2"/>
       <c r="U2" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="V2" s="2"/>
+      <c r="V2" s="2" t="s">
+        <v>38</v>
+      </c>
       <c r="W2" s="2"/>
       <c r="X2" s="2"/>
       <c r="Y2" s="2"/>
       <c r="Z2" s="3"/>
+      <c r="AA2" s="3"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="F3" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="G3" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="H3" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="I3" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="J3" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="K3" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="L3" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="M3" s="2">
+        <v>5.0</v>
+      </c>
+      <c r="N3" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="O3" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="P3" s="2">
+        <v>5.0</v>
+      </c>
+      <c r="Q3" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="R3" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="S3" s="2">
+        <v>4.0</v>
+      </c>
+      <c r="T3" s="2"/>
+      <c r="U3" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="V3" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="B3" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="D3" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="E3" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="F3" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="G3" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="H3" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="I3" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="J3" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="K3" s="2">
-        <v>4.0</v>
-      </c>
-      <c r="L3" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="M3" s="2">
-        <v>3.0</v>
-      </c>
-      <c r="N3" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="O3" s="2">
-        <v>4.0</v>
-      </c>
-      <c r="P3" s="2">
-        <v>5.0</v>
-      </c>
-      <c r="Q3" s="2">
-        <v>5.0</v>
-      </c>
-      <c r="R3" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="S3" s="2"/>
-      <c r="T3" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="U3" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="V3" s="2"/>
       <c r="W3" s="2"/>
       <c r="X3" s="2"/>
       <c r="Y3" s="3"/>
       <c r="Z3" s="3"/>
+      <c r="AA3" s="3"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="F4" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="G4" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="H4" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="I4" s="2">
+        <v>7.0</v>
+      </c>
+      <c r="J4" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="K4" s="2">
+        <v>3.0</v>
+      </c>
+      <c r="L4" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="M4" s="2">
+        <v>4.0</v>
+      </c>
+      <c r="N4" s="2">
+        <v>4.0</v>
+      </c>
+      <c r="O4" s="2">
+        <v>5.0</v>
+      </c>
+      <c r="P4" s="2">
+        <v>3.0</v>
+      </c>
+      <c r="Q4" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="R4" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="S4" s="2">
+        <v>4.0</v>
+      </c>
+      <c r="T4" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="U4" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="G4" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="H4" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="I4" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="J4" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="K4" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="L4" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="M4" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="N4" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="O4" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="P4" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="Q4" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="R4" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="S4" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="T4" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="U4" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="V4" s="2"/>
+      <c r="V4" s="2" t="s">
+        <v>55</v>
+      </c>
       <c r="W4" s="2"/>
       <c r="X4" s="2"/>
       <c r="Y4" s="3"/>
       <c r="Z4" s="3"/>
+      <c r="AA4" s="3"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="s">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="F5" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="G5" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="H5" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="I5" s="2">
+        <v>5.0</v>
+      </c>
+      <c r="J5" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="K5" s="2">
+        <v>4.0</v>
+      </c>
+      <c r="L5" s="2">
+        <v>2.0</v>
+      </c>
+      <c r="M5" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="G5" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="H5" s="2">
-        <v>8.0</v>
-      </c>
-      <c r="I5" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="J5" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="K5" s="2">
-        <v>4.0</v>
-      </c>
-      <c r="L5" s="2">
-        <v>4.0</v>
-      </c>
-      <c r="M5" s="2">
-        <v>4.0</v>
-      </c>
       <c r="N5" s="2">
         <v>4.0</v>
       </c>
-      <c r="O5" s="2">
-        <v>4.0</v>
+      <c r="O5" s="2" t="s">
+        <v>46</v>
       </c>
       <c r="P5" s="2">
-        <v>5.0</v>
+        <v>3.0</v>
       </c>
       <c r="Q5" s="2">
-        <v>5.0</v>
-      </c>
-      <c r="R5" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="S5" s="2"/>
-      <c r="T5" s="2" t="s">
-        <v>44</v>
-      </c>
+        <v>3.0</v>
+      </c>
+      <c r="R5" s="2">
+        <v>2.0</v>
+      </c>
+      <c r="S5" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="T5" s="2"/>
       <c r="U5" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="V5" s="2"/>
+        <v>47</v>
+      </c>
+      <c r="V5" s="2" t="s">
+        <v>61</v>
+      </c>
       <c r="W5" s="2"/>
       <c r="X5" s="2"/>
       <c r="Y5" s="3"/>
       <c r="Z5" s="3"/>
+      <c r="AA5" s="3"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>39</v>
+        <v>28</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>59</v>
+        <v>64</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>60</v>
+        <v>33</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="I6" s="2" t="s">
-        <v>61</v>
+        <v>65</v>
+      </c>
+      <c r="I6" s="2">
+        <v>9.0</v>
       </c>
       <c r="J6" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="K6" s="2" t="s">
-        <v>35</v>
+        <v>66</v>
+      </c>
+      <c r="K6" s="2">
+        <v>5.0</v>
       </c>
       <c r="L6" s="2">
         <v>5.0</v>
       </c>
-      <c r="M6" s="2" t="s">
-        <v>35</v>
+      <c r="M6" s="2">
+        <v>5.0</v>
       </c>
       <c r="N6" s="2">
         <v>5.0</v>
@@ -1768,957 +2119,1003 @@
       <c r="O6" s="2">
         <v>5.0</v>
       </c>
-      <c r="P6" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="Q6" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="R6" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="S6" s="2"/>
-      <c r="T6" s="2" t="s">
-        <v>44</v>
-      </c>
+      <c r="P6" s="2">
+        <v>5.0</v>
+      </c>
+      <c r="Q6" s="2">
+        <v>5.0</v>
+      </c>
+      <c r="R6" s="2">
+        <v>5.0</v>
+      </c>
+      <c r="S6" s="2">
+        <v>5.0</v>
+      </c>
+      <c r="T6" s="2"/>
       <c r="U6" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="V6" s="2"/>
+      <c r="V6" s="2" t="s">
+        <v>38</v>
+      </c>
       <c r="W6" s="2"/>
       <c r="X6" s="2"/>
       <c r="Y6" s="3"/>
       <c r="Z6" s="3"/>
+      <c r="AA6" s="3"/>
     </row>
     <row r="7">
       <c r="A7" s="2" t="s">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>63</v>
+        <v>68</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>64</v>
+        <v>69</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="H7" s="2">
-        <v>7.0</v>
-      </c>
-      <c r="I7" s="2" t="s">
-        <v>66</v>
+        <v>33</v>
+      </c>
+      <c r="H7" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="I7" s="2">
+        <v>9.0</v>
       </c>
       <c r="J7" s="2" t="s">
-        <v>35</v>
+        <v>71</v>
       </c>
       <c r="K7" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="L7" s="2" t="s">
-        <v>35</v>
+        <v>46</v>
+      </c>
+      <c r="L7" s="2">
+        <v>5.0</v>
       </c>
       <c r="M7" s="2">
-        <v>4.0</v>
+        <v>5.0</v>
       </c>
       <c r="N7" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="O7" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="P7" s="2">
-        <v>5.0</v>
+        <v>46</v>
+      </c>
+      <c r="O7" s="2">
+        <v>5.0</v>
+      </c>
+      <c r="P7" s="2" t="s">
+        <v>46</v>
       </c>
       <c r="Q7" s="2">
         <v>5.0</v>
       </c>
       <c r="R7" s="2">
-        <v>5.0</v>
+        <v>4.0</v>
       </c>
       <c r="S7" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="T7" s="2" t="s">
-        <v>36</v>
-      </c>
+        <v>46</v>
+      </c>
+      <c r="T7" s="2"/>
       <c r="U7" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="V7" s="2"/>
+        <v>37</v>
+      </c>
+      <c r="V7" s="2" t="s">
+        <v>38</v>
+      </c>
       <c r="W7" s="2"/>
       <c r="X7" s="2"/>
       <c r="Y7" s="3"/>
       <c r="Z7" s="3"/>
+      <c r="AA7" s="3"/>
     </row>
     <row r="8">
       <c r="A8" s="2" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>39</v>
+        <v>28</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>72</v>
+        <v>33</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="I8" s="2" t="s">
-        <v>73</v>
+        <v>75</v>
+      </c>
+      <c r="I8" s="2">
+        <v>9.0</v>
       </c>
       <c r="J8" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="K8" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="L8" s="2" t="s">
-        <v>35</v>
+        <v>76</v>
+      </c>
+      <c r="K8" s="2">
+        <v>5.0</v>
+      </c>
+      <c r="L8" s="2">
+        <v>4.0</v>
       </c>
       <c r="M8" s="2">
-        <v>4.0</v>
+        <v>5.0</v>
       </c>
       <c r="N8" s="2">
-        <v>5.0</v>
-      </c>
-      <c r="O8" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="P8" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="Q8" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="R8" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="S8" s="2"/>
-      <c r="T8" s="2" t="s">
-        <v>44</v>
-      </c>
+        <v>4.0</v>
+      </c>
+      <c r="O8" s="2">
+        <v>5.0</v>
+      </c>
+      <c r="P8" s="2">
+        <v>5.0</v>
+      </c>
+      <c r="Q8" s="2">
+        <v>5.0</v>
+      </c>
+      <c r="R8" s="2">
+        <v>5.0</v>
+      </c>
+      <c r="S8" s="2">
+        <v>5.0</v>
+      </c>
+      <c r="T8" s="2"/>
       <c r="U8" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="V8" s="2"/>
+      <c r="V8" s="2" t="s">
+        <v>38</v>
+      </c>
       <c r="W8" s="2"/>
       <c r="X8" s="2"/>
       <c r="Y8" s="3"/>
       <c r="Z8" s="3"/>
+      <c r="AA8" s="3"/>
     </row>
     <row r="9">
       <c r="A9" s="2" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="H9" s="2">
-        <v>7.0</v>
+        <v>33</v>
+      </c>
+      <c r="H9" s="2" t="s">
+        <v>80</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="J9" s="2">
-        <v>5.0</v>
+        <v>35</v>
+      </c>
+      <c r="J9" s="2" t="s">
+        <v>81</v>
       </c>
       <c r="K9" s="2">
-        <v>3.0</v>
-      </c>
-      <c r="L9" s="2">
-        <v>3.0</v>
+        <v>5.0</v>
+      </c>
+      <c r="L9" s="2" t="s">
+        <v>46</v>
       </c>
       <c r="M9" s="2">
-        <v>4.0</v>
-      </c>
-      <c r="N9" s="2">
-        <v>5.0</v>
+        <v>5.0</v>
+      </c>
+      <c r="N9" s="2" t="s">
+        <v>46</v>
       </c>
       <c r="O9" s="2">
-        <v>4.0</v>
-      </c>
-      <c r="P9" s="2" t="s">
-        <v>67</v>
+        <v>5.0</v>
+      </c>
+      <c r="P9" s="2">
+        <v>5.0</v>
       </c>
       <c r="Q9" s="2" t="s">
-        <v>67</v>
+        <v>46</v>
       </c>
       <c r="R9" s="2">
-        <v>5.0</v>
-      </c>
-      <c r="S9" s="2" t="s">
-        <v>79</v>
+        <v>4.0</v>
+      </c>
+      <c r="S9" s="2">
+        <v>5.0</v>
       </c>
       <c r="T9" s="2" t="s">
-        <v>36</v>
+        <v>82</v>
       </c>
       <c r="U9" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="V9" s="2"/>
+        <v>37</v>
+      </c>
+      <c r="V9" s="2" t="s">
+        <v>38</v>
+      </c>
       <c r="W9" s="2"/>
       <c r="X9" s="2"/>
       <c r="Y9" s="3"/>
       <c r="Z9" s="3"/>
+      <c r="AA9" s="3"/>
     </row>
     <row r="10">
       <c r="A10" s="2" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>39</v>
+        <v>28</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>83</v>
+        <v>33</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>33</v>
+        <v>86</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>84</v>
+        <v>35</v>
       </c>
       <c r="J10" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="K10" s="2">
-        <v>5.0</v>
+        <v>87</v>
+      </c>
+      <c r="K10" s="2" t="s">
+        <v>46</v>
       </c>
       <c r="L10" s="2" t="s">
-        <v>35</v>
+        <v>46</v>
       </c>
       <c r="M10" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="N10" s="2">
-        <v>4.0</v>
-      </c>
-      <c r="O10" s="2">
-        <v>5.0</v>
+        <v>46</v>
+      </c>
+      <c r="N10" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="O10" s="2" t="s">
+        <v>46</v>
       </c>
       <c r="P10" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="Q10" s="2">
-        <v>4.0</v>
+        <v>46</v>
+      </c>
+      <c r="Q10" s="2" t="s">
+        <v>46</v>
       </c>
       <c r="R10" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="S10" s="2"/>
-      <c r="T10" s="2" t="s">
-        <v>44</v>
-      </c>
+        <v>46</v>
+      </c>
+      <c r="S10" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="T10" s="2"/>
       <c r="U10" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="V10" s="2"/>
+      <c r="V10" s="2" t="s">
+        <v>38</v>
+      </c>
       <c r="W10" s="2"/>
       <c r="X10" s="2"/>
       <c r="Y10" s="3"/>
       <c r="Z10" s="3"/>
+      <c r="AA10" s="3"/>
     </row>
     <row r="11">
       <c r="A11" s="2" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>39</v>
+        <v>28</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>88</v>
+        <v>33</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="I11" s="2" t="s">
-        <v>89</v>
+        <v>91</v>
+      </c>
+      <c r="I11" s="2">
+        <v>8.0</v>
       </c>
       <c r="J11" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="K11" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="L11" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="M11" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="N11" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="O11" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="P11" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="Q11" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="R11" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="S11" s="2"/>
+        <v>92</v>
+      </c>
+      <c r="K11" s="2">
+        <v>5.0</v>
+      </c>
+      <c r="L11" s="2">
+        <v>5.0</v>
+      </c>
+      <c r="M11" s="2">
+        <v>5.0</v>
+      </c>
+      <c r="N11" s="2">
+        <v>4.0</v>
+      </c>
+      <c r="O11" s="2">
+        <v>3.0</v>
+      </c>
+      <c r="P11" s="2">
+        <v>5.0</v>
+      </c>
+      <c r="Q11" s="2">
+        <v>5.0</v>
+      </c>
+      <c r="R11" s="2">
+        <v>5.0</v>
+      </c>
+      <c r="S11" s="2">
+        <v>5.0</v>
+      </c>
       <c r="T11" s="2" t="s">
-        <v>44</v>
+        <v>93</v>
       </c>
       <c r="U11" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="V11" s="2"/>
+      <c r="V11" s="2" t="s">
+        <v>55</v>
+      </c>
       <c r="W11" s="2"/>
       <c r="X11" s="2"/>
       <c r="Y11" s="3"/>
       <c r="Z11" s="3"/>
+      <c r="AA11" s="3"/>
     </row>
     <row r="12">
       <c r="A12" s="2" t="s">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>39</v>
+        <v>28</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>91</v>
+        <v>95</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>93</v>
+        <v>33</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>33</v>
+        <v>97</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>94</v>
+        <v>35</v>
       </c>
       <c r="J12" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="K12" s="2" t="s">
-        <v>35</v>
+        <v>98</v>
+      </c>
+      <c r="K12" s="2">
+        <v>4.0</v>
       </c>
       <c r="L12" s="2">
         <v>5.0</v>
       </c>
       <c r="M12" s="2" t="s">
-        <v>35</v>
+        <v>46</v>
       </c>
       <c r="N12" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="O12" s="2">
-        <v>5.0</v>
+        <v>46</v>
+      </c>
+      <c r="O12" s="2" t="s">
+        <v>46</v>
       </c>
       <c r="P12" s="2">
-        <v>5.0</v>
-      </c>
-      <c r="Q12" s="2">
-        <v>3.0</v>
+        <v>4.0</v>
+      </c>
+      <c r="Q12" s="2" t="s">
+        <v>53</v>
       </c>
       <c r="R12" s="2">
-        <v>5.0</v>
-      </c>
-      <c r="S12" s="2"/>
+        <v>2.0</v>
+      </c>
+      <c r="S12" s="2">
+        <v>5.0</v>
+      </c>
       <c r="T12" s="2" t="s">
-        <v>44</v>
+        <v>99</v>
       </c>
       <c r="U12" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="V12" s="2"/>
+      <c r="V12" s="2" t="s">
+        <v>38</v>
+      </c>
       <c r="W12" s="2"/>
       <c r="X12" s="2"/>
       <c r="Y12" s="3"/>
       <c r="Z12" s="3"/>
+      <c r="AA12" s="3"/>
     </row>
     <row r="13">
       <c r="A13" s="2" t="s">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>39</v>
+        <v>28</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>96</v>
+        <v>101</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>97</v>
+        <v>102</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>98</v>
-      </c>
-      <c r="H13" s="2">
-        <v>3.0</v>
-      </c>
-      <c r="I13" s="2" t="s">
-        <v>99</v>
-      </c>
-      <c r="J13" s="2">
-        <v>4.0</v>
+        <v>33</v>
+      </c>
+      <c r="H13" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="I13" s="2">
+        <v>8.0</v>
+      </c>
+      <c r="J13" s="2" t="s">
+        <v>104</v>
       </c>
       <c r="K13" s="2">
-        <v>3.0</v>
-      </c>
-      <c r="L13" s="2" t="s">
-        <v>35</v>
+        <v>5.0</v>
+      </c>
+      <c r="L13" s="2">
+        <v>5.0</v>
       </c>
       <c r="M13" s="2">
         <v>4.0</v>
       </c>
       <c r="N13" s="2">
-        <v>4.0</v>
+        <v>5.0</v>
       </c>
       <c r="O13" s="2">
-        <v>4.0</v>
+        <v>5.0</v>
       </c>
       <c r="P13" s="2">
-        <v>2.0</v>
+        <v>5.0</v>
       </c>
       <c r="Q13" s="2" t="s">
-        <v>35</v>
+        <v>53</v>
       </c>
       <c r="R13" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="S13" s="2"/>
+        <v>53</v>
+      </c>
+      <c r="S13" s="2" t="s">
+        <v>53</v>
+      </c>
       <c r="T13" s="2" t="s">
-        <v>44</v>
+        <v>105</v>
       </c>
       <c r="U13" s="2" t="s">
-        <v>100</v>
-      </c>
-      <c r="V13" s="2"/>
+        <v>37</v>
+      </c>
+      <c r="V13" s="2" t="s">
+        <v>55</v>
+      </c>
       <c r="W13" s="2"/>
       <c r="X13" s="2"/>
       <c r="Y13" s="3"/>
       <c r="Z13" s="3"/>
+      <c r="AA13" s="3"/>
     </row>
     <row r="14">
       <c r="A14" s="2" t="s">
-        <v>101</v>
+        <v>106</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>39</v>
+        <v>28</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>102</v>
+        <v>107</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>103</v>
+        <v>108</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>104</v>
+        <v>33</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>33</v>
+        <v>109</v>
       </c>
       <c r="I14" s="2" t="s">
-        <v>105</v>
+        <v>35</v>
       </c>
       <c r="J14" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="K14" s="2">
-        <v>5.0</v>
-      </c>
-      <c r="L14" s="2">
-        <v>5.0</v>
-      </c>
-      <c r="M14" s="2">
-        <v>5.0</v>
-      </c>
-      <c r="N14" s="2">
-        <v>5.0</v>
-      </c>
-      <c r="O14" s="2">
-        <v>5.0</v>
-      </c>
-      <c r="P14" s="2">
-        <v>5.0</v>
-      </c>
-      <c r="Q14" s="2">
-        <v>4.0</v>
-      </c>
-      <c r="R14" s="2">
-        <v>5.0</v>
-      </c>
-      <c r="S14" s="2"/>
+        <v>110</v>
+      </c>
+      <c r="K14" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="L14" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="M14" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="N14" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="O14" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="P14" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="Q14" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="R14" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="S14" s="2" t="s">
+        <v>46</v>
+      </c>
       <c r="T14" s="2" t="s">
-        <v>44</v>
+        <v>111</v>
       </c>
       <c r="U14" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="V14" s="2"/>
+      <c r="V14" s="2" t="s">
+        <v>38</v>
+      </c>
       <c r="W14" s="2"/>
       <c r="X14" s="2"/>
       <c r="Y14" s="3"/>
       <c r="Z14" s="3"/>
+      <c r="AA14" s="3"/>
     </row>
     <row r="15">
       <c r="A15" s="2" t="s">
-        <v>106</v>
+        <v>112</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>107</v>
+        <v>113</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>108</v>
+        <v>114</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>109</v>
-      </c>
-      <c r="H15" s="2">
-        <v>6.0</v>
+        <v>33</v>
+      </c>
+      <c r="H15" s="2" t="s">
+        <v>115</v>
       </c>
       <c r="I15" s="2" t="s">
-        <v>110</v>
-      </c>
-      <c r="J15" s="2">
-        <v>4.0</v>
-      </c>
-      <c r="K15" s="2">
-        <v>4.0</v>
+        <v>35</v>
+      </c>
+      <c r="J15" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="K15" s="2" t="s">
+        <v>46</v>
       </c>
       <c r="L15" s="2">
-        <v>4.0</v>
-      </c>
-      <c r="M15" s="2">
-        <v>4.0</v>
-      </c>
-      <c r="N15" s="2">
-        <v>3.0</v>
-      </c>
-      <c r="O15" s="2">
-        <v>3.0</v>
+        <v>5.0</v>
+      </c>
+      <c r="M15" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="N15" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="O15" s="2" t="s">
+        <v>46</v>
       </c>
       <c r="P15" s="2">
-        <v>4.0</v>
+        <v>5.0</v>
       </c>
       <c r="Q15" s="2">
-        <v>3.0</v>
+        <v>5.0</v>
       </c>
       <c r="R15" s="2">
-        <v>4.0</v>
-      </c>
-      <c r="S15" s="2" t="s">
-        <v>111</v>
-      </c>
-      <c r="T15" s="2" t="s">
-        <v>36</v>
-      </c>
+        <v>5.0</v>
+      </c>
+      <c r="S15" s="2">
+        <v>5.0</v>
+      </c>
+      <c r="T15" s="2"/>
       <c r="U15" s="2" t="s">
-        <v>100</v>
-      </c>
-      <c r="V15" s="2"/>
+        <v>37</v>
+      </c>
+      <c r="V15" s="2" t="s">
+        <v>38</v>
+      </c>
       <c r="W15" s="2"/>
       <c r="X15" s="2"/>
       <c r="Y15" s="3"/>
       <c r="Z15" s="3"/>
+      <c r="AA15" s="3"/>
     </row>
     <row r="16">
       <c r="A16" s="2" t="s">
-        <v>112</v>
+        <v>117</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>39</v>
+        <v>28</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>113</v>
+        <v>118</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>114</v>
+        <v>119</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>115</v>
-      </c>
-      <c r="H16" s="2">
-        <v>9.0</v>
+        <v>33</v>
+      </c>
+      <c r="H16" s="2" t="s">
+        <v>120</v>
       </c>
       <c r="I16" s="2" t="s">
-        <v>116</v>
-      </c>
-      <c r="J16" s="2">
-        <v>5.0</v>
+        <v>35</v>
+      </c>
+      <c r="J16" s="2" t="s">
+        <v>121</v>
       </c>
       <c r="K16" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="L16" s="2">
-        <v>5.0</v>
-      </c>
-      <c r="M16" s="2">
-        <v>5.0</v>
-      </c>
-      <c r="N16" s="2">
-        <v>5.0</v>
-      </c>
-      <c r="O16" s="2">
-        <v>5.0</v>
+        <v>46</v>
+      </c>
+      <c r="L16" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="M16" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="N16" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="O16" s="2" t="s">
+        <v>46</v>
       </c>
       <c r="P16" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="Q16" s="2">
-        <v>5.0</v>
-      </c>
-      <c r="R16" s="2">
-        <v>5.0</v>
-      </c>
-      <c r="S16" s="2"/>
+        <v>46</v>
+      </c>
+      <c r="Q16" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="R16" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="S16" s="2" t="s">
+        <v>46</v>
+      </c>
       <c r="T16" s="2" t="s">
-        <v>44</v>
+        <v>122</v>
       </c>
       <c r="U16" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="V16" s="2"/>
+      <c r="V16" s="2" t="s">
+        <v>38</v>
+      </c>
       <c r="W16" s="2"/>
       <c r="X16" s="2"/>
       <c r="Y16" s="3"/>
       <c r="Z16" s="3"/>
+      <c r="AA16" s="3"/>
     </row>
     <row r="17">
       <c r="A17" s="2" t="s">
-        <v>117</v>
+        <v>123</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>39</v>
+        <v>28</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>118</v>
+        <v>124</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>119</v>
+        <v>125</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>120</v>
+        <v>33</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="I17" s="2" t="s">
-        <v>121</v>
+        <v>126</v>
+      </c>
+      <c r="I17" s="2">
+        <v>6.0</v>
       </c>
       <c r="J17" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="K17" s="2" t="s">
-        <v>35</v>
+        <v>127</v>
+      </c>
+      <c r="K17" s="2">
+        <v>5.0</v>
       </c>
       <c r="L17" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="M17" s="2" t="s">
-        <v>35</v>
+        <v>53</v>
+      </c>
+      <c r="M17" s="2">
+        <v>3.0</v>
       </c>
       <c r="N17" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="O17" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="P17" s="2" t="s">
-        <v>35</v>
+        <v>53</v>
+      </c>
+      <c r="O17" s="2">
+        <v>4.0</v>
+      </c>
+      <c r="P17" s="2">
+        <v>3.0</v>
       </c>
       <c r="Q17" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="R17" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="S17" s="2" t="s">
-        <v>122</v>
-      </c>
-      <c r="T17" s="2" t="s">
-        <v>44</v>
-      </c>
+        <v>53</v>
+      </c>
+      <c r="R17" s="2">
+        <v>4.0</v>
+      </c>
+      <c r="S17" s="2">
+        <v>4.0</v>
+      </c>
+      <c r="T17" s="2"/>
       <c r="U17" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="V17" s="2"/>
+      <c r="V17" s="2" t="s">
+        <v>61</v>
+      </c>
       <c r="W17" s="2"/>
       <c r="X17" s="2"/>
       <c r="Y17" s="3"/>
       <c r="Z17" s="3"/>
+      <c r="AA17" s="3"/>
     </row>
     <row r="18">
       <c r="A18" s="2" t="s">
-        <v>123</v>
+        <v>128</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>124</v>
+        <v>129</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>125</v>
+        <v>130</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="H18" s="2">
-        <v>4.0</v>
+        <v>43</v>
+      </c>
+      <c r="H18" s="2" t="s">
+        <v>131</v>
       </c>
       <c r="I18" s="2" t="s">
-        <v>127</v>
-      </c>
-      <c r="J18" s="2">
-        <v>3.0</v>
-      </c>
-      <c r="K18" s="2">
-        <v>3.0</v>
+        <v>35</v>
+      </c>
+      <c r="J18" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="K18" s="2" t="s">
+        <v>46</v>
       </c>
       <c r="L18" s="2" t="s">
-        <v>67</v>
+        <v>46</v>
       </c>
       <c r="M18" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="N18" s="2">
-        <v>2.0</v>
+        <v>46</v>
+      </c>
+      <c r="N18" s="2" t="s">
+        <v>46</v>
       </c>
       <c r="O18" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="P18" s="2">
-        <v>3.0</v>
-      </c>
-      <c r="Q18" s="2">
-        <v>3.0</v>
-      </c>
-      <c r="R18" s="2">
-        <v>5.0</v>
+        <v>46</v>
+      </c>
+      <c r="P18" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="Q18" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="R18" s="2" t="s">
+        <v>46</v>
       </c>
       <c r="S18" s="2" t="s">
-        <v>128</v>
+        <v>46</v>
       </c>
       <c r="T18" s="2" t="s">
-        <v>44</v>
+        <v>132</v>
       </c>
       <c r="U18" s="2" t="s">
-        <v>100</v>
-      </c>
-      <c r="V18" s="2"/>
+        <v>47</v>
+      </c>
+      <c r="V18" s="2" t="s">
+        <v>38</v>
+      </c>
       <c r="W18" s="2"/>
       <c r="X18" s="2"/>
       <c r="Y18" s="3"/>
       <c r="Z18" s="3"/>
+      <c r="AA18" s="3"/>
     </row>
     <row r="19">
       <c r="A19" s="2" t="s">
-        <v>129</v>
+        <v>133</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>130</v>
+        <v>134</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>131</v>
+        <v>135</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>132</v>
-      </c>
-      <c r="H19" s="2">
-        <v>8.0</v>
+        <v>33</v>
+      </c>
+      <c r="H19" s="2" t="s">
+        <v>136</v>
       </c>
       <c r="I19" s="2" t="s">
-        <v>133</v>
-      </c>
-      <c r="J19" s="2">
-        <v>5.0</v>
-      </c>
-      <c r="K19" s="2">
-        <v>5.0</v>
-      </c>
-      <c r="L19" s="2">
-        <v>4.0</v>
-      </c>
-      <c r="M19" s="2">
-        <v>3.0</v>
-      </c>
-      <c r="N19" s="2">
-        <v>5.0</v>
-      </c>
-      <c r="O19" s="2">
-        <v>5.0</v>
-      </c>
-      <c r="P19" s="2">
-        <v>4.0</v>
-      </c>
-      <c r="Q19" s="2">
-        <v>3.0</v>
-      </c>
-      <c r="R19" s="2">
-        <v>2.0</v>
+        <v>35</v>
+      </c>
+      <c r="J19" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="K19" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="L19" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="M19" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="N19" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="O19" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="P19" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="Q19" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="R19" s="2" t="s">
+        <v>46</v>
       </c>
       <c r="S19" s="2" t="s">
-        <v>134</v>
+        <v>46</v>
       </c>
       <c r="T19" s="2" t="s">
-        <v>36</v>
+        <v>138</v>
       </c>
       <c r="U19" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="V19" s="2"/>
+        <v>37</v>
+      </c>
+      <c r="V19" s="2" t="s">
+        <v>38</v>
+      </c>
       <c r="W19" s="2"/>
       <c r="X19" s="2"/>
       <c r="Y19" s="3"/>
       <c r="Z19" s="3"/>
+      <c r="AA19" s="3"/>
     </row>
     <row r="20">
       <c r="A20" s="2" t="s">
-        <v>135</v>
+        <v>139</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>136</v>
+        <v>140</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>138</v>
+        <v>33</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="I20" s="2" t="s">
-        <v>139</v>
+        <v>142</v>
+      </c>
+      <c r="I20" s="2">
+        <v>8.0</v>
       </c>
       <c r="J20" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="K20" s="2" t="s">
-        <v>35</v>
+        <v>143</v>
+      </c>
+      <c r="K20" s="2">
+        <v>5.0</v>
       </c>
       <c r="L20" s="2">
         <v>5.0</v>
@@ -2726,769 +3123,798 @@
       <c r="M20" s="2">
         <v>5.0</v>
       </c>
-      <c r="N20" s="2" t="s">
-        <v>35</v>
+      <c r="N20" s="2">
+        <v>5.0</v>
       </c>
       <c r="O20" s="2">
         <v>5.0</v>
       </c>
       <c r="P20" s="2">
-        <v>5.0</v>
-      </c>
-      <c r="Q20" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="R20" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="S20" s="2" t="s">
-        <v>140</v>
-      </c>
-      <c r="T20" s="2" t="s">
-        <v>36</v>
-      </c>
+        <v>4.0</v>
+      </c>
+      <c r="Q20" s="2">
+        <v>5.0</v>
+      </c>
+      <c r="R20" s="2">
+        <v>3.0</v>
+      </c>
+      <c r="S20" s="2">
+        <v>4.0</v>
+      </c>
+      <c r="T20" s="2"/>
       <c r="U20" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="V20" s="2"/>
+      <c r="V20" s="2" t="s">
+        <v>55</v>
+      </c>
       <c r="W20" s="2"/>
       <c r="X20" s="2"/>
       <c r="Y20" s="3"/>
       <c r="Z20" s="3"/>
+      <c r="AA20" s="3"/>
     </row>
     <row r="21">
       <c r="A21" s="2" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>27</v>
+        <v>40</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>144</v>
+        <v>43</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>33</v>
+        <v>147</v>
       </c>
       <c r="I21" s="2" t="s">
-        <v>145</v>
+        <v>35</v>
       </c>
       <c r="J21" s="2" t="s">
-        <v>35</v>
+        <v>148</v>
       </c>
       <c r="K21" s="2" t="s">
-        <v>35</v>
+        <v>46</v>
       </c>
       <c r="L21" s="2" t="s">
-        <v>35</v>
+        <v>46</v>
       </c>
       <c r="M21" s="2" t="s">
-        <v>35</v>
+        <v>46</v>
       </c>
       <c r="N21" s="2" t="s">
-        <v>35</v>
+        <v>46</v>
       </c>
       <c r="O21" s="2" t="s">
-        <v>35</v>
+        <v>46</v>
       </c>
       <c r="P21" s="2" t="s">
-        <v>35</v>
+        <v>46</v>
       </c>
       <c r="Q21" s="2" t="s">
-        <v>35</v>
+        <v>46</v>
       </c>
       <c r="R21" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="S21" s="2"/>
-      <c r="T21" s="2" t="s">
-        <v>36</v>
-      </c>
+        <v>46</v>
+      </c>
+      <c r="S21" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="T21" s="2"/>
       <c r="U21" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="V21" s="2"/>
+        <v>47</v>
+      </c>
+      <c r="V21" s="2" t="s">
+        <v>38</v>
+      </c>
       <c r="W21" s="2"/>
       <c r="X21" s="2"/>
       <c r="Y21" s="3"/>
       <c r="Z21" s="3"/>
+      <c r="AA21" s="3"/>
     </row>
     <row r="22">
       <c r="A22" s="2" t="s">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>149</v>
+        <v>33</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>33</v>
+        <v>152</v>
       </c>
       <c r="I22" s="2" t="s">
-        <v>150</v>
+        <v>35</v>
       </c>
       <c r="J22" s="2" t="s">
-        <v>35</v>
+        <v>153</v>
       </c>
       <c r="K22" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="L22" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="M22" s="2">
-        <v>5.0</v>
+        <v>46</v>
+      </c>
+      <c r="L22" s="2">
+        <v>4.0</v>
+      </c>
+      <c r="M22" s="2" t="s">
+        <v>46</v>
       </c>
       <c r="N22" s="2">
-        <v>5.0</v>
-      </c>
-      <c r="O22" s="2">
-        <v>5.0</v>
-      </c>
-      <c r="P22" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="Q22" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="R22" s="2" t="s">
-        <v>35</v>
+        <v>3.0</v>
+      </c>
+      <c r="O22" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="P22" s="2">
+        <v>4.0</v>
+      </c>
+      <c r="Q22" s="2">
+        <v>5.0</v>
+      </c>
+      <c r="R22" s="2">
+        <v>5.0</v>
       </c>
       <c r="S22" s="2" t="s">
-        <v>150</v>
-      </c>
-      <c r="T22" s="2" t="s">
-        <v>36</v>
-      </c>
+        <v>46</v>
+      </c>
+      <c r="T22" s="2"/>
       <c r="U22" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="V22" s="2"/>
+      <c r="V22" s="2" t="s">
+        <v>38</v>
+      </c>
       <c r="W22" s="2"/>
       <c r="X22" s="2"/>
       <c r="Y22" s="3"/>
       <c r="Z22" s="3"/>
+      <c r="AA22" s="3"/>
     </row>
     <row r="23">
       <c r="A23" s="2" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>39</v>
+        <v>28</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>154</v>
+        <v>33</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>33</v>
+        <v>157</v>
       </c>
       <c r="I23" s="2" t="s">
-        <v>155</v>
-      </c>
-      <c r="J23" s="2">
-        <v>5.0</v>
-      </c>
-      <c r="K23" s="2">
-        <v>5.0</v>
-      </c>
-      <c r="L23" s="2">
-        <v>5.0</v>
-      </c>
-      <c r="M23" s="2">
-        <v>4.0</v>
-      </c>
-      <c r="N23" s="2">
-        <v>4.0</v>
-      </c>
-      <c r="O23" s="2">
-        <v>5.0</v>
-      </c>
-      <c r="P23" s="2">
-        <v>5.0</v>
-      </c>
-      <c r="Q23" s="2">
-        <v>5.0</v>
-      </c>
-      <c r="R23" s="2">
-        <v>5.0</v>
-      </c>
-      <c r="S23" s="2"/>
+        <v>35</v>
+      </c>
+      <c r="J23" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="K23" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="L23" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="M23" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="N23" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="O23" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="P23" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="Q23" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="R23" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="S23" s="2" t="s">
+        <v>46</v>
+      </c>
       <c r="T23" s="2" t="s">
-        <v>44</v>
+        <v>159</v>
       </c>
       <c r="U23" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="V23" s="2"/>
+      <c r="V23" s="2" t="s">
+        <v>38</v>
+      </c>
       <c r="W23" s="2"/>
       <c r="X23" s="2"/>
       <c r="Y23" s="3"/>
       <c r="Z23" s="3"/>
+      <c r="AA23" s="3"/>
     </row>
     <row r="24">
       <c r="A24" s="2" t="s">
-        <v>156</v>
+        <v>160</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>39</v>
+        <v>28</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>157</v>
+        <v>161</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>158</v>
+        <v>162</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>159</v>
+        <v>33</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="I24" s="2" t="s">
-        <v>160</v>
-      </c>
-      <c r="J24" s="2">
-        <v>5.0</v>
+        <v>163</v>
+      </c>
+      <c r="I24" s="2">
+        <v>8.0</v>
+      </c>
+      <c r="J24" s="2" t="s">
+        <v>164</v>
       </c>
       <c r="K24" s="2" t="s">
-        <v>35</v>
+        <v>46</v>
       </c>
       <c r="L24" s="2">
-        <v>5.0</v>
-      </c>
-      <c r="M24" s="2" t="s">
-        <v>35</v>
+        <v>4.0</v>
+      </c>
+      <c r="M24" s="2">
+        <v>4.0</v>
       </c>
       <c r="N24" s="2">
-        <v>5.0</v>
+        <v>4.0</v>
       </c>
       <c r="O24" s="2">
-        <v>5.0</v>
-      </c>
-      <c r="P24" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="Q24" s="2" t="s">
-        <v>35</v>
+        <v>4.0</v>
+      </c>
+      <c r="P24" s="2">
+        <v>4.0</v>
+      </c>
+      <c r="Q24" s="2">
+        <v>5.0</v>
       </c>
       <c r="R24" s="2">
         <v>5.0</v>
       </c>
-      <c r="S24" s="2"/>
-      <c r="T24" s="2" t="s">
-        <v>44</v>
-      </c>
+      <c r="S24" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="T24" s="2"/>
       <c r="U24" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="V24" s="2"/>
+      <c r="V24" s="2" t="s">
+        <v>55</v>
+      </c>
       <c r="W24" s="2"/>
       <c r="X24" s="2"/>
       <c r="Y24" s="3"/>
       <c r="Z24" s="3"/>
+      <c r="AA24" s="3"/>
     </row>
     <row r="25">
       <c r="A25" s="2" t="s">
-        <v>161</v>
+        <v>165</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>39</v>
+        <v>28</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>162</v>
+        <v>166</v>
       </c>
       <c r="F25" s="2" t="s">
-        <v>163</v>
+        <v>167</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>164</v>
+        <v>33</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>33</v>
+        <v>168</v>
       </c>
       <c r="I25" s="2" t="s">
-        <v>165</v>
-      </c>
-      <c r="J25" s="2">
-        <v>5.0</v>
+        <v>35</v>
+      </c>
+      <c r="J25" s="2" t="s">
+        <v>169</v>
       </c>
       <c r="K25" s="2" t="s">
-        <v>35</v>
+        <v>46</v>
       </c>
       <c r="L25" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="M25" s="2" t="s">
-        <v>35</v>
+        <v>46</v>
+      </c>
+      <c r="M25" s="2">
+        <v>5.0</v>
       </c>
       <c r="N25" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="O25" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="P25" s="2" t="s">
-        <v>35</v>
+        <v>46</v>
+      </c>
+      <c r="O25" s="2">
+        <v>5.0</v>
+      </c>
+      <c r="P25" s="2">
+        <v>5.0</v>
       </c>
       <c r="Q25" s="2" t="s">
-        <v>35</v>
+        <v>46</v>
       </c>
       <c r="R25" s="2" t="s">
-        <v>35</v>
+        <v>46</v>
       </c>
       <c r="S25" s="2" t="s">
-        <v>166</v>
-      </c>
-      <c r="T25" s="2" t="s">
-        <v>44</v>
-      </c>
+        <v>46</v>
+      </c>
+      <c r="T25" s="2"/>
       <c r="U25" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="V25" s="2"/>
+      <c r="V25" s="2" t="s">
+        <v>38</v>
+      </c>
       <c r="W25" s="2"/>
       <c r="X25" s="2"/>
       <c r="Y25" s="3"/>
       <c r="Z25" s="3"/>
+      <c r="AA25" s="3"/>
     </row>
     <row r="26">
       <c r="A26" s="2" t="s">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>168</v>
+        <v>171</v>
       </c>
       <c r="F26" s="2" t="s">
-        <v>169</v>
+        <v>172</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>170</v>
+        <v>43</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="I26" s="2" t="s">
-        <v>171</v>
+        <v>173</v>
+      </c>
+      <c r="I26" s="2">
+        <v>7.0</v>
       </c>
       <c r="J26" s="2" t="s">
-        <v>35</v>
+        <v>174</v>
       </c>
       <c r="K26" s="2" t="s">
-        <v>35</v>
+        <v>46</v>
       </c>
       <c r="L26" s="2" t="s">
-        <v>35</v>
+        <v>46</v>
       </c>
       <c r="M26" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="N26" s="2" t="s">
-        <v>35</v>
+        <v>46</v>
+      </c>
+      <c r="N26" s="2">
+        <v>4.0</v>
       </c>
       <c r="O26" s="2" t="s">
-        <v>35</v>
+        <v>53</v>
       </c>
       <c r="P26" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="Q26" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="R26" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="S26" s="2" t="s">
-        <v>172</v>
+        <v>46</v>
+      </c>
+      <c r="Q26" s="2">
+        <v>5.0</v>
+      </c>
+      <c r="R26" s="2">
+        <v>5.0</v>
+      </c>
+      <c r="S26" s="2">
+        <v>5.0</v>
       </c>
       <c r="T26" s="2" t="s">
-        <v>44</v>
+        <v>175</v>
       </c>
       <c r="U26" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="V26" s="2"/>
+        <v>47</v>
+      </c>
+      <c r="V26" s="2" t="s">
+        <v>55</v>
+      </c>
       <c r="W26" s="2"/>
       <c r="X26" s="2"/>
       <c r="Y26" s="3"/>
       <c r="Z26" s="3"/>
+      <c r="AA26" s="3"/>
     </row>
     <row r="27">
       <c r="A27" s="2" t="s">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>39</v>
+        <v>28</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="F27" s="2" t="s">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>176</v>
-      </c>
-      <c r="H27" s="2">
-        <v>6.0</v>
+        <v>33</v>
+      </c>
+      <c r="H27" s="2" t="s">
+        <v>179</v>
       </c>
       <c r="I27" s="2" t="s">
-        <v>177</v>
-      </c>
-      <c r="J27" s="2">
-        <v>5.0</v>
-      </c>
-      <c r="K27" s="2">
-        <v>5.0</v>
-      </c>
-      <c r="L27" s="2">
-        <v>5.0</v>
-      </c>
-      <c r="M27" s="2">
-        <v>5.0</v>
+        <v>35</v>
+      </c>
+      <c r="J27" s="2" t="s">
+        <v>180</v>
+      </c>
+      <c r="K27" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="L27" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="M27" s="2" t="s">
+        <v>46</v>
       </c>
       <c r="N27" s="2">
-        <v>5.0</v>
+        <v>4.0</v>
       </c>
       <c r="O27" s="2">
         <v>5.0</v>
       </c>
       <c r="P27" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="Q27" s="2">
-        <v>5.0</v>
+        <v>46</v>
+      </c>
+      <c r="Q27" s="2" t="s">
+        <v>46</v>
       </c>
       <c r="R27" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="S27" s="2"/>
-      <c r="T27" s="2" t="s">
-        <v>44</v>
-      </c>
+        <v>46</v>
+      </c>
+      <c r="S27" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="T27" s="2"/>
       <c r="U27" s="2" t="s">
-        <v>100</v>
-      </c>
-      <c r="V27" s="2"/>
+        <v>37</v>
+      </c>
+      <c r="V27" s="2" t="s">
+        <v>38</v>
+      </c>
       <c r="W27" s="2"/>
       <c r="X27" s="2"/>
       <c r="Y27" s="3"/>
       <c r="Z27" s="3"/>
+      <c r="AA27" s="3"/>
     </row>
     <row r="28">
       <c r="A28" s="2" t="s">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="F28" s="2" t="s">
-        <v>180</v>
+        <v>183</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>181</v>
-      </c>
-      <c r="H28" s="2">
-        <v>9.0</v>
-      </c>
-      <c r="I28" s="2" t="s">
-        <v>182</v>
-      </c>
-      <c r="J28" s="2">
-        <v>5.0</v>
+        <v>43</v>
+      </c>
+      <c r="H28" s="2" t="s">
+        <v>184</v>
+      </c>
+      <c r="I28" s="2">
+        <v>7.0</v>
+      </c>
+      <c r="J28" s="2" t="s">
+        <v>185</v>
       </c>
       <c r="K28" s="2">
         <v>5.0</v>
       </c>
       <c r="L28" s="2">
-        <v>5.0</v>
+        <v>3.0</v>
       </c>
       <c r="M28" s="2">
-        <v>5.0</v>
+        <v>3.0</v>
       </c>
       <c r="N28" s="2">
-        <v>5.0</v>
+        <v>4.0</v>
       </c>
       <c r="O28" s="2">
         <v>5.0</v>
       </c>
       <c r="P28" s="2">
-        <v>5.0</v>
-      </c>
-      <c r="Q28" s="2">
-        <v>5.0</v>
-      </c>
-      <c r="R28" s="2">
-        <v>5.0</v>
-      </c>
-      <c r="S28" s="2"/>
+        <v>4.0</v>
+      </c>
+      <c r="Q28" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="R28" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="S28" s="2">
+        <v>5.0</v>
+      </c>
       <c r="T28" s="2" t="s">
-        <v>44</v>
+        <v>186</v>
       </c>
       <c r="U28" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="V28" s="2"/>
+        <v>47</v>
+      </c>
+      <c r="V28" s="2" t="s">
+        <v>55</v>
+      </c>
       <c r="W28" s="2"/>
       <c r="X28" s="2"/>
       <c r="Y28" s="3"/>
       <c r="Z28" s="3"/>
+      <c r="AA28" s="3"/>
     </row>
     <row r="29">
       <c r="A29" s="2" t="s">
-        <v>183</v>
+        <v>187</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>39</v>
+        <v>28</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>184</v>
+        <v>188</v>
       </c>
       <c r="F29" s="2" t="s">
-        <v>185</v>
+        <v>189</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>186</v>
-      </c>
-      <c r="H29" s="2">
-        <v>9.0</v>
+        <v>33</v>
+      </c>
+      <c r="H29" s="2" t="s">
+        <v>190</v>
       </c>
       <c r="I29" s="2" t="s">
-        <v>187</v>
-      </c>
-      <c r="J29" s="2">
-        <v>5.0</v>
-      </c>
-      <c r="K29" s="2">
-        <v>5.0</v>
+        <v>35</v>
+      </c>
+      <c r="J29" s="2" t="s">
+        <v>191</v>
+      </c>
+      <c r="K29" s="2" t="s">
+        <v>46</v>
       </c>
       <c r="L29" s="2">
         <v>5.0</v>
       </c>
-      <c r="M29" s="2">
-        <v>5.0</v>
+      <c r="M29" s="2" t="s">
+        <v>46</v>
       </c>
       <c r="N29" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="O29" s="2" t="s">
-        <v>35</v>
+        <v>46</v>
+      </c>
+      <c r="O29" s="2">
+        <v>4.0</v>
       </c>
       <c r="P29" s="2">
         <v>5.0</v>
       </c>
-      <c r="Q29" s="2">
-        <v>5.0</v>
+      <c r="Q29" s="2" t="s">
+        <v>46</v>
       </c>
       <c r="R29" s="2">
-        <v>5.0</v>
-      </c>
-      <c r="S29" s="2"/>
-      <c r="T29" s="2" t="s">
-        <v>44</v>
-      </c>
+        <v>4.0</v>
+      </c>
+      <c r="S29" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="T29" s="2"/>
       <c r="U29" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="V29" s="2"/>
+      <c r="V29" s="2" t="s">
+        <v>38</v>
+      </c>
       <c r="W29" s="2"/>
       <c r="X29" s="2"/>
       <c r="Y29" s="3"/>
       <c r="Z29" s="3"/>
+      <c r="AA29" s="3"/>
     </row>
     <row r="30">
       <c r="A30" s="2" t="s">
-        <v>188</v>
+        <v>192</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>39</v>
+        <v>28</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>189</v>
+        <v>193</v>
       </c>
       <c r="F30" s="2" t="s">
-        <v>190</v>
+        <v>194</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>191</v>
+        <v>33</v>
       </c>
       <c r="H30" s="2" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="I30" s="2" t="s">
-        <v>193</v>
-      </c>
-      <c r="J30" s="2">
-        <v>4.0</v>
+        <v>35</v>
+      </c>
+      <c r="J30" s="2" t="s">
+        <v>196</v>
       </c>
       <c r="K30" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="L30" s="2">
-        <v>3.0</v>
+        <v>46</v>
+      </c>
+      <c r="L30" s="2" t="s">
+        <v>46</v>
       </c>
       <c r="M30" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="N30" s="2">
-        <v>2.0</v>
+        <v>46</v>
+      </c>
+      <c r="N30" s="2" t="s">
+        <v>46</v>
       </c>
       <c r="O30" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="P30" s="2">
-        <v>4.0</v>
-      </c>
-      <c r="Q30" s="2">
-        <v>4.0</v>
-      </c>
-      <c r="R30" s="2">
-        <v>3.0</v>
+        <v>46</v>
+      </c>
+      <c r="P30" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="Q30" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="R30" s="2" t="s">
+        <v>46</v>
       </c>
       <c r="S30" s="2" t="s">
-        <v>194</v>
-      </c>
-      <c r="T30" s="2" t="s">
-        <v>44</v>
-      </c>
+        <v>46</v>
+      </c>
+      <c r="T30" s="2"/>
       <c r="U30" s="2" t="s">
-        <v>100</v>
-      </c>
-      <c r="V30" s="2"/>
+        <v>37</v>
+      </c>
+      <c r="V30" s="2" t="s">
+        <v>38</v>
+      </c>
       <c r="W30" s="2"/>
       <c r="X30" s="2"/>
       <c r="Y30" s="3"/>
       <c r="Z30" s="3"/>
+      <c r="AA30" s="3"/>
     </row>
     <row r="31">
       <c r="A31" s="2" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>39</v>
+        <v>28</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="F31" s="2" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="G31" s="2" t="s">
-        <v>198</v>
-      </c>
-      <c r="H31" s="2">
-        <v>9.0</v>
+        <v>33</v>
+      </c>
+      <c r="H31" s="2" t="s">
+        <v>200</v>
       </c>
       <c r="I31" s="2" t="s">
-        <v>199</v>
-      </c>
-      <c r="J31" s="2">
-        <v>5.0</v>
-      </c>
-      <c r="K31" s="2">
-        <v>4.0</v>
-      </c>
-      <c r="L31" s="2">
-        <v>5.0</v>
+        <v>35</v>
+      </c>
+      <c r="J31" s="2" t="s">
+        <v>201</v>
+      </c>
+      <c r="K31" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="L31" s="2" t="s">
+        <v>46</v>
       </c>
       <c r="M31" s="2">
         <v>5.0</v>
       </c>
-      <c r="N31" s="2">
-        <v>5.0</v>
-      </c>
-      <c r="O31" s="2">
-        <v>5.0</v>
+      <c r="N31" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="O31" s="2" t="s">
+        <v>46</v>
       </c>
       <c r="P31" s="2">
         <v>5.0</v>
@@ -3497,863 +3923,900 @@
         <v>5.0</v>
       </c>
       <c r="R31" s="2">
-        <v>5.0</v>
-      </c>
-      <c r="S31" s="2"/>
-      <c r="T31" s="2" t="s">
-        <v>44</v>
-      </c>
+        <v>3.0</v>
+      </c>
+      <c r="S31" s="2">
+        <v>5.0</v>
+      </c>
+      <c r="T31" s="2"/>
       <c r="U31" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="V31" s="2"/>
+      <c r="V31" s="2" t="s">
+        <v>38</v>
+      </c>
       <c r="W31" s="2"/>
       <c r="X31" s="2"/>
       <c r="Y31" s="3"/>
       <c r="Z31" s="3"/>
+      <c r="AA31" s="3"/>
     </row>
     <row r="32">
       <c r="A32" s="2" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E32" s="2" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="F32" s="2" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="G32" s="2" t="s">
-        <v>203</v>
+        <v>33</v>
       </c>
       <c r="H32" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="I32" s="2" t="s">
-        <v>204</v>
+        <v>205</v>
+      </c>
+      <c r="I32" s="2">
+        <v>3.0</v>
       </c>
       <c r="J32" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="K32" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="L32" s="2" t="s">
-        <v>35</v>
+        <v>206</v>
+      </c>
+      <c r="K32" s="2">
+        <v>4.0</v>
+      </c>
+      <c r="L32" s="2">
+        <v>3.0</v>
       </c>
       <c r="M32" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="N32" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="O32" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="P32" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="Q32" s="2" t="s">
-        <v>35</v>
+        <v>46</v>
+      </c>
+      <c r="N32" s="2">
+        <v>4.0</v>
+      </c>
+      <c r="O32" s="2">
+        <v>4.0</v>
+      </c>
+      <c r="P32" s="2">
+        <v>4.0</v>
+      </c>
+      <c r="Q32" s="2">
+        <v>2.0</v>
       </c>
       <c r="R32" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="S32" s="2"/>
-      <c r="T32" s="2" t="s">
-        <v>36</v>
-      </c>
+        <v>46</v>
+      </c>
+      <c r="S32" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="T32" s="2"/>
       <c r="U32" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="V32" s="2"/>
+      <c r="V32" s="2" t="s">
+        <v>61</v>
+      </c>
       <c r="W32" s="2"/>
       <c r="X32" s="2"/>
       <c r="Y32" s="3"/>
       <c r="Z32" s="3"/>
+      <c r="AA32" s="3"/>
     </row>
     <row r="33">
       <c r="A33" s="2" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E33" s="2" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="F33" s="2" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="G33" s="2" t="s">
-        <v>208</v>
-      </c>
-      <c r="H33" s="2">
-        <v>8.0</v>
+        <v>33</v>
+      </c>
+      <c r="H33" s="2" t="s">
+        <v>210</v>
       </c>
       <c r="I33" s="2" t="s">
-        <v>209</v>
-      </c>
-      <c r="J33" s="2">
-        <v>5.0</v>
+        <v>35</v>
+      </c>
+      <c r="J33" s="2" t="s">
+        <v>211</v>
       </c>
       <c r="K33" s="2" t="s">
-        <v>35</v>
+        <v>46</v>
       </c>
       <c r="L33" s="2">
         <v>5.0</v>
       </c>
       <c r="M33" s="2">
-        <v>3.0</v>
+        <v>5.0</v>
       </c>
       <c r="N33" s="2">
-        <v>4.0</v>
-      </c>
-      <c r="O33" s="2" t="s">
-        <v>35</v>
+        <v>5.0</v>
+      </c>
+      <c r="O33" s="2">
+        <v>5.0</v>
       </c>
       <c r="P33" s="2">
         <v>5.0</v>
       </c>
-      <c r="Q33" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="R33" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="S33" s="2" t="s">
-        <v>210</v>
-      </c>
-      <c r="T33" s="2" t="s">
-        <v>36</v>
-      </c>
+      <c r="Q33" s="2">
+        <v>5.0</v>
+      </c>
+      <c r="R33" s="2">
+        <v>4.0</v>
+      </c>
+      <c r="S33" s="2">
+        <v>5.0</v>
+      </c>
+      <c r="T33" s="2"/>
       <c r="U33" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="V33" s="2"/>
+        <v>37</v>
+      </c>
+      <c r="V33" s="2" t="s">
+        <v>38</v>
+      </c>
       <c r="W33" s="2"/>
       <c r="X33" s="2"/>
       <c r="Y33" s="3"/>
       <c r="Z33" s="3"/>
+      <c r="AA33" s="3"/>
     </row>
     <row r="34">
-      <c r="A34" s="2" t="s">
-        <v>211</v>
-      </c>
-      <c r="B34" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="C34" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="D34" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="E34" s="2" t="s">
+      <c r="A34" s="5" t="s">
         <v>212</v>
       </c>
-      <c r="F34" s="2" t="s">
+      <c r="B34" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="C34" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="D34" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="E34" s="5" t="s">
         <v>213</v>
       </c>
-      <c r="G34" s="2" t="s">
+      <c r="F34" s="5" t="s">
         <v>214</v>
       </c>
-      <c r="H34" s="2">
-        <v>5.0</v>
-      </c>
-      <c r="I34" s="2" t="s">
+      <c r="G34" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="H34" s="5" t="s">
         <v>215</v>
       </c>
-      <c r="J34" s="2">
-        <v>5.0</v>
-      </c>
-      <c r="K34" s="2">
-        <v>5.0</v>
-      </c>
-      <c r="L34" s="2">
-        <v>4.0</v>
-      </c>
-      <c r="M34" s="2">
-        <v>5.0</v>
-      </c>
-      <c r="N34" s="2">
-        <v>5.0</v>
-      </c>
-      <c r="O34" s="2">
-        <v>4.0</v>
-      </c>
-      <c r="P34" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="Q34" s="2">
+      <c r="I34" s="5">
+        <v>6.0</v>
+      </c>
+      <c r="J34" s="5" t="s">
+        <v>216</v>
+      </c>
+      <c r="K34" s="5">
+        <v>4.0</v>
+      </c>
+      <c r="L34" s="5">
+        <v>4.0</v>
+      </c>
+      <c r="M34" s="5">
+        <v>4.0</v>
+      </c>
+      <c r="N34" s="5">
+        <v>4.0</v>
+      </c>
+      <c r="O34" s="5">
         <v>3.0</v>
       </c>
-      <c r="R34" s="2">
-        <v>5.0</v>
-      </c>
-      <c r="S34" s="2" t="s">
-        <v>216</v>
-      </c>
-      <c r="T34" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="U34" s="2" t="s">
-        <v>100</v>
-      </c>
-      <c r="V34" s="2"/>
-      <c r="W34" s="2"/>
-      <c r="X34" s="2"/>
-      <c r="Y34" s="3"/>
-      <c r="Z34" s="3"/>
+      <c r="P34" s="5">
+        <v>3.0</v>
+      </c>
+      <c r="Q34" s="5">
+        <v>4.0</v>
+      </c>
+      <c r="R34" s="5">
+        <v>3.0</v>
+      </c>
+      <c r="S34" s="5">
+        <v>4.0</v>
+      </c>
+      <c r="T34" s="5" t="s">
+        <v>217</v>
+      </c>
+      <c r="U34" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="V34" s="5" t="s">
+        <v>61</v>
+      </c>
+      <c r="W34" s="5"/>
+      <c r="X34" s="5"/>
+      <c r="Y34" s="6"/>
+      <c r="Z34" s="6"/>
+      <c r="AA34" s="6"/>
     </row>
     <row r="35">
       <c r="A35" s="2" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E35" s="2" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="F35" s="2" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="G35" s="2" t="s">
-        <v>220</v>
+        <v>33</v>
       </c>
       <c r="H35" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="I35" s="2" t="s">
         <v>221</v>
       </c>
+      <c r="I35" s="2">
+        <v>9.0</v>
+      </c>
       <c r="J35" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="K35" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="L35" s="2">
-        <v>4.0</v>
-      </c>
-      <c r="M35" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="N35" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="O35" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="P35" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="Q35" s="2">
-        <v>4.0</v>
-      </c>
-      <c r="R35" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="S35" s="2"/>
-      <c r="T35" s="2" t="s">
-        <v>36</v>
-      </c>
+        <v>222</v>
+      </c>
+      <c r="K35" s="2">
+        <v>5.0</v>
+      </c>
+      <c r="L35" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="M35" s="2">
+        <v>5.0</v>
+      </c>
+      <c r="N35" s="2">
+        <v>5.0</v>
+      </c>
+      <c r="O35" s="2">
+        <v>5.0</v>
+      </c>
+      <c r="P35" s="2">
+        <v>5.0</v>
+      </c>
+      <c r="Q35" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="R35" s="2">
+        <v>5.0</v>
+      </c>
+      <c r="S35" s="2">
+        <v>5.0</v>
+      </c>
+      <c r="T35" s="2"/>
       <c r="U35" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="V35" s="2"/>
+      <c r="V35" s="2" t="s">
+        <v>38</v>
+      </c>
       <c r="W35" s="2"/>
       <c r="X35" s="2"/>
       <c r="Y35" s="3"/>
       <c r="Z35" s="3"/>
+      <c r="AA35" s="3"/>
     </row>
     <row r="36">
       <c r="A36" s="2" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E36" s="2" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="F36" s="2" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="G36" s="2" t="s">
-        <v>225</v>
+        <v>33</v>
       </c>
       <c r="H36" s="2" t="s">
-        <v>33</v>
+        <v>226</v>
       </c>
       <c r="I36" s="2" t="s">
-        <v>226</v>
+        <v>35</v>
       </c>
       <c r="J36" s="2" t="s">
-        <v>35</v>
+        <v>227</v>
       </c>
       <c r="K36" s="2" t="s">
-        <v>35</v>
+        <v>46</v>
       </c>
       <c r="L36" s="2" t="s">
-        <v>35</v>
+        <v>46</v>
       </c>
       <c r="M36" s="2" t="s">
-        <v>35</v>
+        <v>46</v>
       </c>
       <c r="N36" s="2" t="s">
-        <v>35</v>
+        <v>46</v>
       </c>
       <c r="O36" s="2" t="s">
-        <v>35</v>
+        <v>46</v>
       </c>
       <c r="P36" s="2" t="s">
-        <v>35</v>
+        <v>46</v>
       </c>
       <c r="Q36" s="2" t="s">
-        <v>35</v>
+        <v>46</v>
       </c>
       <c r="R36" s="2" t="s">
-        <v>35</v>
+        <v>46</v>
       </c>
       <c r="S36" s="2" t="s">
-        <v>227</v>
+        <v>46</v>
       </c>
       <c r="T36" s="2" t="s">
-        <v>36</v>
+        <v>228</v>
       </c>
       <c r="U36" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="V36" s="2"/>
+      <c r="V36" s="2" t="s">
+        <v>38</v>
+      </c>
       <c r="W36" s="2"/>
       <c r="X36" s="2"/>
       <c r="Y36" s="3"/>
       <c r="Z36" s="3"/>
+      <c r="AA36" s="3"/>
     </row>
     <row r="37">
       <c r="A37" s="2" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E37" s="2" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="F37" s="2" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="G37" s="2" t="s">
-        <v>231</v>
-      </c>
-      <c r="H37" s="2">
-        <v>9.0</v>
-      </c>
-      <c r="I37" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="H37" s="2" t="s">
         <v>232</v>
       </c>
+      <c r="I37" s="2">
+        <v>4.0</v>
+      </c>
       <c r="J37" s="2" t="s">
-        <v>35</v>
+        <v>233</v>
       </c>
       <c r="K37" s="2">
-        <v>5.0</v>
+        <v>3.0</v>
       </c>
       <c r="L37" s="2">
-        <v>5.0</v>
+        <v>3.0</v>
       </c>
       <c r="M37" s="2" t="s">
-        <v>35</v>
+        <v>53</v>
       </c>
       <c r="N37" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="O37" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="P37" s="2">
-        <v>5.0</v>
+        <v>53</v>
+      </c>
+      <c r="O37" s="2">
+        <v>2.0</v>
+      </c>
+      <c r="P37" s="2" t="s">
+        <v>53</v>
       </c>
       <c r="Q37" s="2">
-        <v>5.0</v>
-      </c>
-      <c r="R37" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="S37" s="2" t="s">
-        <v>233</v>
+        <v>3.0</v>
+      </c>
+      <c r="R37" s="2">
+        <v>3.0</v>
+      </c>
+      <c r="S37" s="2">
+        <v>5.0</v>
       </c>
       <c r="T37" s="2" t="s">
-        <v>36</v>
+        <v>234</v>
       </c>
       <c r="U37" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="V37" s="2"/>
+      <c r="V37" s="2" t="s">
+        <v>61</v>
+      </c>
       <c r="W37" s="2"/>
       <c r="X37" s="2"/>
       <c r="Y37" s="3"/>
       <c r="Z37" s="3"/>
+      <c r="AA37" s="3"/>
     </row>
     <row r="38">
       <c r="A38" s="2" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>27</v>
+        <v>40</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E38" s="2" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="F38" s="2" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="G38" s="2" t="s">
-        <v>237</v>
+        <v>43</v>
       </c>
       <c r="H38" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="I38" s="2" t="s">
         <v>238</v>
       </c>
+      <c r="I38" s="2">
+        <v>8.0</v>
+      </c>
       <c r="J38" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="K38" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="L38" s="2" t="s">
-        <v>35</v>
+        <v>239</v>
+      </c>
+      <c r="K38" s="2">
+        <v>5.0</v>
+      </c>
+      <c r="L38" s="2">
+        <v>5.0</v>
       </c>
       <c r="M38" s="2">
         <v>4.0</v>
       </c>
-      <c r="N38" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="O38" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="P38" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="Q38" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="R38" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="S38" s="2" t="s">
-        <v>239</v>
+      <c r="N38" s="2">
+        <v>3.0</v>
+      </c>
+      <c r="O38" s="2">
+        <v>5.0</v>
+      </c>
+      <c r="P38" s="2">
+        <v>5.0</v>
+      </c>
+      <c r="Q38" s="2">
+        <v>4.0</v>
+      </c>
+      <c r="R38" s="2">
+        <v>3.0</v>
+      </c>
+      <c r="S38" s="2">
+        <v>2.0</v>
       </c>
       <c r="T38" s="2" t="s">
-        <v>36</v>
+        <v>240</v>
       </c>
       <c r="U38" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="V38" s="2"/>
+        <v>47</v>
+      </c>
+      <c r="V38" s="2" t="s">
+        <v>55</v>
+      </c>
       <c r="W38" s="2"/>
       <c r="X38" s="2"/>
       <c r="Y38" s="3"/>
       <c r="Z38" s="3"/>
+      <c r="AA38" s="3"/>
     </row>
     <row r="39">
       <c r="A39" s="2" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>27</v>
+        <v>40</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D39" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E39" s="2" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="F39" s="2" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="G39" s="2" t="s">
-        <v>243</v>
+        <v>43</v>
       </c>
       <c r="H39" s="2" t="s">
-        <v>33</v>
+        <v>244</v>
       </c>
       <c r="I39" s="2" t="s">
-        <v>244</v>
+        <v>35</v>
       </c>
       <c r="J39" s="2" t="s">
-        <v>35</v>
+        <v>245</v>
       </c>
       <c r="K39" s="2" t="s">
-        <v>35</v>
+        <v>46</v>
       </c>
       <c r="L39" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="M39" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="N39" s="2" t="s">
-        <v>35</v>
+        <v>46</v>
+      </c>
+      <c r="M39" s="2">
+        <v>5.0</v>
+      </c>
+      <c r="N39" s="2">
+        <v>5.0</v>
       </c>
       <c r="O39" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="P39" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="Q39" s="2" t="s">
-        <v>35</v>
+        <v>46</v>
+      </c>
+      <c r="P39" s="2">
+        <v>5.0</v>
+      </c>
+      <c r="Q39" s="2">
+        <v>5.0</v>
       </c>
       <c r="R39" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="S39" s="2"/>
+        <v>46</v>
+      </c>
+      <c r="S39" s="2" t="s">
+        <v>46</v>
+      </c>
       <c r="T39" s="2" t="s">
-        <v>36</v>
+        <v>246</v>
       </c>
       <c r="U39" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="V39" s="2"/>
+        <v>47</v>
+      </c>
+      <c r="V39" s="2" t="s">
+        <v>38</v>
+      </c>
       <c r="W39" s="2"/>
       <c r="X39" s="2"/>
       <c r="Y39" s="3"/>
       <c r="Z39" s="3"/>
+      <c r="AA39" s="3"/>
     </row>
     <row r="40">
       <c r="A40" s="2" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>27</v>
+        <v>40</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E40" s="2" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="F40" s="2" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="G40" s="2" t="s">
-        <v>248</v>
-      </c>
-      <c r="H40" s="2">
-        <v>8.0</v>
+        <v>43</v>
+      </c>
+      <c r="H40" s="2" t="s">
+        <v>250</v>
       </c>
       <c r="I40" s="2" t="s">
-        <v>249</v>
-      </c>
-      <c r="J40" s="2">
-        <v>5.0</v>
-      </c>
-      <c r="K40" s="2">
-        <v>4.0</v>
-      </c>
-      <c r="L40" s="2">
-        <v>5.0</v>
-      </c>
-      <c r="M40" s="2">
-        <v>5.0</v>
+        <v>35</v>
+      </c>
+      <c r="J40" s="2" t="s">
+        <v>251</v>
+      </c>
+      <c r="K40" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="L40" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="M40" s="2" t="s">
+        <v>46</v>
       </c>
       <c r="N40" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="O40" s="2">
-        <v>5.0</v>
+        <v>46</v>
+      </c>
+      <c r="O40" s="2" t="s">
+        <v>46</v>
       </c>
       <c r="P40" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="Q40" s="2">
-        <v>5.0</v>
+        <v>46</v>
+      </c>
+      <c r="Q40" s="2" t="s">
+        <v>46</v>
       </c>
       <c r="R40" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="S40" s="2"/>
-      <c r="T40" s="2" t="s">
-        <v>36</v>
-      </c>
+        <v>46</v>
+      </c>
+      <c r="S40" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="T40" s="2"/>
       <c r="U40" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="V40" s="2"/>
+        <v>47</v>
+      </c>
+      <c r="V40" s="2" t="s">
+        <v>38</v>
+      </c>
       <c r="W40" s="2"/>
       <c r="X40" s="2"/>
       <c r="Y40" s="3"/>
       <c r="Z40" s="3"/>
+      <c r="AA40" s="3"/>
     </row>
     <row r="41">
       <c r="A41" s="2" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="B41" s="2" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C41" s="2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D41" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E41" s="2" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="F41" s="2" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="G41" s="2" t="s">
-        <v>253</v>
+        <v>43</v>
       </c>
       <c r="H41" s="2" t="s">
-        <v>33</v>
+        <v>255</v>
       </c>
       <c r="I41" s="2" t="s">
-        <v>254</v>
+        <v>35</v>
       </c>
       <c r="J41" s="2" t="s">
-        <v>35</v>
+        <v>256</v>
       </c>
       <c r="K41" s="2" t="s">
-        <v>35</v>
+        <v>46</v>
       </c>
       <c r="L41" s="2" t="s">
-        <v>35</v>
+        <v>46</v>
       </c>
       <c r="M41" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="N41" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="O41" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="P41" s="2" t="s">
-        <v>35</v>
+        <v>46</v>
+      </c>
+      <c r="N41" s="2">
+        <v>5.0</v>
+      </c>
+      <c r="O41" s="2">
+        <v>5.0</v>
+      </c>
+      <c r="P41" s="2">
+        <v>5.0</v>
       </c>
       <c r="Q41" s="2" t="s">
-        <v>35</v>
+        <v>46</v>
       </c>
       <c r="R41" s="2" t="s">
-        <v>35</v>
+        <v>46</v>
       </c>
       <c r="S41" s="2" t="s">
-        <v>255</v>
+        <v>46</v>
       </c>
       <c r="T41" s="2" t="s">
-        <v>44</v>
+        <v>256</v>
       </c>
       <c r="U41" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="V41" s="2"/>
+        <v>47</v>
+      </c>
+      <c r="V41" s="2" t="s">
+        <v>38</v>
+      </c>
       <c r="W41" s="2"/>
       <c r="X41" s="2"/>
       <c r="Y41" s="3"/>
       <c r="Z41" s="3"/>
+      <c r="AA41" s="3"/>
     </row>
     <row r="42">
       <c r="A42" s="2" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>39</v>
+        <v>28</v>
       </c>
       <c r="C42" s="2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D42" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E42" s="2" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="F42" s="2" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="G42" s="2" t="s">
-        <v>259</v>
+        <v>33</v>
       </c>
       <c r="H42" s="2" t="s">
-        <v>33</v>
+        <v>260</v>
       </c>
       <c r="I42" s="2" t="s">
-        <v>260</v>
+        <v>35</v>
       </c>
       <c r="J42" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="K42" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="L42" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="M42" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="N42" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="O42" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="P42" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="Q42" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="R42" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="S42" s="2"/>
-      <c r="T42" s="2" t="s">
-        <v>44</v>
-      </c>
+        <v>261</v>
+      </c>
+      <c r="K42" s="2">
+        <v>5.0</v>
+      </c>
+      <c r="L42" s="2">
+        <v>5.0</v>
+      </c>
+      <c r="M42" s="2">
+        <v>5.0</v>
+      </c>
+      <c r="N42" s="2">
+        <v>4.0</v>
+      </c>
+      <c r="O42" s="2">
+        <v>4.0</v>
+      </c>
+      <c r="P42" s="2">
+        <v>5.0</v>
+      </c>
+      <c r="Q42" s="2">
+        <v>5.0</v>
+      </c>
+      <c r="R42" s="2">
+        <v>5.0</v>
+      </c>
+      <c r="S42" s="2">
+        <v>5.0</v>
+      </c>
+      <c r="T42" s="2"/>
       <c r="U42" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="V42" s="2"/>
+      <c r="V42" s="2" t="s">
+        <v>38</v>
+      </c>
       <c r="W42" s="2"/>
       <c r="X42" s="2"/>
       <c r="Y42" s="3"/>
       <c r="Z42" s="3"/>
+      <c r="AA42" s="3"/>
     </row>
     <row r="43">
       <c r="A43" s="2" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="B43" s="2" t="s">
-        <v>39</v>
+        <v>28</v>
       </c>
       <c r="C43" s="2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D43" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E43" s="2" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="F43" s="2" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="G43" s="2" t="s">
-        <v>264</v>
-      </c>
-      <c r="H43" s="2">
-        <v>5.0</v>
+        <v>33</v>
+      </c>
+      <c r="H43" s="2" t="s">
+        <v>265</v>
       </c>
       <c r="I43" s="2" t="s">
-        <v>265</v>
-      </c>
-      <c r="J43" s="2">
-        <v>3.0</v>
+        <v>35</v>
+      </c>
+      <c r="J43" s="2" t="s">
+        <v>266</v>
       </c>
       <c r="K43" s="2">
-        <v>4.0</v>
+        <v>5.0</v>
       </c>
       <c r="L43" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="M43" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="N43" s="2">
-        <v>5.0</v>
+        <v>46</v>
+      </c>
+      <c r="M43" s="2">
+        <v>5.0</v>
+      </c>
+      <c r="N43" s="2" t="s">
+        <v>46</v>
       </c>
       <c r="O43" s="2">
-        <v>3.0</v>
-      </c>
-      <c r="P43" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="Q43" s="2">
-        <v>2.0</v>
-      </c>
-      <c r="R43" s="2">
-        <v>2.0</v>
-      </c>
-      <c r="S43" s="2" t="s">
-        <v>266</v>
-      </c>
-      <c r="T43" s="2" t="s">
-        <v>44</v>
-      </c>
+        <v>5.0</v>
+      </c>
+      <c r="P43" s="2">
+        <v>5.0</v>
+      </c>
+      <c r="Q43" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="R43" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="S43" s="2">
+        <v>5.0</v>
+      </c>
+      <c r="T43" s="2"/>
       <c r="U43" s="2" t="s">
-        <v>100</v>
-      </c>
-      <c r="V43" s="2"/>
+        <v>37</v>
+      </c>
+      <c r="V43" s="2" t="s">
+        <v>38</v>
+      </c>
       <c r="W43" s="2"/>
       <c r="X43" s="2"/>
       <c r="Y43" s="3"/>
       <c r="Z43" s="3"/>
+      <c r="AA43" s="3"/>
     </row>
     <row r="44">
       <c r="A44" s="2" t="s">
         <v>267</v>
       </c>
       <c r="B44" s="2" t="s">
-        <v>39</v>
+        <v>28</v>
       </c>
       <c r="C44" s="2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D44" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E44" s="2" t="s">
         <v>268</v>
@@ -4362,68 +4825,71 @@
         <v>269</v>
       </c>
       <c r="G44" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="H44" s="2" t="s">
         <v>270</v>
       </c>
-      <c r="H44" s="2">
-        <v>8.0</v>
-      </c>
       <c r="I44" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="J44" s="2" t="s">
         <v>271</v>
       </c>
-      <c r="J44" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="K44" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="L44" s="2">
-        <v>5.0</v>
-      </c>
-      <c r="M44" s="2">
-        <v>5.0</v>
-      </c>
-      <c r="N44" s="2">
-        <v>4.0</v>
+      <c r="K44" s="2">
+        <v>5.0</v>
+      </c>
+      <c r="L44" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="M44" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="N44" s="2" t="s">
+        <v>46</v>
       </c>
       <c r="O44" s="2" t="s">
-        <v>35</v>
+        <v>46</v>
       </c>
       <c r="P44" s="2" t="s">
-        <v>35</v>
+        <v>46</v>
       </c>
       <c r="Q44" s="2" t="s">
-        <v>35</v>
+        <v>46</v>
       </c>
       <c r="R44" s="2" t="s">
-        <v>35</v>
+        <v>46</v>
       </c>
       <c r="S44" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="T44" s="2" t="s">
         <v>272</v>
       </c>
-      <c r="T44" s="2" t="s">
-        <v>44</v>
-      </c>
       <c r="U44" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="V44" s="2"/>
+        <v>37</v>
+      </c>
+      <c r="V44" s="2" t="s">
+        <v>38</v>
+      </c>
       <c r="W44" s="2"/>
       <c r="X44" s="2"/>
       <c r="Y44" s="3"/>
       <c r="Z44" s="3"/>
+      <c r="AA44" s="3"/>
     </row>
     <row r="45">
       <c r="A45" s="2" t="s">
         <v>273</v>
       </c>
       <c r="B45" s="2" t="s">
-        <v>39</v>
+        <v>28</v>
       </c>
       <c r="C45" s="2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D45" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E45" s="2" t="s">
         <v>274</v>
@@ -4432,68 +4898,71 @@
         <v>275</v>
       </c>
       <c r="G45" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="H45" s="2" t="s">
         <v>276</v>
       </c>
-      <c r="H45" s="2" t="s">
-        <v>33</v>
-      </c>
       <c r="I45" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="J45" s="2" t="s">
         <v>277</v>
       </c>
-      <c r="J45" s="2" t="s">
-        <v>35</v>
-      </c>
       <c r="K45" s="2" t="s">
-        <v>35</v>
+        <v>46</v>
       </c>
       <c r="L45" s="2" t="s">
-        <v>35</v>
+        <v>46</v>
       </c>
       <c r="M45" s="2" t="s">
-        <v>35</v>
+        <v>46</v>
       </c>
       <c r="N45" s="2" t="s">
-        <v>35</v>
+        <v>46</v>
       </c>
       <c r="O45" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="P45" s="2">
-        <v>4.0</v>
+        <v>46</v>
+      </c>
+      <c r="P45" s="2" t="s">
+        <v>46</v>
       </c>
       <c r="Q45" s="2" t="s">
-        <v>35</v>
+        <v>46</v>
       </c>
       <c r="R45" s="2" t="s">
-        <v>35</v>
+        <v>46</v>
       </c>
       <c r="S45" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="T45" s="2" t="s">
         <v>278</v>
-      </c>
-      <c r="T45" s="2" t="s">
-        <v>44</v>
       </c>
       <c r="U45" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="V45" s="2"/>
+      <c r="V45" s="2" t="s">
+        <v>38</v>
+      </c>
       <c r="W45" s="2"/>
       <c r="X45" s="2"/>
       <c r="Y45" s="3"/>
       <c r="Z45" s="3"/>
+      <c r="AA45" s="3"/>
     </row>
     <row r="46">
       <c r="A46" s="2" t="s">
         <v>279</v>
       </c>
       <c r="B46" s="2" t="s">
-        <v>39</v>
+        <v>28</v>
       </c>
       <c r="C46" s="2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D46" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E46" s="2" t="s">
         <v>280</v>
@@ -4502,66 +4971,69 @@
         <v>281</v>
       </c>
       <c r="G46" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="H46" s="2" t="s">
         <v>282</v>
       </c>
-      <c r="H46" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="I46" s="2" t="s">
+      <c r="I46" s="2">
+        <v>6.0</v>
+      </c>
+      <c r="J46" s="2" t="s">
         <v>283</v>
       </c>
-      <c r="J46" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="K46" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="L46" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="M46" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="N46" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="O46" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="P46" s="2" t="s">
-        <v>35</v>
+      <c r="K46" s="2">
+        <v>5.0</v>
+      </c>
+      <c r="L46" s="2">
+        <v>5.0</v>
+      </c>
+      <c r="M46" s="2">
+        <v>5.0</v>
+      </c>
+      <c r="N46" s="2">
+        <v>5.0</v>
+      </c>
+      <c r="O46" s="2">
+        <v>5.0</v>
+      </c>
+      <c r="P46" s="2">
+        <v>5.0</v>
       </c>
       <c r="Q46" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="R46" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="S46" s="2"/>
-      <c r="T46" s="2" t="s">
-        <v>44</v>
-      </c>
+        <v>46</v>
+      </c>
+      <c r="R46" s="2">
+        <v>5.0</v>
+      </c>
+      <c r="S46" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="T46" s="2"/>
       <c r="U46" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="V46" s="2"/>
+      <c r="V46" s="2" t="s">
+        <v>61</v>
+      </c>
       <c r="W46" s="2"/>
       <c r="X46" s="2"/>
       <c r="Y46" s="3"/>
       <c r="Z46" s="3"/>
+      <c r="AA46" s="3"/>
     </row>
     <row r="47">
       <c r="A47" s="2" t="s">
         <v>284</v>
       </c>
       <c r="B47" s="2" t="s">
-        <v>39</v>
+        <v>28</v>
       </c>
       <c r="C47" s="2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D47" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E47" s="2" t="s">
         <v>285</v>
@@ -4570,138 +5042,140 @@
         <v>286</v>
       </c>
       <c r="G47" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="H47" s="2" t="s">
         <v>287</v>
       </c>
-      <c r="H47" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="I47" s="2" t="s">
-        <v>260</v>
+      <c r="I47" s="2">
+        <v>9.0</v>
       </c>
       <c r="J47" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="K47" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="L47" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="M47" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="N47" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="O47" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="P47" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="Q47" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="R47" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="S47" s="2" t="s">
-        <v>260</v>
-      </c>
-      <c r="T47" s="2" t="s">
-        <v>44</v>
-      </c>
+        <v>288</v>
+      </c>
+      <c r="K47" s="2">
+        <v>5.0</v>
+      </c>
+      <c r="L47" s="2">
+        <v>5.0</v>
+      </c>
+      <c r="M47" s="2">
+        <v>5.0</v>
+      </c>
+      <c r="N47" s="2">
+        <v>5.0</v>
+      </c>
+      <c r="O47" s="2">
+        <v>5.0</v>
+      </c>
+      <c r="P47" s="2">
+        <v>5.0</v>
+      </c>
+      <c r="Q47" s="2">
+        <v>5.0</v>
+      </c>
+      <c r="R47" s="2">
+        <v>5.0</v>
+      </c>
+      <c r="S47" s="2">
+        <v>5.0</v>
+      </c>
+      <c r="T47" s="2"/>
       <c r="U47" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="V47" s="2"/>
+      <c r="V47" s="2" t="s">
+        <v>38</v>
+      </c>
       <c r="W47" s="2"/>
       <c r="X47" s="2"/>
       <c r="Y47" s="3"/>
       <c r="Z47" s="3"/>
+      <c r="AA47" s="3"/>
     </row>
     <row r="48">
       <c r="A48" s="2" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="B48" s="2" t="s">
-        <v>39</v>
+        <v>28</v>
       </c>
       <c r="C48" s="2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D48" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E48" s="2" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="F48" s="2" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="G48" s="2" t="s">
-        <v>291</v>
-      </c>
-      <c r="H48" s="2">
+        <v>33</v>
+      </c>
+      <c r="H48" s="2" t="s">
+        <v>292</v>
+      </c>
+      <c r="I48" s="2">
         <v>9.0</v>
       </c>
-      <c r="I48" s="2" t="s">
-        <v>292</v>
-      </c>
       <c r="J48" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="K48" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="L48" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="M48" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="N48" s="2" t="s">
-        <v>67</v>
+        <v>293</v>
+      </c>
+      <c r="K48" s="2">
+        <v>5.0</v>
+      </c>
+      <c r="L48" s="2">
+        <v>5.0</v>
+      </c>
+      <c r="M48" s="2">
+        <v>5.0</v>
+      </c>
+      <c r="N48" s="2">
+        <v>5.0</v>
       </c>
       <c r="O48" s="2" t="s">
-        <v>35</v>
+        <v>46</v>
       </c>
       <c r="P48" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="Q48" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="R48" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="S48" s="2" t="s">
-        <v>293</v>
-      </c>
-      <c r="T48" s="2" t="s">
-        <v>44</v>
-      </c>
+        <v>46</v>
+      </c>
+      <c r="Q48" s="2">
+        <v>5.0</v>
+      </c>
+      <c r="R48" s="2">
+        <v>5.0</v>
+      </c>
+      <c r="S48" s="2">
+        <v>5.0</v>
+      </c>
+      <c r="T48" s="2"/>
       <c r="U48" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="V48" s="2"/>
+      <c r="V48" s="2" t="s">
+        <v>38</v>
+      </c>
       <c r="W48" s="2"/>
       <c r="X48" s="2"/>
       <c r="Y48" s="3"/>
       <c r="Z48" s="3"/>
+      <c r="AA48" s="3"/>
     </row>
     <row r="49">
       <c r="A49" s="2" t="s">
         <v>294</v>
       </c>
       <c r="B49" s="2" t="s">
-        <v>39</v>
+        <v>28</v>
       </c>
       <c r="C49" s="2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D49" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E49" s="2" t="s">
         <v>295</v>
@@ -4710,608 +5184,2008 @@
         <v>296</v>
       </c>
       <c r="G49" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="H49" s="2" t="s">
         <v>297</v>
-      </c>
-      <c r="H49" s="2" t="s">
-        <v>33</v>
       </c>
       <c r="I49" s="2" t="s">
         <v>298</v>
       </c>
       <c r="J49" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="K49" s="2" t="s">
-        <v>35</v>
+        <v>299</v>
+      </c>
+      <c r="K49" s="2">
+        <v>4.0</v>
       </c>
       <c r="L49" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="M49" s="2" t="s">
-        <v>35</v>
+        <v>53</v>
+      </c>
+      <c r="M49" s="2">
+        <v>3.0</v>
       </c>
       <c r="N49" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="O49" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="P49" s="2">
-        <v>5.0</v>
+        <v>53</v>
+      </c>
+      <c r="O49" s="2">
+        <v>2.0</v>
+      </c>
+      <c r="P49" s="2" t="s">
+        <v>53</v>
       </c>
       <c r="Q49" s="2">
-        <v>5.0</v>
-      </c>
-      <c r="R49" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="S49" s="2" t="s">
-        <v>299</v>
+        <v>4.0</v>
+      </c>
+      <c r="R49" s="2">
+        <v>4.0</v>
+      </c>
+      <c r="S49" s="2">
+        <v>3.0</v>
       </c>
       <c r="T49" s="2" t="s">
-        <v>44</v>
+        <v>300</v>
       </c>
       <c r="U49" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="V49" s="2"/>
+      <c r="V49" s="2" t="s">
+        <v>61</v>
+      </c>
       <c r="W49" s="2"/>
       <c r="X49" s="2"/>
       <c r="Y49" s="3"/>
       <c r="Z49" s="3"/>
+      <c r="AA49" s="3"/>
     </row>
     <row r="50">
       <c r="A50" s="2" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="B50" s="2" t="s">
-        <v>39</v>
+        <v>28</v>
       </c>
       <c r="C50" s="2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D50" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E50" s="2" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="F50" s="2" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="G50" s="2" t="s">
-        <v>303</v>
+        <v>33</v>
       </c>
       <c r="H50" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="I50" s="2" t="s">
         <v>304</v>
       </c>
+      <c r="I50" s="2">
+        <v>9.0</v>
+      </c>
       <c r="J50" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="K50" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="L50" s="2" t="s">
-        <v>35</v>
+        <v>305</v>
+      </c>
+      <c r="K50" s="2">
+        <v>5.0</v>
+      </c>
+      <c r="L50" s="2">
+        <v>4.0</v>
       </c>
       <c r="M50" s="2">
         <v>5.0</v>
       </c>
-      <c r="N50" s="2" t="s">
-        <v>35</v>
+      <c r="N50" s="2">
+        <v>5.0</v>
       </c>
       <c r="O50" s="2">
-        <v>4.0</v>
-      </c>
-      <c r="P50" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="Q50" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="R50" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="S50" s="2"/>
-      <c r="T50" s="2" t="s">
-        <v>44</v>
-      </c>
+        <v>5.0</v>
+      </c>
+      <c r="P50" s="2">
+        <v>5.0</v>
+      </c>
+      <c r="Q50" s="2">
+        <v>5.0</v>
+      </c>
+      <c r="R50" s="2">
+        <v>5.0</v>
+      </c>
+      <c r="S50" s="2">
+        <v>5.0</v>
+      </c>
+      <c r="T50" s="2"/>
       <c r="U50" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="V50" s="2"/>
+      <c r="V50" s="2" t="s">
+        <v>38</v>
+      </c>
       <c r="W50" s="2"/>
       <c r="X50" s="2"/>
       <c r="Y50" s="3"/>
       <c r="Z50" s="3"/>
+      <c r="AA50" s="3"/>
     </row>
     <row r="51">
       <c r="A51" s="2" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="B51" s="2" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C51" s="2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D51" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E51" s="2" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="F51" s="2" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="G51" s="2" t="s">
-        <v>308</v>
-      </c>
-      <c r="H51" s="2">
-        <v>9.0</v>
+        <v>43</v>
+      </c>
+      <c r="H51" s="2" t="s">
+        <v>309</v>
       </c>
       <c r="I51" s="2" t="s">
-        <v>309</v>
+        <v>35</v>
       </c>
       <c r="J51" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="K51" s="2">
-        <v>5.0</v>
-      </c>
-      <c r="L51" s="2">
-        <v>5.0</v>
-      </c>
-      <c r="M51" s="2">
-        <v>5.0</v>
-      </c>
-      <c r="N51" s="2">
-        <v>5.0</v>
-      </c>
-      <c r="O51" s="2">
-        <v>5.0</v>
+        <v>310</v>
+      </c>
+      <c r="K51" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="L51" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="M51" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="N51" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="O51" s="2" t="s">
+        <v>46</v>
       </c>
       <c r="P51" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="Q51" s="2">
-        <v>5.0</v>
-      </c>
-      <c r="R51" s="2">
-        <v>5.0</v>
-      </c>
-      <c r="S51" s="2"/>
-      <c r="T51" s="2" t="s">
-        <v>44</v>
-      </c>
+        <v>46</v>
+      </c>
+      <c r="Q51" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="R51" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="S51" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="T51" s="2"/>
       <c r="U51" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="V51" s="2"/>
+        <v>47</v>
+      </c>
+      <c r="V51" s="2" t="s">
+        <v>38</v>
+      </c>
       <c r="W51" s="2"/>
       <c r="X51" s="2"/>
       <c r="Y51" s="3"/>
       <c r="Z51" s="3"/>
+      <c r="AA51" s="3"/>
     </row>
     <row r="52">
       <c r="A52" s="2" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="B52" s="2" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C52" s="2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D52" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E52" s="2" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="F52" s="2" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="G52" s="2" t="s">
-        <v>313</v>
-      </c>
-      <c r="H52" s="2">
-        <v>9.0</v>
-      </c>
-      <c r="I52" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="H52" s="2" t="s">
         <v>314</v>
       </c>
-      <c r="J52" s="2">
-        <v>5.0</v>
+      <c r="I52" s="2">
+        <v>8.0</v>
+      </c>
+      <c r="J52" s="2" t="s">
+        <v>315</v>
       </c>
       <c r="K52" s="2">
         <v>5.0</v>
       </c>
-      <c r="L52" s="2">
-        <v>5.0</v>
+      <c r="L52" s="2" t="s">
+        <v>46</v>
       </c>
       <c r="M52" s="2">
-        <v>4.0</v>
+        <v>5.0</v>
       </c>
       <c r="N52" s="2">
-        <v>5.0</v>
+        <v>3.0</v>
       </c>
       <c r="O52" s="2">
-        <v>5.0</v>
-      </c>
-      <c r="P52" s="2">
-        <v>5.0</v>
+        <v>4.0</v>
+      </c>
+      <c r="P52" s="2" t="s">
+        <v>46</v>
       </c>
       <c r="Q52" s="2">
-        <v>4.0</v>
-      </c>
-      <c r="R52" s="2">
-        <v>5.0</v>
+        <v>5.0</v>
+      </c>
+      <c r="R52" s="2" t="s">
+        <v>53</v>
       </c>
       <c r="S52" s="2" t="s">
-        <v>315</v>
+        <v>46</v>
       </c>
       <c r="T52" s="2" t="s">
-        <v>44</v>
+        <v>316</v>
       </c>
       <c r="U52" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="V52" s="2"/>
+        <v>47</v>
+      </c>
+      <c r="V52" s="2" t="s">
+        <v>55</v>
+      </c>
       <c r="W52" s="2"/>
       <c r="X52" s="2"/>
       <c r="Y52" s="3"/>
       <c r="Z52" s="3"/>
+      <c r="AA52" s="3"/>
     </row>
     <row r="53">
       <c r="A53" s="2" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="B53" s="2" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C53" s="2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D53" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E53" s="2" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="F53" s="2" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="G53" s="2" t="s">
-        <v>319</v>
+        <v>43</v>
       </c>
       <c r="H53" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="I53" s="2" t="s">
         <v>320</v>
       </c>
+      <c r="I53" s="2">
+        <v>5.0</v>
+      </c>
       <c r="J53" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="K53" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="L53" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="M53" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="N53" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="O53" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="P53" s="2" t="s">
-        <v>35</v>
+        <v>321</v>
+      </c>
+      <c r="K53" s="2">
+        <v>5.0</v>
+      </c>
+      <c r="L53" s="2">
+        <v>5.0</v>
+      </c>
+      <c r="M53" s="2">
+        <v>4.0</v>
+      </c>
+      <c r="N53" s="2">
+        <v>5.0</v>
+      </c>
+      <c r="O53" s="2">
+        <v>5.0</v>
+      </c>
+      <c r="P53" s="2">
+        <v>4.0</v>
       </c>
       <c r="Q53" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="R53" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="S53" s="2"/>
+        <v>46</v>
+      </c>
+      <c r="R53" s="2">
+        <v>3.0</v>
+      </c>
+      <c r="S53" s="2">
+        <v>5.0</v>
+      </c>
       <c r="T53" s="2" t="s">
-        <v>44</v>
+        <v>322</v>
       </c>
       <c r="U53" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="V53" s="2"/>
+        <v>47</v>
+      </c>
+      <c r="V53" s="2" t="s">
+        <v>61</v>
+      </c>
       <c r="W53" s="2"/>
       <c r="X53" s="2"/>
       <c r="Y53" s="3"/>
       <c r="Z53" s="3"/>
+      <c r="AA53" s="3"/>
     </row>
     <row r="54">
       <c r="A54" s="2" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="B54" s="2" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C54" s="2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D54" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E54" s="2" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="F54" s="2" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="G54" s="2" t="s">
-        <v>324</v>
+        <v>43</v>
       </c>
       <c r="H54" s="2" t="s">
-        <v>33</v>
+        <v>326</v>
       </c>
       <c r="I54" s="2" t="s">
-        <v>325</v>
+        <v>35</v>
       </c>
       <c r="J54" s="2" t="s">
-        <v>35</v>
+        <v>327</v>
       </c>
       <c r="K54" s="2" t="s">
-        <v>35</v>
+        <v>46</v>
       </c>
       <c r="L54" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="M54" s="2" t="s">
-        <v>35</v>
+        <v>46</v>
+      </c>
+      <c r="M54" s="2">
+        <v>4.0</v>
       </c>
       <c r="N54" s="2" t="s">
-        <v>35</v>
+        <v>46</v>
       </c>
       <c r="O54" s="2" t="s">
-        <v>35</v>
+        <v>46</v>
       </c>
       <c r="P54" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="Q54" s="2">
-        <v>5.0</v>
-      </c>
-      <c r="R54" s="2" t="s">
-        <v>35</v>
+        <v>46</v>
+      </c>
+      <c r="Q54" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="R54" s="2">
+        <v>4.0</v>
       </c>
       <c r="S54" s="2" t="s">
-        <v>326</v>
-      </c>
-      <c r="T54" s="2" t="s">
-        <v>44</v>
-      </c>
+        <v>46</v>
+      </c>
+      <c r="T54" s="2"/>
       <c r="U54" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="V54" s="2"/>
+        <v>47</v>
+      </c>
+      <c r="V54" s="2" t="s">
+        <v>38</v>
+      </c>
       <c r="W54" s="2"/>
       <c r="X54" s="2"/>
       <c r="Y54" s="3"/>
       <c r="Z54" s="3"/>
+      <c r="AA54" s="3"/>
     </row>
     <row r="55">
       <c r="A55" s="2" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="B55" s="2" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C55" s="2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D55" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E55" s="2" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="F55" s="2" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="G55" s="2" t="s">
-        <v>330</v>
-      </c>
-      <c r="H55" s="2">
-        <v>7.0</v>
+        <v>43</v>
+      </c>
+      <c r="H55" s="2" t="s">
+        <v>331</v>
       </c>
       <c r="I55" s="2" t="s">
-        <v>331</v>
+        <v>35</v>
       </c>
       <c r="J55" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="K55" s="2">
-        <v>5.0</v>
-      </c>
-      <c r="L55" s="2">
-        <v>4.0</v>
-      </c>
-      <c r="M55" s="2">
-        <v>3.0</v>
+        <v>332</v>
+      </c>
+      <c r="K55" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="L55" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="M55" s="2" t="s">
+        <v>46</v>
       </c>
       <c r="N55" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="O55" s="2">
-        <v>5.0</v>
-      </c>
-      <c r="P55" s="2">
-        <v>5.0</v>
-      </c>
-      <c r="Q55" s="2">
-        <v>5.0</v>
-      </c>
-      <c r="R55" s="2">
-        <v>5.0</v>
-      </c>
-      <c r="S55" s="2"/>
+        <v>46</v>
+      </c>
+      <c r="O55" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="P55" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="Q55" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="R55" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="S55" s="2" t="s">
+        <v>46</v>
+      </c>
       <c r="T55" s="2" t="s">
-        <v>44</v>
+        <v>333</v>
       </c>
       <c r="U55" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="V55" s="2"/>
+        <v>47</v>
+      </c>
+      <c r="V55" s="2" t="s">
+        <v>38</v>
+      </c>
       <c r="W55" s="2"/>
       <c r="X55" s="2"/>
       <c r="Y55" s="3"/>
       <c r="Z55" s="3"/>
+      <c r="AA55" s="3"/>
     </row>
     <row r="56">
       <c r="A56" s="2" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="B56" s="2" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C56" s="2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D56" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E56" s="2" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="F56" s="2" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="G56" s="2" t="s">
-        <v>335</v>
-      </c>
-      <c r="H56" s="2">
+        <v>43</v>
+      </c>
+      <c r="H56" s="2" t="s">
+        <v>337</v>
+      </c>
+      <c r="I56" s="2">
         <v>9.0</v>
       </c>
-      <c r="I56" s="2" t="s">
-        <v>336</v>
-      </c>
-      <c r="J56" s="2">
-        <v>5.0</v>
-      </c>
-      <c r="K56" s="2">
-        <v>5.0</v>
+      <c r="J56" s="2" t="s">
+        <v>338</v>
+      </c>
+      <c r="K56" s="2" t="s">
+        <v>46</v>
       </c>
       <c r="L56" s="2">
         <v>5.0</v>
       </c>
       <c r="M56" s="2">
-        <v>4.0</v>
-      </c>
-      <c r="N56" s="2">
-        <v>4.0</v>
-      </c>
-      <c r="O56" s="2">
-        <v>4.0</v>
-      </c>
-      <c r="P56" s="2">
-        <v>5.0</v>
+        <v>5.0</v>
+      </c>
+      <c r="N56" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="O56" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="P56" s="2" t="s">
+        <v>46</v>
       </c>
       <c r="Q56" s="2">
-        <v>4.0</v>
+        <v>5.0</v>
       </c>
       <c r="R56" s="2">
-        <v>4.0</v>
+        <v>5.0</v>
       </c>
       <c r="S56" s="2" t="s">
-        <v>337</v>
+        <v>46</v>
       </c>
       <c r="T56" s="2" t="s">
-        <v>44</v>
+        <v>339</v>
       </c>
       <c r="U56" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="V56" s="3"/>
+        <v>47</v>
+      </c>
+      <c r="V56" s="2" t="s">
+        <v>38</v>
+      </c>
       <c r="W56" s="3"/>
       <c r="X56" s="3"/>
       <c r="Y56" s="3"/>
       <c r="Z56" s="3"/>
+      <c r="AA56" s="3"/>
     </row>
     <row r="57">
       <c r="A57" s="2" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="B57" s="2" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C57" s="2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D57" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E57" s="2" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="F57" s="2" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="G57" s="2" t="s">
-        <v>341</v>
+        <v>43</v>
       </c>
       <c r="H57" s="2" t="s">
-        <v>33</v>
+        <v>343</v>
       </c>
       <c r="I57" s="2" t="s">
-        <v>342</v>
+        <v>35</v>
       </c>
       <c r="J57" s="2" t="s">
-        <v>35</v>
+        <v>344</v>
       </c>
       <c r="K57" s="2" t="s">
-        <v>35</v>
+        <v>46</v>
       </c>
       <c r="L57" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="M57" s="2">
-        <v>2.0</v>
-      </c>
-      <c r="N57" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="O57" s="2">
-        <v>3.0</v>
+        <v>46</v>
+      </c>
+      <c r="M57" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="N57" s="2">
+        <v>4.0</v>
+      </c>
+      <c r="O57" s="2" t="s">
+        <v>46</v>
       </c>
       <c r="P57" s="2" t="s">
-        <v>35</v>
+        <v>46</v>
       </c>
       <c r="Q57" s="2" t="s">
-        <v>35</v>
+        <v>46</v>
       </c>
       <c r="R57" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="S57" s="3"/>
+        <v>46</v>
+      </c>
+      <c r="S57" s="2" t="s">
+        <v>46</v>
+      </c>
       <c r="T57" s="2" t="s">
-        <v>44</v>
+        <v>345</v>
       </c>
       <c r="U57" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="V57" s="3"/>
+        <v>47</v>
+      </c>
+      <c r="V57" s="2" t="s">
+        <v>38</v>
+      </c>
       <c r="W57" s="3"/>
       <c r="X57" s="3"/>
       <c r="Y57" s="3"/>
       <c r="Z57" s="3"/>
+      <c r="AA57" s="3"/>
+    </row>
+    <row r="58">
+      <c r="A58" s="2" t="s">
+        <v>346</v>
+      </c>
+      <c r="B58" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="C58" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="D58" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="E58" s="2" t="s">
+        <v>347</v>
+      </c>
+      <c r="F58" s="2" t="s">
+        <v>348</v>
+      </c>
+      <c r="G58" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="H58" s="2" t="s">
+        <v>349</v>
+      </c>
+      <c r="I58" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="J58" s="2" t="s">
+        <v>350</v>
+      </c>
+      <c r="K58" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="L58" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="M58" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="N58" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="O58" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="P58" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="Q58" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="R58" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="S58" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="T58" s="2"/>
+      <c r="U58" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="V58" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="W58" s="3"/>
+      <c r="X58" s="3"/>
+      <c r="Y58" s="3"/>
+      <c r="Z58" s="3"/>
+      <c r="AA58" s="3"/>
+    </row>
+    <row r="59">
+      <c r="A59" s="2" t="s">
+        <v>351</v>
+      </c>
+      <c r="B59" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="C59" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="D59" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="E59" s="2" t="s">
+        <v>352</v>
+      </c>
+      <c r="F59" s="2" t="s">
+        <v>353</v>
+      </c>
+      <c r="G59" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="H59" s="2" t="s">
+        <v>354</v>
+      </c>
+      <c r="I59" s="2">
+        <v>8.0</v>
+      </c>
+      <c r="J59" s="2" t="s">
+        <v>355</v>
+      </c>
+      <c r="K59" s="2">
+        <v>5.0</v>
+      </c>
+      <c r="L59" s="2">
+        <v>4.0</v>
+      </c>
+      <c r="M59" s="2">
+        <v>5.0</v>
+      </c>
+      <c r="N59" s="2">
+        <v>5.0</v>
+      </c>
+      <c r="O59" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="P59" s="2">
+        <v>5.0</v>
+      </c>
+      <c r="Q59" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="R59" s="2">
+        <v>5.0</v>
+      </c>
+      <c r="S59" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="T59" s="2"/>
+      <c r="U59" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="V59" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="W59" s="3"/>
+      <c r="X59" s="3"/>
+      <c r="Y59" s="3"/>
+      <c r="Z59" s="3"/>
+      <c r="AA59" s="3"/>
+    </row>
+    <row r="60">
+      <c r="A60" s="2" t="s">
+        <v>356</v>
+      </c>
+      <c r="B60" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="C60" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="D60" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="E60" s="2" t="s">
+        <v>357</v>
+      </c>
+      <c r="F60" s="2" t="s">
+        <v>358</v>
+      </c>
+      <c r="G60" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="H60" s="2" t="s">
+        <v>359</v>
+      </c>
+      <c r="I60" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="J60" s="2" t="s">
+        <v>360</v>
+      </c>
+      <c r="K60" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="L60" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="M60" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="N60" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="O60" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="P60" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="Q60" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="R60" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="S60" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="T60" s="2" t="s">
+        <v>361</v>
+      </c>
+      <c r="U60" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="V60" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="W60" s="3"/>
+      <c r="X60" s="3"/>
+      <c r="Y60" s="3"/>
+      <c r="Z60" s="3"/>
+      <c r="AA60" s="3"/>
+    </row>
+    <row r="61">
+      <c r="A61" s="2" t="s">
+        <v>362</v>
+      </c>
+      <c r="B61" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="C61" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="D61" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="E61" s="2" t="s">
+        <v>363</v>
+      </c>
+      <c r="F61" s="2" t="s">
+        <v>364</v>
+      </c>
+      <c r="G61" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="H61" s="2" t="s">
+        <v>365</v>
+      </c>
+      <c r="I61" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="J61" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="K61" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="L61" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="M61" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="N61" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="O61" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="P61" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="Q61" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="R61" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="S61" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="T61" s="2"/>
+      <c r="U61" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="V61" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="W61" s="3"/>
+      <c r="X61" s="3"/>
+      <c r="Y61" s="3"/>
+      <c r="Z61" s="3"/>
+      <c r="AA61" s="3"/>
+    </row>
+    <row r="62">
+      <c r="A62" s="2" t="s">
+        <v>366</v>
+      </c>
+      <c r="B62" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="C62" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="D62" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="E62" s="2" t="s">
+        <v>367</v>
+      </c>
+      <c r="F62" s="2" t="s">
+        <v>368</v>
+      </c>
+      <c r="G62" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="H62" s="2" t="s">
+        <v>369</v>
+      </c>
+      <c r="I62" s="2">
+        <v>5.0</v>
+      </c>
+      <c r="J62" s="2" t="s">
+        <v>370</v>
+      </c>
+      <c r="K62" s="2">
+        <v>3.0</v>
+      </c>
+      <c r="L62" s="2">
+        <v>4.0</v>
+      </c>
+      <c r="M62" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="N62" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="O62" s="2">
+        <v>5.0</v>
+      </c>
+      <c r="P62" s="2">
+        <v>3.0</v>
+      </c>
+      <c r="Q62" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="R62" s="2">
+        <v>2.0</v>
+      </c>
+      <c r="S62" s="2">
+        <v>2.0</v>
+      </c>
+      <c r="T62" s="2" t="s">
+        <v>371</v>
+      </c>
+      <c r="U62" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="V62" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="W62" s="3"/>
+      <c r="X62" s="3"/>
+      <c r="Y62" s="3"/>
+      <c r="Z62" s="3"/>
+      <c r="AA62" s="3"/>
+    </row>
+    <row r="63">
+      <c r="A63" s="2" t="s">
+        <v>372</v>
+      </c>
+      <c r="B63" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="C63" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="D63" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="E63" s="2" t="s">
+        <v>373</v>
+      </c>
+      <c r="F63" s="2" t="s">
+        <v>374</v>
+      </c>
+      <c r="G63" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="H63" s="2" t="s">
+        <v>375</v>
+      </c>
+      <c r="I63" s="2">
+        <v>8.0</v>
+      </c>
+      <c r="J63" s="2" t="s">
+        <v>376</v>
+      </c>
+      <c r="K63" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="L63" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="M63" s="2">
+        <v>5.0</v>
+      </c>
+      <c r="N63" s="2">
+        <v>5.0</v>
+      </c>
+      <c r="O63" s="2">
+        <v>4.0</v>
+      </c>
+      <c r="P63" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="Q63" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="R63" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="S63" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="T63" s="2" t="s">
+        <v>377</v>
+      </c>
+      <c r="U63" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="V63" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="W63" s="3"/>
+      <c r="X63" s="3"/>
+      <c r="Y63" s="3"/>
+      <c r="Z63" s="3"/>
+      <c r="AA63" s="3"/>
+    </row>
+    <row r="64">
+      <c r="A64" s="2" t="s">
+        <v>378</v>
+      </c>
+      <c r="B64" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="C64" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="D64" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="E64" s="2" t="s">
+        <v>379</v>
+      </c>
+      <c r="F64" s="2" t="s">
+        <v>380</v>
+      </c>
+      <c r="G64" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="H64" s="2" t="s">
+        <v>381</v>
+      </c>
+      <c r="I64" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="J64" s="2" t="s">
+        <v>382</v>
+      </c>
+      <c r="K64" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="L64" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="M64" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="N64" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="O64" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="P64" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="Q64" s="2">
+        <v>4.0</v>
+      </c>
+      <c r="R64" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="S64" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="T64" s="2" t="s">
+        <v>383</v>
+      </c>
+      <c r="U64" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="V64" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="W64" s="3"/>
+      <c r="X64" s="3"/>
+      <c r="Y64" s="3"/>
+      <c r="Z64" s="3"/>
+      <c r="AA64" s="3"/>
+    </row>
+    <row r="65">
+      <c r="A65" s="2" t="s">
+        <v>384</v>
+      </c>
+      <c r="B65" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="C65" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="D65" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="E65" s="2" t="s">
+        <v>385</v>
+      </c>
+      <c r="F65" s="2" t="s">
+        <v>386</v>
+      </c>
+      <c r="G65" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="H65" s="2" t="s">
+        <v>387</v>
+      </c>
+      <c r="I65" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="J65" s="2" t="s">
+        <v>388</v>
+      </c>
+      <c r="K65" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="L65" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="M65" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="N65" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="O65" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="P65" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="Q65" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="R65" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="S65" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="T65" s="2"/>
+      <c r="U65" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="V65" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="W65" s="3"/>
+      <c r="X65" s="3"/>
+      <c r="Y65" s="3"/>
+      <c r="Z65" s="3"/>
+      <c r="AA65" s="3"/>
+    </row>
+    <row r="66">
+      <c r="A66" s="2" t="s">
+        <v>389</v>
+      </c>
+      <c r="B66" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="C66" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="D66" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="E66" s="2" t="s">
+        <v>390</v>
+      </c>
+      <c r="F66" s="2" t="s">
+        <v>391</v>
+      </c>
+      <c r="G66" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="H66" s="2" t="s">
+        <v>392</v>
+      </c>
+      <c r="I66" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="J66" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="K66" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="L66" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="M66" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="N66" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="O66" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="P66" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="Q66" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="R66" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="S66" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="T66" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="U66" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="V66" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="W66" s="3"/>
+      <c r="X66" s="3"/>
+      <c r="Y66" s="3"/>
+      <c r="Z66" s="3"/>
+      <c r="AA66" s="3"/>
+    </row>
+    <row r="67">
+      <c r="A67" s="2" t="s">
+        <v>393</v>
+      </c>
+      <c r="B67" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="C67" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="D67" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="E67" s="2" t="s">
+        <v>394</v>
+      </c>
+      <c r="F67" s="2" t="s">
+        <v>395</v>
+      </c>
+      <c r="G67" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="H67" s="2" t="s">
+        <v>396</v>
+      </c>
+      <c r="I67" s="2">
+        <v>9.0</v>
+      </c>
+      <c r="J67" s="2" t="s">
+        <v>397</v>
+      </c>
+      <c r="K67" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="L67" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="M67" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="N67" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="O67" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="P67" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="Q67" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="R67" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="S67" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="T67" s="2" t="s">
+        <v>398</v>
+      </c>
+      <c r="U67" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="V67" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="W67" s="3"/>
+      <c r="X67" s="3"/>
+      <c r="Y67" s="3"/>
+      <c r="Z67" s="3"/>
+      <c r="AA67" s="3"/>
+    </row>
+    <row r="68">
+      <c r="A68" s="2" t="s">
+        <v>399</v>
+      </c>
+      <c r="B68" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="C68" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="D68" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="E68" s="2" t="s">
+        <v>400</v>
+      </c>
+      <c r="F68" s="2" t="s">
+        <v>401</v>
+      </c>
+      <c r="G68" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="H68" s="2" t="s">
+        <v>402</v>
+      </c>
+      <c r="I68" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="J68" s="2" t="s">
+        <v>403</v>
+      </c>
+      <c r="K68" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="L68" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="M68" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="N68" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="O68" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="P68" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="Q68" s="2">
+        <v>5.0</v>
+      </c>
+      <c r="R68" s="2">
+        <v>5.0</v>
+      </c>
+      <c r="S68" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="T68" s="2" t="s">
+        <v>404</v>
+      </c>
+      <c r="U68" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="V68" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="W68" s="3"/>
+      <c r="X68" s="3"/>
+      <c r="Y68" s="3"/>
+      <c r="Z68" s="3"/>
+      <c r="AA68" s="3"/>
+    </row>
+    <row r="69">
+      <c r="A69" s="2" t="s">
+        <v>405</v>
+      </c>
+      <c r="B69" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="C69" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="D69" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="E69" s="2" t="s">
+        <v>406</v>
+      </c>
+      <c r="F69" s="2" t="s">
+        <v>407</v>
+      </c>
+      <c r="G69" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="H69" s="2" t="s">
+        <v>408</v>
+      </c>
+      <c r="I69" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="J69" s="2" t="s">
+        <v>409</v>
+      </c>
+      <c r="K69" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="L69" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="M69" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="N69" s="2">
+        <v>5.0</v>
+      </c>
+      <c r="O69" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="P69" s="2">
+        <v>4.0</v>
+      </c>
+      <c r="Q69" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="R69" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="S69" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="T69" s="3"/>
+      <c r="U69" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="V69" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="W69" s="3"/>
+      <c r="X69" s="3"/>
+      <c r="Y69" s="3"/>
+      <c r="Z69" s="3"/>
+      <c r="AA69" s="3"/>
+    </row>
+    <row r="70">
+      <c r="A70" s="2" t="s">
+        <v>410</v>
+      </c>
+      <c r="B70" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="C70" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="D70" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="E70" s="2" t="s">
+        <v>411</v>
+      </c>
+      <c r="F70" s="2" t="s">
+        <v>412</v>
+      </c>
+      <c r="G70" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="H70" s="2" t="s">
+        <v>413</v>
+      </c>
+      <c r="I70" s="2">
+        <v>9.0</v>
+      </c>
+      <c r="J70" s="2" t="s">
+        <v>414</v>
+      </c>
+      <c r="K70" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="L70" s="2">
+        <v>5.0</v>
+      </c>
+      <c r="M70" s="2">
+        <v>5.0</v>
+      </c>
+      <c r="N70" s="2">
+        <v>5.0</v>
+      </c>
+      <c r="O70" s="2">
+        <v>5.0</v>
+      </c>
+      <c r="P70" s="2">
+        <v>5.0</v>
+      </c>
+      <c r="Q70" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="R70" s="2">
+        <v>5.0</v>
+      </c>
+      <c r="S70" s="2">
+        <v>5.0</v>
+      </c>
+      <c r="T70" s="3"/>
+      <c r="U70" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="V70" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="W70" s="3"/>
+      <c r="X70" s="3"/>
+      <c r="Y70" s="3"/>
+      <c r="Z70" s="3"/>
+      <c r="AA70" s="3"/>
+    </row>
+    <row r="71">
+      <c r="A71" s="2" t="s">
+        <v>415</v>
+      </c>
+      <c r="B71" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="C71" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="D71" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="E71" s="2" t="s">
+        <v>416</v>
+      </c>
+      <c r="F71" s="2" t="s">
+        <v>417</v>
+      </c>
+      <c r="G71" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="H71" s="2" t="s">
+        <v>418</v>
+      </c>
+      <c r="I71" s="2">
+        <v>9.0</v>
+      </c>
+      <c r="J71" s="2" t="s">
+        <v>419</v>
+      </c>
+      <c r="K71" s="2">
+        <v>5.0</v>
+      </c>
+      <c r="L71" s="2">
+        <v>5.0</v>
+      </c>
+      <c r="M71" s="2">
+        <v>5.0</v>
+      </c>
+      <c r="N71" s="2">
+        <v>4.0</v>
+      </c>
+      <c r="O71" s="2">
+        <v>5.0</v>
+      </c>
+      <c r="P71" s="2">
+        <v>5.0</v>
+      </c>
+      <c r="Q71" s="2">
+        <v>5.0</v>
+      </c>
+      <c r="R71" s="2">
+        <v>4.0</v>
+      </c>
+      <c r="S71" s="2">
+        <v>5.0</v>
+      </c>
+      <c r="T71" s="2" t="s">
+        <v>420</v>
+      </c>
+      <c r="U71" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="V71" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="W71" s="3"/>
+      <c r="X71" s="3"/>
+      <c r="Y71" s="3"/>
+      <c r="Z71" s="3"/>
+      <c r="AA71" s="3"/>
+    </row>
+    <row r="72">
+      <c r="A72" s="2" t="s">
+        <v>421</v>
+      </c>
+      <c r="B72" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="C72" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="D72" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="E72" s="2" t="s">
+        <v>422</v>
+      </c>
+      <c r="F72" s="2" t="s">
+        <v>423</v>
+      </c>
+      <c r="G72" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="H72" s="2" t="s">
+        <v>424</v>
+      </c>
+      <c r="I72" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="J72" s="2" t="s">
+        <v>425</v>
+      </c>
+      <c r="K72" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="L72" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="M72" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="N72" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="O72" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="P72" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="Q72" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="R72" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="S72" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="T72" s="3"/>
+      <c r="U72" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="V72" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="W72" s="3"/>
+      <c r="X72" s="3"/>
+      <c r="Y72" s="3"/>
+      <c r="Z72" s="3"/>
+      <c r="AA72" s="3"/>
+    </row>
+    <row r="73">
+      <c r="A73" s="2" t="s">
+        <v>426</v>
+      </c>
+      <c r="B73" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="C73" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="D73" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="E73" s="2" t="s">
+        <v>427</v>
+      </c>
+      <c r="F73" s="2" t="s">
+        <v>428</v>
+      </c>
+      <c r="G73" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="H73" s="2" t="s">
+        <v>429</v>
+      </c>
+      <c r="I73" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="J73" s="2" t="s">
+        <v>430</v>
+      </c>
+      <c r="K73" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="L73" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="M73" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="N73" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="O73" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="P73" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="Q73" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="R73" s="2">
+        <v>5.0</v>
+      </c>
+      <c r="S73" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="T73" s="2" t="s">
+        <v>431</v>
+      </c>
+      <c r="U73" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="V73" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="W73" s="3"/>
+      <c r="X73" s="3"/>
+      <c r="Y73" s="3"/>
+      <c r="Z73" s="3"/>
+      <c r="AA73" s="3"/>
+    </row>
+    <row r="74">
+      <c r="A74" s="2" t="s">
+        <v>432</v>
+      </c>
+      <c r="B74" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="C74" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="D74" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="E74" s="2" t="s">
+        <v>433</v>
+      </c>
+      <c r="F74" s="2" t="s">
+        <v>434</v>
+      </c>
+      <c r="G74" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="H74" s="2" t="s">
+        <v>435</v>
+      </c>
+      <c r="I74" s="2">
+        <v>7.0</v>
+      </c>
+      <c r="J74" s="2" t="s">
+        <v>436</v>
+      </c>
+      <c r="K74" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="L74" s="2">
+        <v>5.0</v>
+      </c>
+      <c r="M74" s="2">
+        <v>4.0</v>
+      </c>
+      <c r="N74" s="2">
+        <v>3.0</v>
+      </c>
+      <c r="O74" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="P74" s="2">
+        <v>5.0</v>
+      </c>
+      <c r="Q74" s="2">
+        <v>5.0</v>
+      </c>
+      <c r="R74" s="2">
+        <v>5.0</v>
+      </c>
+      <c r="S74" s="2">
+        <v>5.0</v>
+      </c>
+      <c r="T74" s="3"/>
+      <c r="U74" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="V74" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="W74" s="3"/>
+      <c r="X74" s="3"/>
+      <c r="Y74" s="3"/>
+      <c r="Z74" s="3"/>
+      <c r="AA74" s="3"/>
+    </row>
+    <row r="75">
+      <c r="A75" s="2" t="s">
+        <v>437</v>
+      </c>
+      <c r="B75" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="C75" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="D75" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="E75" s="2" t="s">
+        <v>438</v>
+      </c>
+      <c r="F75" s="2" t="s">
+        <v>439</v>
+      </c>
+      <c r="G75" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="H75" s="2" t="s">
+        <v>440</v>
+      </c>
+      <c r="I75" s="2">
+        <v>9.0</v>
+      </c>
+      <c r="J75" s="2" t="s">
+        <v>441</v>
+      </c>
+      <c r="K75" s="2">
+        <v>5.0</v>
+      </c>
+      <c r="L75" s="2">
+        <v>5.0</v>
+      </c>
+      <c r="M75" s="2">
+        <v>5.0</v>
+      </c>
+      <c r="N75" s="2">
+        <v>4.0</v>
+      </c>
+      <c r="O75" s="2">
+        <v>4.0</v>
+      </c>
+      <c r="P75" s="2">
+        <v>4.0</v>
+      </c>
+      <c r="Q75" s="2">
+        <v>5.0</v>
+      </c>
+      <c r="R75" s="2">
+        <v>4.0</v>
+      </c>
+      <c r="S75" s="2">
+        <v>4.0</v>
+      </c>
+      <c r="T75" s="2" t="s">
+        <v>442</v>
+      </c>
+      <c r="U75" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="V75" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="W75" s="3"/>
+      <c r="X75" s="3"/>
+      <c r="Y75" s="3"/>
+      <c r="Z75" s="3"/>
+      <c r="AA75" s="3"/>
+    </row>
+    <row r="76">
+      <c r="A76" s="2" t="s">
+        <v>443</v>
+      </c>
+      <c r="B76" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="C76" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="D76" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="E76" s="2" t="s">
+        <v>444</v>
+      </c>
+      <c r="F76" s="2" t="s">
+        <v>445</v>
+      </c>
+      <c r="G76" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="H76" s="2" t="s">
+        <v>446</v>
+      </c>
+      <c r="I76" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="J76" s="2" t="s">
+        <v>447</v>
+      </c>
+      <c r="K76" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="L76" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="M76" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="N76" s="2">
+        <v>2.0</v>
+      </c>
+      <c r="O76" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="P76" s="2">
+        <v>3.0</v>
+      </c>
+      <c r="Q76" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="R76" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="S76" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="T76" s="3"/>
+      <c r="U76" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="V76" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="W76" s="3"/>
+      <c r="X76" s="3"/>
+      <c r="Y76" s="3"/>
+      <c r="Z76" s="3"/>
+      <c r="AA76" s="3"/>
     </row>
   </sheetData>
-  <autoFilter ref="$A$1:$Z$57"/>
+  <autoFilter ref="$A$1:$Z$76"/>
   <drawing r:id="rId1"/>
 </worksheet>
 </file>
--- a/NPS - matriz-saojoaodemeriti.xlsx
+++ b/NPS - matriz-saojoaodemeriti.xlsx
@@ -6,14 +6,14 @@
     <sheet state="visible" name="CSAT 1" sheetId="1" r:id="rId5"/>
   </sheets>
   <definedNames>
-    <definedName hidden="1" localSheetId="0" name="_xlnm._FilterDatabase">'CSAT 1'!$A$1:$Z$76</definedName>
+    <definedName hidden="1" localSheetId="0" name="_xlnm._FilterDatabase">'CSAT 1'!$A$1:$Z$88</definedName>
   </definedNames>
   <calcPr/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1296" uniqueCount="448">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1408" uniqueCount="513">
   <si>
     <t>userId</t>
   </si>
@@ -75,9 +75,6 @@
     <t>Estamos interessados ​​em ouvir suas ideias! Por favor, compartilhe suas sugestões ou comentários</t>
   </si>
   <si>
-    <t>Tipo Respondente</t>
-  </si>
-  <si>
     <t>Perfil</t>
   </si>
   <si>
@@ -93,72 +90,286 @@
     <t>AÇÃO</t>
   </si>
   <si>
-    <t>Última atualização: 25/03/2026 18:30</t>
+    <t>Última atualização: 30/03/2026 14:47</t>
+  </si>
+  <si>
+    <t>Última atualização: 26/03/2026 14:31</t>
+  </si>
+  <si>
+    <t>65a99b981c199e72150b3c65</t>
+  </si>
+  <si>
+    <t>69b86abb3648364cda618a5d</t>
+  </si>
+  <si>
+    <t>Queremos ouvir a sua opinião</t>
+  </si>
+  <si>
+    <t>matriz-saojoaodemeriti</t>
+  </si>
+  <si>
+    <t>MELISSA ARGOLLO DOS SANTOS</t>
+  </si>
+  <si>
+    <t>melissaargollo02@gmail.com</t>
+  </si>
+  <si>
+    <t>responsavel</t>
+  </si>
+  <si>
+    <t>2026-03-29T13:06:42.979Z</t>
+  </si>
+  <si>
+    <t>Como é primeiro ano do meu filho, ainda estou me ambientando com a escola. Mas tenho uma ótima devolutiva da coordenadora Laís, o que conforta meu coração. Ela é muito solicita.</t>
+  </si>
+  <si>
+    <t>6 - Muito Satisfeito</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Até o presente momento estou gostando e me adaptando. Sempre que preciso de qualquer suporte a Laís me auxiliar, o que faz toda a diferença. </t>
+  </si>
+  <si>
+    <t>Promotor</t>
+  </si>
+  <si>
+    <t>6036854abf1dfcdda0fc7a06</t>
+  </si>
+  <si>
+    <t>CAROLINE DOS SANTOS FERNANDES DE AMORIM</t>
+  </si>
+  <si>
+    <t>prof.carolinefernandes@gmail.com</t>
+  </si>
+  <si>
+    <t>2026-03-29T10:12:11.849Z</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Estou satisfeito com a escola </t>
+  </si>
+  <si>
+    <t>O valor da cantina poderia ser mais acessível.</t>
+  </si>
+  <si>
+    <t>65a99b981c199e453a0b3d45</t>
+  </si>
+  <si>
+    <t>RENATO SILVEIRA CAVALCANTE JUNIOR</t>
+  </si>
+  <si>
+    <t>renatoscjunior@hotmail.com</t>
+  </si>
+  <si>
+    <t>2026-03-27T14:15:37.062Z</t>
+  </si>
+  <si>
+    <t>10 - Extremamente provável</t>
+  </si>
+  <si>
+    <t>Eu gosto da funcionalidade da escola.</t>
+  </si>
+  <si>
+    <t>6785ab547656e741ae2c7715</t>
+  </si>
+  <si>
+    <t>CRISTIANO GOMES CARVALHO</t>
+  </si>
+  <si>
+    <t>cristianogomescarvalho1973@gmail.com</t>
+  </si>
+  <si>
+    <t>2026-03-27T02:48:41.507Z</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Confiança </t>
+  </si>
+  <si>
+    <t>69813c644410ffe581f6601c</t>
+  </si>
+  <si>
+    <t>VIVIANE MARCIA DEODATO FERREIRA</t>
+  </si>
+  <si>
+    <t>vivianedeodatoseso@gmail.com</t>
+  </si>
+  <si>
+    <t>2026-03-27T00:38:30.812Z</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Estou gostando muito. </t>
+  </si>
+  <si>
+    <t>6983df16880d49447982938e</t>
+  </si>
+  <si>
+    <t>NATHALIA DA CRUZ SANTOS DE MELLO</t>
+  </si>
+  <si>
+    <t>nathyld1@gmail.com</t>
+  </si>
+  <si>
+    <t>2026-03-27T00:36:33.29Z</t>
+  </si>
+  <si>
+    <t>Algumas questões estão me.deixando 
+Insatisfeita. Principalmente comunicação escola/família.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Melhoria no contato escola /família .
+</t>
+  </si>
+  <si>
+    <t>Detrator</t>
+  </si>
+  <si>
+    <t>698e6b717cca2eb611314a62</t>
+  </si>
+  <si>
+    <t>69b898ede32111b0684fb44a</t>
+  </si>
+  <si>
+    <t>ALICIA GUIMARÃES RODRIGUES</t>
+  </si>
+  <si>
+    <t>aliciamt26202341@matrizeducacao.com.br</t>
+  </si>
+  <si>
+    <t>estudante</t>
+  </si>
+  <si>
+    <t>2026-03-26T17:54:26.787Z</t>
+  </si>
+  <si>
+    <t xml:space="preserve">O colégio é bom 
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">As cadeiras podiam ser um pouco mais confortáveis, e o brownie da cantina podia voltar </t>
+  </si>
+  <si>
+    <t>Neutro</t>
+  </si>
+  <si>
+    <t>65a99b981c199eec7f0b3c1e</t>
+  </si>
+  <si>
+    <t>MARCOS PEREIRA DOS SANTOS</t>
+  </si>
+  <si>
+    <t>msantos.musico@gmail.com</t>
+  </si>
+  <si>
+    <t>2026-03-26T17:36:32.058Z</t>
+  </si>
+  <si>
+    <t>Colegio entrega o que promete.</t>
+  </si>
+  <si>
+    <t>698bc861c9656e1678cfab76</t>
+  </si>
+  <si>
+    <t>CRISTIANE DE FIGUEIREDO FERREIRA FERNANDES</t>
+  </si>
+  <si>
+    <t>cris.fffernandes@gmail.com</t>
+  </si>
+  <si>
+    <t>2026-03-26T01:01:23.954Z</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ainda temos pouco tempo na escola para ter uma avaliação mais ampla </t>
+  </si>
+  <si>
+    <t>Ainda temos pouco tempo na escola para ter uma avaliação mais ampla .</t>
+  </si>
+  <si>
+    <t>64121f46f16a6c00178234b2</t>
+  </si>
+  <si>
+    <t>MÔNICA DA SILVA DINIZ VATIMO</t>
+  </si>
+  <si>
+    <t>monicavatimo@gmail.com</t>
+  </si>
+  <si>
+    <t>2026-03-25T22:58:12.663Z</t>
+  </si>
+  <si>
+    <t>Gosto do ensino forte e do pedagógico..</t>
+  </si>
+  <si>
+    <t>60368546bf1dfc5670fc7991</t>
+  </si>
+  <si>
+    <t>DIONE DA SILVA MOREIRA FRANÇA</t>
+  </si>
+  <si>
+    <t>dionesidnei@outlook.com</t>
+  </si>
+  <si>
+    <t>2026-03-25T21:50:01.97Z</t>
+  </si>
+  <si>
+    <t xml:space="preserve">O administrativo do colégio é estressante,  sistema falho não melhora desde a migração do FLUMINENSE para o Matriz . Isaac é falho ,desorganizado,  cobranças indevidas etc. Isso não é de agora , se não melhorar certamente perderá muitos alunos. 
+</t>
+  </si>
+  <si>
+    <t>1 - Muito Insatisfeito</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Vou deixar aqui a minha insatisfação ; atendimento presencial é bom secretaria ,recepção muito boa , porem o financeiro é péssimo. Melhorem o sistema, facilitem a comunicação quanto a plataforma do tal Isaac que é péssimo, não sei se melhorou mas algumas salas de aula o sistema de refrigeração não estava 100% . Setor pedagógico,  metodologia gosto bastante mas a questão de entrega de livros vocês precisam melhorar isso urgente, é inadmissível um material didático que custa um rim demorar tanto pra ser entregue.  A instituição está pecando nos pequenos detalhes que fazem a diferença. 
+Não adianta ter um ensino muito bom e deixar a desejar na parte admistrativa como entrega de livros, dificultar a realização de um pagamento no tal app , dificultar a comunicação com o pessoal de financeiro, etc. Isaac já deu é péssimo. O FLUMINENSE dava aulas e sim a maioria ficou porque migrou do FLUMINENSE que era impecável em tudo , não deixava a desejar em nada . O que não é o caso do Matriz . Inclusive a gestão da Daniele foi maravilhoso posso dizer que a melhor até aqui . O ensino é muito bom , mas o burocrático e parte do administrativo não é bom . Espero que possam rever algumas coisas porque meus filhos amam o ambiente escolar do Matriz .
+Forte abraço 
+</t>
+  </si>
+  <si>
+    <t>66c9f60d13488196c2204b2f</t>
+  </si>
+  <si>
+    <t>Vânia Moura Barbosa</t>
+  </si>
+  <si>
+    <t>vaniapsirj@gmail.com</t>
+  </si>
+  <si>
+    <t>2026-03-25T21:49:08.909Z</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Por conta de toda proposta educacional e desenvolvimento apresentada. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gostaria de parabenizar as propostas de ensino e aprendizagem apresentadas até o presente momento, porém sugiro a possibilidade de retorno da educação sócioemocional, visto que é no ambiente escolar que se faz necessário ainda trabalhar questões relacionadas a autonomia e respeito aos colegas e professores. No mais, somente tenho elogios a dar </t>
   </si>
   <si>
     <t>677bc2d45316892336c5d39e</t>
   </si>
   <si>
-    <t>69b86abb3648364cda618a5d</t>
-  </si>
-  <si>
-    <t>Queremos ouvir a sua opinião</t>
-  </si>
-  <si>
-    <t>matriz-saojoaodemeriti</t>
-  </si>
-  <si>
     <t>CRISTIANE NOVAES CANDIDO SCHUENCK</t>
   </si>
   <si>
     <t>crisliviaschuenck@gmail.com</t>
   </si>
   <si>
-    <t>responsavel</t>
-  </si>
-  <si>
     <t>2026-03-25T21:15:42.108Z</t>
   </si>
   <si>
-    <t>10 - Extremamente provável</t>
-  </si>
-  <si>
     <t xml:space="preserve">Minha filha entrou em 2025 e até o momento não tenho nenhuma reclamação </t>
   </si>
   <si>
-    <t>Responsável</t>
-  </si>
-  <si>
-    <t>Promotor</t>
-  </si>
-  <si>
     <t>65aa9e22611c74921eb70328</t>
   </si>
   <si>
-    <t>69b898ede32111b0684fb44a</t>
-  </si>
-  <si>
     <t>MIGUEL BORGES DE CARVALHO</t>
   </si>
   <si>
     <t>miguelmt23119951@matrizeducacao.com.br</t>
   </si>
   <si>
-    <t>estudante</t>
-  </si>
-  <si>
     <t>2026-03-25T20:54:49.392Z</t>
   </si>
   <si>
     <t>Acho o ensino muito bom</t>
   </si>
   <si>
-    <t>6 - Muito Satisfeito</t>
-  </si>
-  <si>
-    <t>Aluno</t>
-  </si>
-  <si>
     <t>65aa9e26611c7404bdb70f1e</t>
   </si>
   <si>
@@ -174,15 +385,9 @@
     <t>a escola é boa, mas ainda tem pontos ruins</t>
   </si>
   <si>
-    <t>1 - Muito Insatisfeito</t>
-  </si>
-  <si>
     <t xml:space="preserve">a cantina está horrorosa! decaiu muito, as coisas estão caras, com poucas qualidades, lanches pequenos, sem recheio, má higienização, produtos de baixa qualidade para preços altos. o Guaravita totalmente de baixa qualidade, 5 reais em nuggsts pra vim nuggsts minúsculos e pouquíssimos. a mesma coisa com a batata. outro dia tinha uma mosca nos salgados. sem variedade nenhuma, e vários alunos reclamando </t>
   </si>
   <si>
-    <t>Neutro</t>
-  </si>
-  <si>
     <t>60368552bff8bc73b402749b</t>
   </si>
   <si>
@@ -196,9 +401,6 @@
   </si>
   <si>
     <t xml:space="preserve">5 pois o colégio é realmente bom mas deixa a desejar no quesito de material didático, principalmente os online q deveria ser para todos os alunos </t>
-  </si>
-  <si>
-    <t>Detrator</t>
   </si>
   <si>
     <t>66ba24bc26275a3f0664c348</t>
@@ -1694,13 +1896,13 @@
     <col customWidth="1" min="17" max="17" width="52.75"/>
     <col customWidth="1" min="18" max="18" width="71.88"/>
     <col customWidth="1" min="19" max="19" width="64.5"/>
-    <col customWidth="1" min="20" max="20" width="302.75"/>
-    <col customWidth="1" min="21" max="21" width="16.75"/>
-    <col customWidth="1" min="22" max="22" width="7.75"/>
-    <col customWidth="1" min="23" max="23" width="15.25"/>
-    <col customWidth="1" min="24" max="24" width="26.63"/>
-    <col customWidth="1" min="25" max="25" width="18.88"/>
-    <col customWidth="1" min="26" max="26" width="7.75"/>
+    <col customWidth="1" min="20" max="20" width="484.88"/>
+    <col customWidth="1" min="21" max="21" width="7.75"/>
+    <col customWidth="1" min="22" max="22" width="15.25"/>
+    <col customWidth="1" min="23" max="23" width="26.63"/>
+    <col customWidth="1" min="24" max="24" width="18.88"/>
+    <col customWidth="1" min="25" max="25" width="7.75"/>
+    <col customWidth="1" min="26" max="26" width="31.13"/>
     <col customWidth="1" min="27" max="27" width="28.63"/>
   </cols>
   <sheetData>
@@ -1812,46 +2014,46 @@
       <c r="H2" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="I2" s="2" t="s">
+      <c r="I2" s="2">
+        <v>9.0</v>
+      </c>
+      <c r="J2" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="J2" s="2" t="s">
-        <v>36</v>
-      </c>
       <c r="K2" s="2">
         <v>5.0</v>
       </c>
-      <c r="L2" s="2">
-        <v>5.0</v>
+      <c r="L2" s="2" t="s">
+        <v>36</v>
       </c>
       <c r="M2" s="2">
         <v>5.0</v>
       </c>
       <c r="N2" s="2">
-        <v>5.0</v>
+        <v>3.0</v>
       </c>
       <c r="O2" s="2">
         <v>4.0</v>
       </c>
       <c r="P2" s="2">
-        <v>5.0</v>
+        <v>4.0</v>
       </c>
       <c r="Q2" s="2">
         <v>5.0</v>
       </c>
       <c r="R2" s="2">
-        <v>4.0</v>
-      </c>
-      <c r="S2" s="2">
-        <v>5.0</v>
-      </c>
-      <c r="T2" s="2"/>
+        <v>3.0</v>
+      </c>
+      <c r="S2" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="T2" s="2" t="s">
+        <v>37</v>
+      </c>
       <c r="U2" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="V2" s="2" t="s">
         <v>38</v>
       </c>
+      <c r="V2" s="2"/>
       <c r="W2" s="2"/>
       <c r="X2" s="2"/>
       <c r="Y2" s="2"/>
@@ -1863,66 +2065,66 @@
         <v>39</v>
       </c>
       <c r="B3" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="E3" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="C3" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="D3" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="E3" s="2" t="s">
+      <c r="F3" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="F3" s="2" t="s">
+      <c r="G3" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="H3" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="G3" s="2" t="s">
+      <c r="I3" s="2">
+        <v>9.0</v>
+      </c>
+      <c r="J3" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="H3" s="2" t="s">
+      <c r="K3" s="2">
+        <v>5.0</v>
+      </c>
+      <c r="L3" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="M3" s="2">
+        <v>5.0</v>
+      </c>
+      <c r="N3" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="O3" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="P3" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="Q3" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="R3" s="4">
+        <v>4.0</v>
+      </c>
+      <c r="S3" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="T3" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="I3" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="J3" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="K3" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="L3" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="M3" s="2">
-        <v>5.0</v>
-      </c>
-      <c r="N3" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="O3" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="P3" s="2">
-        <v>5.0</v>
-      </c>
-      <c r="Q3" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="R3" s="4" t="s">
-        <v>46</v>
-      </c>
-      <c r="S3" s="2">
-        <v>4.0</v>
-      </c>
-      <c r="T3" s="2"/>
       <c r="U3" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="V3" s="2" t="s">
         <v>38</v>
       </c>
+      <c r="V3" s="2"/>
       <c r="W3" s="2"/>
       <c r="X3" s="2"/>
       <c r="Y3" s="3"/>
@@ -1931,71 +2133,67 @@
     </row>
     <row r="4">
       <c r="A4" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="F4" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="G4" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="H4" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="B4" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="E4" s="2" t="s">
+      <c r="I4" s="2" t="s">
         <v>49</v>
       </c>
-      <c r="F4" s="2" t="s">
+      <c r="J4" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="G4" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="H4" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="I4" s="2">
-        <v>7.0</v>
-      </c>
-      <c r="J4" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="K4" s="2">
-        <v>3.0</v>
+      <c r="K4" s="2" t="s">
+        <v>36</v>
       </c>
       <c r="L4" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="M4" s="2">
-        <v>4.0</v>
-      </c>
-      <c r="N4" s="2">
-        <v>4.0</v>
-      </c>
-      <c r="O4" s="2">
-        <v>5.0</v>
-      </c>
-      <c r="P4" s="2">
-        <v>3.0</v>
+        <v>36</v>
+      </c>
+      <c r="M4" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="N4" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="O4" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="P4" s="2" t="s">
+        <v>36</v>
       </c>
       <c r="Q4" s="2" t="s">
-        <v>46</v>
+        <v>36</v>
       </c>
       <c r="R4" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="S4" s="2">
-        <v>4.0</v>
-      </c>
-      <c r="T4" s="2" t="s">
-        <v>54</v>
-      </c>
+        <v>36</v>
+      </c>
+      <c r="S4" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="T4" s="2"/>
       <c r="U4" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="V4" s="2" t="s">
-        <v>55</v>
-      </c>
+        <v>38</v>
+      </c>
+      <c r="V4" s="2"/>
       <c r="W4" s="2"/>
       <c r="X4" s="2"/>
       <c r="Y4" s="3"/>
@@ -2004,10 +2202,10 @@
     </row>
     <row r="5">
       <c r="A5" s="2" t="s">
-        <v>56</v>
+        <v>51</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>40</v>
+        <v>28</v>
       </c>
       <c r="C5" s="2" t="s">
         <v>29</v>
@@ -2016,57 +2214,55 @@
         <v>30</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>57</v>
+        <v>52</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>58</v>
+        <v>53</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>43</v>
+        <v>33</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>59</v>
-      </c>
-      <c r="I5" s="2">
-        <v>5.0</v>
+        <v>54</v>
+      </c>
+      <c r="I5" s="2" t="s">
+        <v>49</v>
       </c>
       <c r="J5" s="2" t="s">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="K5" s="2">
-        <v>4.0</v>
+        <v>5.0</v>
       </c>
       <c r="L5" s="2">
-        <v>2.0</v>
-      </c>
-      <c r="M5" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="N5" s="2">
-        <v>4.0</v>
-      </c>
-      <c r="O5" s="2" t="s">
-        <v>46</v>
+        <v>5.0</v>
+      </c>
+      <c r="M5" s="2">
+        <v>5.0</v>
+      </c>
+      <c r="N5" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="O5" s="2">
+        <v>5.0</v>
       </c>
       <c r="P5" s="2">
-        <v>3.0</v>
+        <v>5.0</v>
       </c>
       <c r="Q5" s="2">
-        <v>3.0</v>
+        <v>5.0</v>
       </c>
       <c r="R5" s="2">
-        <v>2.0</v>
-      </c>
-      <c r="S5" s="2" t="s">
-        <v>46</v>
+        <v>5.0</v>
+      </c>
+      <c r="S5" s="2">
+        <v>5.0</v>
       </c>
       <c r="T5" s="2"/>
       <c r="U5" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="V5" s="2" t="s">
-        <v>61</v>
-      </c>
+        <v>38</v>
+      </c>
+      <c r="V5" s="2"/>
       <c r="W5" s="2"/>
       <c r="X5" s="2"/>
       <c r="Y5" s="3"/>
@@ -2075,7 +2271,7 @@
     </row>
     <row r="6">
       <c r="A6" s="2" t="s">
-        <v>62</v>
+        <v>56</v>
       </c>
       <c r="B6" s="2" t="s">
         <v>28</v>
@@ -2087,34 +2283,34 @@
         <v>30</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>63</v>
+        <v>57</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>64</v>
+        <v>58</v>
       </c>
       <c r="G6" s="2" t="s">
         <v>33</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="I6" s="2">
-        <v>9.0</v>
+        <v>59</v>
+      </c>
+      <c r="I6" s="2" t="s">
+        <v>49</v>
       </c>
       <c r="J6" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="K6" s="2">
-        <v>5.0</v>
-      </c>
-      <c r="L6" s="2">
-        <v>5.0</v>
+        <v>60</v>
+      </c>
+      <c r="K6" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="L6" s="2" t="s">
+        <v>36</v>
       </c>
       <c r="M6" s="2">
-        <v>5.0</v>
-      </c>
-      <c r="N6" s="2">
-        <v>5.0</v>
+        <v>4.0</v>
+      </c>
+      <c r="N6" s="2" t="s">
+        <v>36</v>
       </c>
       <c r="O6" s="2">
         <v>5.0</v>
@@ -2122,8 +2318,8 @@
       <c r="P6" s="2">
         <v>5.0</v>
       </c>
-      <c r="Q6" s="2">
-        <v>5.0</v>
+      <c r="Q6" s="2" t="s">
+        <v>36</v>
       </c>
       <c r="R6" s="2">
         <v>5.0</v>
@@ -2133,11 +2329,9 @@
       </c>
       <c r="T6" s="2"/>
       <c r="U6" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="V6" s="2" t="s">
         <v>38</v>
       </c>
+      <c r="V6" s="2"/>
       <c r="W6" s="2"/>
       <c r="X6" s="2"/>
       <c r="Y6" s="3"/>
@@ -2146,7 +2340,7 @@
     </row>
     <row r="7">
       <c r="A7" s="2" t="s">
-        <v>67</v>
+        <v>61</v>
       </c>
       <c r="B7" s="2" t="s">
         <v>28</v>
@@ -2158,57 +2352,57 @@
         <v>30</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>68</v>
+        <v>62</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>69</v>
+        <v>63</v>
       </c>
       <c r="G7" s="2" t="s">
         <v>33</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>70</v>
+        <v>64</v>
       </c>
       <c r="I7" s="2">
-        <v>9.0</v>
+        <v>6.0</v>
       </c>
       <c r="J7" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="K7" s="2" t="s">
-        <v>46</v>
+        <v>65</v>
+      </c>
+      <c r="K7" s="2">
+        <v>5.0</v>
       </c>
       <c r="L7" s="2">
         <v>5.0</v>
       </c>
       <c r="M7" s="2">
-        <v>5.0</v>
+        <v>3.0</v>
       </c>
       <c r="N7" s="2" t="s">
-        <v>46</v>
+        <v>36</v>
       </c>
       <c r="O7" s="2">
-        <v>5.0</v>
-      </c>
-      <c r="P7" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="Q7" s="2">
-        <v>5.0</v>
+        <v>2.0</v>
+      </c>
+      <c r="P7" s="2">
+        <v>4.0</v>
+      </c>
+      <c r="Q7" s="2" t="s">
+        <v>36</v>
       </c>
       <c r="R7" s="2">
-        <v>4.0</v>
-      </c>
-      <c r="S7" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="T7" s="2"/>
+        <v>5.0</v>
+      </c>
+      <c r="S7" s="2">
+        <v>5.0</v>
+      </c>
+      <c r="T7" s="2" t="s">
+        <v>66</v>
+      </c>
       <c r="U7" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="V7" s="2" t="s">
-        <v>38</v>
-      </c>
+        <v>67</v>
+      </c>
+      <c r="V7" s="2"/>
       <c r="W7" s="2"/>
       <c r="X7" s="2"/>
       <c r="Y7" s="3"/>
@@ -2217,69 +2411,69 @@
     </row>
     <row r="8">
       <c r="A8" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="E8" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="F8" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="G8" s="2" t="s">
         <v>72</v>
       </c>
-      <c r="B8" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="C8" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="D8" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="E8" s="2" t="s">
+      <c r="H8" s="2" t="s">
         <v>73</v>
       </c>
-      <c r="F8" s="2" t="s">
+      <c r="I8" s="2">
+        <v>8.0</v>
+      </c>
+      <c r="J8" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="G8" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="H8" s="2" t="s">
+      <c r="K8" s="2">
+        <v>5.0</v>
+      </c>
+      <c r="L8" s="2">
+        <v>2.0</v>
+      </c>
+      <c r="M8" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="N8" s="2">
+        <v>5.0</v>
+      </c>
+      <c r="O8" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="P8" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="Q8" s="2">
+        <v>5.0</v>
+      </c>
+      <c r="R8" s="2">
+        <v>5.0</v>
+      </c>
+      <c r="S8" s="2">
+        <v>5.0</v>
+      </c>
+      <c r="T8" s="2" t="s">
         <v>75</v>
       </c>
-      <c r="I8" s="2">
-        <v>9.0</v>
-      </c>
-      <c r="J8" s="2" t="s">
+      <c r="U8" s="2" t="s">
         <v>76</v>
       </c>
-      <c r="K8" s="2">
-        <v>5.0</v>
-      </c>
-      <c r="L8" s="2">
-        <v>4.0</v>
-      </c>
-      <c r="M8" s="2">
-        <v>5.0</v>
-      </c>
-      <c r="N8" s="2">
-        <v>4.0</v>
-      </c>
-      <c r="O8" s="2">
-        <v>5.0</v>
-      </c>
-      <c r="P8" s="2">
-        <v>5.0</v>
-      </c>
-      <c r="Q8" s="2">
-        <v>5.0</v>
-      </c>
-      <c r="R8" s="2">
-        <v>5.0</v>
-      </c>
-      <c r="S8" s="2">
-        <v>5.0</v>
-      </c>
-      <c r="T8" s="2"/>
-      <c r="U8" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="V8" s="2" t="s">
-        <v>38</v>
-      </c>
+      <c r="V8" s="2"/>
       <c r="W8" s="2"/>
       <c r="X8" s="2"/>
       <c r="Y8" s="3"/>
@@ -2312,47 +2506,43 @@
         <v>80</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>35</v>
+        <v>49</v>
       </c>
       <c r="J9" s="2" t="s">
         <v>81</v>
       </c>
-      <c r="K9" s="2">
-        <v>5.0</v>
+      <c r="K9" s="2" t="s">
+        <v>36</v>
       </c>
       <c r="L9" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="M9" s="2">
-        <v>5.0</v>
+        <v>36</v>
+      </c>
+      <c r="M9" s="2" t="s">
+        <v>36</v>
       </c>
       <c r="N9" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="O9" s="2">
-        <v>5.0</v>
-      </c>
-      <c r="P9" s="2">
-        <v>5.0</v>
+        <v>36</v>
+      </c>
+      <c r="O9" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="P9" s="2" t="s">
+        <v>36</v>
       </c>
       <c r="Q9" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="R9" s="2">
-        <v>4.0</v>
-      </c>
-      <c r="S9" s="2">
-        <v>5.0</v>
-      </c>
-      <c r="T9" s="2" t="s">
-        <v>82</v>
-      </c>
+        <v>36</v>
+      </c>
+      <c r="R9" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="S9" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="T9" s="2"/>
       <c r="U9" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="V9" s="2" t="s">
         <v>38</v>
       </c>
+      <c r="V9" s="2"/>
       <c r="W9" s="2"/>
       <c r="X9" s="2"/>
       <c r="Y9" s="3"/>
@@ -2361,7 +2551,7 @@
     </row>
     <row r="10">
       <c r="A10" s="2" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B10" s="2" t="s">
         <v>28</v>
@@ -2373,57 +2563,57 @@
         <v>30</v>
       </c>
       <c r="E10" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="F10" s="2" t="s">
         <v>84</v>
-      </c>
-      <c r="F10" s="2" t="s">
-        <v>85</v>
       </c>
       <c r="G10" s="2" t="s">
         <v>33</v>
       </c>
       <c r="H10" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="I10" s="2">
+        <v>5.0</v>
+      </c>
+      <c r="J10" s="2" t="s">
         <v>86</v>
       </c>
-      <c r="I10" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="J10" s="2" t="s">
+      <c r="K10" s="2">
+        <v>4.0</v>
+      </c>
+      <c r="L10" s="2">
+        <v>4.0</v>
+      </c>
+      <c r="M10" s="2">
+        <v>4.0</v>
+      </c>
+      <c r="N10" s="2">
+        <v>4.0</v>
+      </c>
+      <c r="O10" s="2">
+        <v>4.0</v>
+      </c>
+      <c r="P10" s="2">
+        <v>4.0</v>
+      </c>
+      <c r="Q10" s="2">
+        <v>4.0</v>
+      </c>
+      <c r="R10" s="2">
+        <v>4.0</v>
+      </c>
+      <c r="S10" s="2">
+        <v>4.0</v>
+      </c>
+      <c r="T10" s="2" t="s">
         <v>87</v>
       </c>
-      <c r="K10" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="L10" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="M10" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="N10" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="O10" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="P10" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="Q10" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="R10" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="S10" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="T10" s="2"/>
       <c r="U10" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="V10" s="2" t="s">
-        <v>38</v>
-      </c>
+        <v>67</v>
+      </c>
+      <c r="V10" s="2"/>
       <c r="W10" s="2"/>
       <c r="X10" s="2"/>
       <c r="Y10" s="3"/>
@@ -2455,48 +2645,44 @@
       <c r="H11" s="2" t="s">
         <v>91</v>
       </c>
-      <c r="I11" s="2">
-        <v>8.0</v>
+      <c r="I11" s="2" t="s">
+        <v>49</v>
       </c>
       <c r="J11" s="2" t="s">
         <v>92</v>
       </c>
-      <c r="K11" s="2">
-        <v>5.0</v>
-      </c>
-      <c r="L11" s="2">
-        <v>5.0</v>
-      </c>
-      <c r="M11" s="2">
-        <v>5.0</v>
-      </c>
-      <c r="N11" s="2">
-        <v>4.0</v>
-      </c>
-      <c r="O11" s="2">
+      <c r="K11" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="L11" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="M11" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="N11" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="O11" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="P11" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="Q11" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="R11" s="2">
         <v>3.0</v>
       </c>
-      <c r="P11" s="2">
-        <v>5.0</v>
-      </c>
-      <c r="Q11" s="2">
-        <v>5.0</v>
-      </c>
-      <c r="R11" s="2">
-        <v>5.0</v>
-      </c>
       <c r="S11" s="2">
         <v>5.0</v>
       </c>
-      <c r="T11" s="2" t="s">
-        <v>93</v>
-      </c>
+      <c r="T11" s="2"/>
       <c r="U11" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="V11" s="2" t="s">
-        <v>55</v>
-      </c>
+        <v>38</v>
+      </c>
+      <c r="V11" s="2"/>
       <c r="W11" s="2"/>
       <c r="X11" s="2"/>
       <c r="Y11" s="3"/>
@@ -2505,7 +2691,7 @@
     </row>
     <row r="12">
       <c r="A12" s="2" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="B12" s="2" t="s">
         <v>28</v>
@@ -2517,46 +2703,46 @@
         <v>30</v>
       </c>
       <c r="E12" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="F12" s="2" t="s">
         <v>95</v>
-      </c>
-      <c r="F12" s="2" t="s">
-        <v>96</v>
       </c>
       <c r="G12" s="2" t="s">
         <v>33</v>
       </c>
       <c r="H12" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="I12" s="2">
+        <v>5.0</v>
+      </c>
+      <c r="J12" s="2" t="s">
         <v>97</v>
       </c>
-      <c r="I12" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="J12" s="2" t="s">
+      <c r="K12" s="2">
+        <v>5.0</v>
+      </c>
+      <c r="L12" s="2">
+        <v>5.0</v>
+      </c>
+      <c r="M12" s="2">
+        <v>3.0</v>
+      </c>
+      <c r="N12" s="2" t="s">
         <v>98</v>
       </c>
-      <c r="K12" s="2">
-        <v>4.0</v>
-      </c>
-      <c r="L12" s="2">
-        <v>5.0</v>
-      </c>
-      <c r="M12" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="N12" s="2" t="s">
-        <v>46</v>
-      </c>
       <c r="O12" s="2" t="s">
-        <v>46</v>
+        <v>98</v>
       </c>
       <c r="P12" s="2">
         <v>4.0</v>
       </c>
-      <c r="Q12" s="2" t="s">
-        <v>53</v>
+      <c r="Q12" s="2">
+        <v>5.0</v>
       </c>
       <c r="R12" s="2">
-        <v>2.0</v>
+        <v>4.0</v>
       </c>
       <c r="S12" s="2">
         <v>5.0</v>
@@ -2565,11 +2751,9 @@
         <v>99</v>
       </c>
       <c r="U12" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="V12" s="2" t="s">
-        <v>38</v>
-      </c>
+        <v>67</v>
+      </c>
+      <c r="V12" s="2"/>
       <c r="W12" s="2"/>
       <c r="X12" s="2"/>
       <c r="Y12" s="3"/>
@@ -2601,48 +2785,46 @@
       <c r="H13" s="2" t="s">
         <v>103</v>
       </c>
-      <c r="I13" s="2">
-        <v>8.0</v>
+      <c r="I13" s="2" t="s">
+        <v>49</v>
       </c>
       <c r="J13" s="2" t="s">
         <v>104</v>
       </c>
-      <c r="K13" s="2">
-        <v>5.0</v>
-      </c>
-      <c r="L13" s="2">
-        <v>5.0</v>
-      </c>
-      <c r="M13" s="2">
-        <v>4.0</v>
-      </c>
-      <c r="N13" s="2">
-        <v>5.0</v>
-      </c>
-      <c r="O13" s="2">
-        <v>5.0</v>
-      </c>
-      <c r="P13" s="2">
-        <v>5.0</v>
+      <c r="K13" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="L13" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="M13" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="N13" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="O13" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="P13" s="2" t="s">
+        <v>36</v>
       </c>
       <c r="Q13" s="2" t="s">
-        <v>53</v>
+        <v>36</v>
       </c>
       <c r="R13" s="2" t="s">
-        <v>53</v>
+        <v>36</v>
       </c>
       <c r="S13" s="2" t="s">
-        <v>53</v>
+        <v>36</v>
       </c>
       <c r="T13" s="2" t="s">
         <v>105</v>
       </c>
       <c r="U13" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="V13" s="2" t="s">
-        <v>55</v>
-      </c>
+        <v>38</v>
+      </c>
+      <c r="V13" s="2"/>
       <c r="W13" s="2"/>
       <c r="X13" s="2"/>
       <c r="Y13" s="3"/>
@@ -2675,47 +2857,43 @@
         <v>109</v>
       </c>
       <c r="I14" s="2" t="s">
-        <v>35</v>
+        <v>49</v>
       </c>
       <c r="J14" s="2" t="s">
         <v>110</v>
       </c>
-      <c r="K14" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="L14" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="M14" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="N14" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="O14" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="P14" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="Q14" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="R14" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="S14" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="T14" s="2" t="s">
-        <v>111</v>
-      </c>
+      <c r="K14" s="2">
+        <v>5.0</v>
+      </c>
+      <c r="L14" s="2">
+        <v>5.0</v>
+      </c>
+      <c r="M14" s="2">
+        <v>5.0</v>
+      </c>
+      <c r="N14" s="2">
+        <v>5.0</v>
+      </c>
+      <c r="O14" s="2">
+        <v>4.0</v>
+      </c>
+      <c r="P14" s="2">
+        <v>5.0</v>
+      </c>
+      <c r="Q14" s="2">
+        <v>5.0</v>
+      </c>
+      <c r="R14" s="2">
+        <v>4.0</v>
+      </c>
+      <c r="S14" s="2">
+        <v>5.0</v>
+      </c>
+      <c r="T14" s="2"/>
       <c r="U14" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="V14" s="2" t="s">
         <v>38</v>
       </c>
+      <c r="V14" s="2"/>
       <c r="W14" s="2"/>
       <c r="X14" s="2"/>
       <c r="Y14" s="3"/>
@@ -2724,69 +2902,67 @@
     </row>
     <row r="15">
       <c r="A15" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="D15" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="E15" s="2" t="s">
         <v>112</v>
       </c>
-      <c r="B15" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="C15" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="D15" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="E15" s="2" t="s">
+      <c r="F15" s="2" t="s">
         <v>113</v>
       </c>
-      <c r="F15" s="2" t="s">
+      <c r="G15" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="H15" s="2" t="s">
         <v>114</v>
       </c>
-      <c r="G15" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="H15" s="2" t="s">
+      <c r="I15" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="J15" s="2" t="s">
         <v>115</v>
       </c>
-      <c r="I15" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="J15" s="2" t="s">
-        <v>116</v>
-      </c>
       <c r="K15" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="L15" s="2">
-        <v>5.0</v>
-      </c>
-      <c r="M15" s="2" t="s">
-        <v>46</v>
+        <v>36</v>
+      </c>
+      <c r="L15" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="M15" s="2">
+        <v>5.0</v>
       </c>
       <c r="N15" s="2" t="s">
-        <v>46</v>
+        <v>36</v>
       </c>
       <c r="O15" s="2" t="s">
-        <v>46</v>
+        <v>36</v>
       </c>
       <c r="P15" s="2">
         <v>5.0</v>
       </c>
-      <c r="Q15" s="2">
-        <v>5.0</v>
-      </c>
-      <c r="R15" s="2">
-        <v>5.0</v>
+      <c r="Q15" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="R15" s="2" t="s">
+        <v>36</v>
       </c>
       <c r="S15" s="2">
-        <v>5.0</v>
+        <v>4.0</v>
       </c>
       <c r="T15" s="2"/>
       <c r="U15" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="V15" s="2" t="s">
         <v>38</v>
       </c>
+      <c r="V15" s="2"/>
       <c r="W15" s="2"/>
       <c r="X15" s="2"/>
       <c r="Y15" s="3"/>
@@ -2795,71 +2971,69 @@
     </row>
     <row r="16">
       <c r="A16" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="B16" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="C16" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="D16" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="E16" s="2" t="s">
         <v>117</v>
       </c>
-      <c r="B16" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="C16" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="D16" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="E16" s="2" t="s">
+      <c r="F16" s="2" t="s">
         <v>118</v>
       </c>
-      <c r="F16" s="2" t="s">
+      <c r="G16" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="H16" s="2" t="s">
         <v>119</v>
       </c>
-      <c r="G16" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="H16" s="2" t="s">
+      <c r="I16" s="2">
+        <v>7.0</v>
+      </c>
+      <c r="J16" s="2" t="s">
         <v>120</v>
       </c>
-      <c r="I16" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="J16" s="2" t="s">
+      <c r="K16" s="2">
+        <v>3.0</v>
+      </c>
+      <c r="L16" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="M16" s="2">
+        <v>4.0</v>
+      </c>
+      <c r="N16" s="2">
+        <v>4.0</v>
+      </c>
+      <c r="O16" s="2">
+        <v>5.0</v>
+      </c>
+      <c r="P16" s="2">
+        <v>3.0</v>
+      </c>
+      <c r="Q16" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="R16" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="S16" s="2">
+        <v>4.0</v>
+      </c>
+      <c r="T16" s="2" t="s">
         <v>121</v>
       </c>
-      <c r="K16" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="L16" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="M16" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="N16" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="O16" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="P16" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="Q16" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="R16" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="S16" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="T16" s="2" t="s">
-        <v>122</v>
-      </c>
       <c r="U16" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="V16" s="2" t="s">
-        <v>38</v>
-      </c>
+        <v>76</v>
+      </c>
+      <c r="V16" s="2"/>
       <c r="W16" s="2"/>
       <c r="X16" s="2"/>
       <c r="Y16" s="3"/>
@@ -2868,69 +3042,67 @@
     </row>
     <row r="17">
       <c r="A17" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="B17" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="C17" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="D17" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="E17" s="2" t="s">
         <v>123</v>
       </c>
-      <c r="B17" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="C17" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="D17" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="E17" s="2" t="s">
+      <c r="F17" s="2" t="s">
         <v>124</v>
       </c>
-      <c r="F17" s="2" t="s">
+      <c r="G17" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="H17" s="2" t="s">
         <v>125</v>
       </c>
-      <c r="G17" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="H17" s="2" t="s">
+      <c r="I17" s="2">
+        <v>5.0</v>
+      </c>
+      <c r="J17" s="2" t="s">
         <v>126</v>
       </c>
-      <c r="I17" s="2">
-        <v>6.0</v>
-      </c>
-      <c r="J17" s="2" t="s">
-        <v>127</v>
-      </c>
       <c r="K17" s="2">
-        <v>5.0</v>
-      </c>
-      <c r="L17" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="M17" s="2">
-        <v>3.0</v>
-      </c>
-      <c r="N17" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="O17" s="2">
-        <v>4.0</v>
+        <v>4.0</v>
+      </c>
+      <c r="L17" s="2">
+        <v>2.0</v>
+      </c>
+      <c r="M17" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="N17" s="2">
+        <v>4.0</v>
+      </c>
+      <c r="O17" s="2" t="s">
+        <v>36</v>
       </c>
       <c r="P17" s="2">
         <v>3.0</v>
       </c>
-      <c r="Q17" s="2" t="s">
-        <v>53</v>
+      <c r="Q17" s="2">
+        <v>3.0</v>
       </c>
       <c r="R17" s="2">
-        <v>4.0</v>
-      </c>
-      <c r="S17" s="2">
-        <v>4.0</v>
+        <v>2.0</v>
+      </c>
+      <c r="S17" s="2" t="s">
+        <v>36</v>
       </c>
       <c r="T17" s="2"/>
       <c r="U17" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="V17" s="2" t="s">
-        <v>61</v>
-      </c>
+        <v>67</v>
+      </c>
+      <c r="V17" s="2"/>
       <c r="W17" s="2"/>
       <c r="X17" s="2"/>
       <c r="Y17" s="3"/>
@@ -2939,71 +3111,67 @@
     </row>
     <row r="18">
       <c r="A18" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="B18" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="C18" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="D18" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="E18" s="2" t="s">
         <v>128</v>
       </c>
-      <c r="B18" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="C18" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="D18" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="E18" s="2" t="s">
+      <c r="F18" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="F18" s="2" t="s">
+      <c r="G18" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="H18" s="2" t="s">
         <v>130</v>
       </c>
-      <c r="G18" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="H18" s="2" t="s">
+      <c r="I18" s="2">
+        <v>9.0</v>
+      </c>
+      <c r="J18" s="2" t="s">
         <v>131</v>
       </c>
-      <c r="I18" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="J18" s="2" t="s">
-        <v>132</v>
-      </c>
-      <c r="K18" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="L18" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="M18" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="N18" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="O18" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="P18" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="Q18" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="R18" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="S18" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="T18" s="2" t="s">
-        <v>132</v>
-      </c>
+      <c r="K18" s="2">
+        <v>5.0</v>
+      </c>
+      <c r="L18" s="2">
+        <v>5.0</v>
+      </c>
+      <c r="M18" s="2">
+        <v>5.0</v>
+      </c>
+      <c r="N18" s="2">
+        <v>5.0</v>
+      </c>
+      <c r="O18" s="2">
+        <v>5.0</v>
+      </c>
+      <c r="P18" s="2">
+        <v>5.0</v>
+      </c>
+      <c r="Q18" s="2">
+        <v>5.0</v>
+      </c>
+      <c r="R18" s="2">
+        <v>5.0</v>
+      </c>
+      <c r="S18" s="2">
+        <v>5.0</v>
+      </c>
+      <c r="T18" s="2"/>
       <c r="U18" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="V18" s="2" t="s">
         <v>38</v>
       </c>
+      <c r="V18" s="2"/>
       <c r="W18" s="2"/>
       <c r="X18" s="2"/>
       <c r="Y18" s="3"/>
@@ -3012,7 +3180,7 @@
     </row>
     <row r="19">
       <c r="A19" s="2" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="B19" s="2" t="s">
         <v>28</v>
@@ -3024,59 +3192,55 @@
         <v>30</v>
       </c>
       <c r="E19" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="F19" s="2" t="s">
         <v>134</v>
-      </c>
-      <c r="F19" s="2" t="s">
-        <v>135</v>
       </c>
       <c r="G19" s="2" t="s">
         <v>33</v>
       </c>
       <c r="H19" s="2" t="s">
+        <v>135</v>
+      </c>
+      <c r="I19" s="2">
+        <v>9.0</v>
+      </c>
+      <c r="J19" s="2" t="s">
         <v>136</v>
       </c>
-      <c r="I19" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="J19" s="2" t="s">
-        <v>137</v>
-      </c>
       <c r="K19" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="L19" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="M19" s="2" t="s">
-        <v>46</v>
+        <v>36</v>
+      </c>
+      <c r="L19" s="2">
+        <v>5.0</v>
+      </c>
+      <c r="M19" s="2">
+        <v>5.0</v>
       </c>
       <c r="N19" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="O19" s="2" t="s">
-        <v>46</v>
+        <v>36</v>
+      </c>
+      <c r="O19" s="2">
+        <v>5.0</v>
       </c>
       <c r="P19" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="Q19" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="R19" s="2" t="s">
-        <v>46</v>
+        <v>36</v>
+      </c>
+      <c r="Q19" s="2">
+        <v>5.0</v>
+      </c>
+      <c r="R19" s="2">
+        <v>4.0</v>
       </c>
       <c r="S19" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="T19" s="2" t="s">
-        <v>138</v>
-      </c>
+        <v>36</v>
+      </c>
+      <c r="T19" s="2"/>
       <c r="U19" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="V19" s="2" t="s">
         <v>38</v>
       </c>
+      <c r="V19" s="2"/>
       <c r="W19" s="2"/>
       <c r="X19" s="2"/>
       <c r="Y19" s="3"/>
@@ -3085,7 +3249,7 @@
     </row>
     <row r="20">
       <c r="A20" s="2" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="B20" s="2" t="s">
         <v>28</v>
@@ -3097,57 +3261,55 @@
         <v>30</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="G20" s="2" t="s">
         <v>33</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="I20" s="2">
-        <v>8.0</v>
+        <v>9.0</v>
       </c>
       <c r="J20" s="2" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="K20" s="2">
         <v>5.0</v>
       </c>
       <c r="L20" s="2">
-        <v>5.0</v>
+        <v>4.0</v>
       </c>
       <c r="M20" s="2">
         <v>5.0</v>
       </c>
       <c r="N20" s="2">
-        <v>5.0</v>
+        <v>4.0</v>
       </c>
       <c r="O20" s="2">
         <v>5.0</v>
       </c>
       <c r="P20" s="2">
-        <v>4.0</v>
+        <v>5.0</v>
       </c>
       <c r="Q20" s="2">
         <v>5.0</v>
       </c>
       <c r="R20" s="2">
-        <v>3.0</v>
+        <v>5.0</v>
       </c>
       <c r="S20" s="2">
-        <v>4.0</v>
+        <v>5.0</v>
       </c>
       <c r="T20" s="2"/>
       <c r="U20" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="V20" s="2" t="s">
-        <v>55</v>
-      </c>
+        <v>38</v>
+      </c>
+      <c r="V20" s="2"/>
       <c r="W20" s="2"/>
       <c r="X20" s="2"/>
       <c r="Y20" s="3"/>
@@ -3156,69 +3318,69 @@
     </row>
     <row r="21">
       <c r="A21" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="B21" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="C21" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="D21" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="E21" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="F21" s="2" t="s">
         <v>144</v>
       </c>
-      <c r="B21" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="C21" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="D21" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="E21" s="2" t="s">
+      <c r="G21" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="H21" s="2" t="s">
         <v>145</v>
       </c>
-      <c r="F21" s="2" t="s">
+      <c r="I21" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="J21" s="2" t="s">
         <v>146</v>
       </c>
-      <c r="G21" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="H21" s="2" t="s">
+      <c r="K21" s="2">
+        <v>5.0</v>
+      </c>
+      <c r="L21" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="M21" s="2">
+        <v>5.0</v>
+      </c>
+      <c r="N21" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="O21" s="2">
+        <v>5.0</v>
+      </c>
+      <c r="P21" s="2">
+        <v>5.0</v>
+      </c>
+      <c r="Q21" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="R21" s="2">
+        <v>4.0</v>
+      </c>
+      <c r="S21" s="2">
+        <v>5.0</v>
+      </c>
+      <c r="T21" s="2" t="s">
         <v>147</v>
       </c>
-      <c r="I21" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="J21" s="2" t="s">
-        <v>148</v>
-      </c>
-      <c r="K21" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="L21" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="M21" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="N21" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="O21" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="P21" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="Q21" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="R21" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="S21" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="T21" s="2"/>
       <c r="U21" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="V21" s="2" t="s">
         <v>38</v>
       </c>
+      <c r="V21" s="2"/>
       <c r="W21" s="2"/>
       <c r="X21" s="2"/>
       <c r="Y21" s="3"/>
@@ -3227,7 +3389,7 @@
     </row>
     <row r="22">
       <c r="A22" s="2" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="B22" s="2" t="s">
         <v>28</v>
@@ -3239,57 +3401,55 @@
         <v>30</v>
       </c>
       <c r="E22" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="F22" s="2" t="s">
         <v>150</v>
-      </c>
-      <c r="F22" s="2" t="s">
-        <v>151</v>
       </c>
       <c r="G22" s="2" t="s">
         <v>33</v>
       </c>
       <c r="H22" s="2" t="s">
+        <v>151</v>
+      </c>
+      <c r="I22" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="J22" s="2" t="s">
         <v>152</v>
       </c>
-      <c r="I22" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="J22" s="2" t="s">
-        <v>153</v>
-      </c>
       <c r="K22" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="L22" s="2">
-        <v>4.0</v>
+        <v>36</v>
+      </c>
+      <c r="L22" s="2" t="s">
+        <v>36</v>
       </c>
       <c r="M22" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="N22" s="2">
-        <v>3.0</v>
+        <v>36</v>
+      </c>
+      <c r="N22" s="2" t="s">
+        <v>36</v>
       </c>
       <c r="O22" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="P22" s="2">
-        <v>4.0</v>
-      </c>
-      <c r="Q22" s="2">
-        <v>5.0</v>
-      </c>
-      <c r="R22" s="2">
-        <v>5.0</v>
+        <v>36</v>
+      </c>
+      <c r="P22" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="Q22" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="R22" s="2" t="s">
+        <v>36</v>
       </c>
       <c r="S22" s="2" t="s">
-        <v>46</v>
+        <v>36</v>
       </c>
       <c r="T22" s="2"/>
       <c r="U22" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="V22" s="2" t="s">
         <v>38</v>
       </c>
+      <c r="V22" s="2"/>
       <c r="W22" s="2"/>
       <c r="X22" s="2"/>
       <c r="Y22" s="3"/>
@@ -3298,7 +3458,7 @@
     </row>
     <row r="23">
       <c r="A23" s="2" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="B23" s="2" t="s">
         <v>28</v>
@@ -3310,59 +3470,57 @@
         <v>30</v>
       </c>
       <c r="E23" s="2" t="s">
+        <v>154</v>
+      </c>
+      <c r="F23" s="2" t="s">
         <v>155</v>
-      </c>
-      <c r="F23" s="2" t="s">
-        <v>156</v>
       </c>
       <c r="G23" s="2" t="s">
         <v>33</v>
       </c>
       <c r="H23" s="2" t="s">
+        <v>156</v>
+      </c>
+      <c r="I23" s="2">
+        <v>8.0</v>
+      </c>
+      <c r="J23" s="2" t="s">
         <v>157</v>
       </c>
-      <c r="I23" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="J23" s="2" t="s">
+      <c r="K23" s="2">
+        <v>5.0</v>
+      </c>
+      <c r="L23" s="2">
+        <v>5.0</v>
+      </c>
+      <c r="M23" s="2">
+        <v>5.0</v>
+      </c>
+      <c r="N23" s="2">
+        <v>4.0</v>
+      </c>
+      <c r="O23" s="2">
+        <v>3.0</v>
+      </c>
+      <c r="P23" s="2">
+        <v>5.0</v>
+      </c>
+      <c r="Q23" s="2">
+        <v>5.0</v>
+      </c>
+      <c r="R23" s="2">
+        <v>5.0</v>
+      </c>
+      <c r="S23" s="2">
+        <v>5.0</v>
+      </c>
+      <c r="T23" s="2" t="s">
         <v>158</v>
       </c>
-      <c r="K23" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="L23" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="M23" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="N23" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="O23" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="P23" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="Q23" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="R23" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="S23" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="T23" s="2" t="s">
-        <v>159</v>
-      </c>
       <c r="U23" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="V23" s="2" t="s">
-        <v>38</v>
-      </c>
+        <v>76</v>
+      </c>
+      <c r="V23" s="2"/>
       <c r="W23" s="2"/>
       <c r="X23" s="2"/>
       <c r="Y23" s="3"/>
@@ -3371,7 +3529,7 @@
     </row>
     <row r="24">
       <c r="A24" s="2" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="B24" s="2" t="s">
         <v>28</v>
@@ -3383,57 +3541,57 @@
         <v>30</v>
       </c>
       <c r="E24" s="2" t="s">
+        <v>160</v>
+      </c>
+      <c r="F24" s="2" t="s">
         <v>161</v>
-      </c>
-      <c r="F24" s="2" t="s">
-        <v>162</v>
       </c>
       <c r="G24" s="2" t="s">
         <v>33</v>
       </c>
       <c r="H24" s="2" t="s">
+        <v>162</v>
+      </c>
+      <c r="I24" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="J24" s="2" t="s">
         <v>163</v>
       </c>
-      <c r="I24" s="2">
-        <v>8.0</v>
-      </c>
-      <c r="J24" s="2" t="s">
+      <c r="K24" s="2">
+        <v>4.0</v>
+      </c>
+      <c r="L24" s="2">
+        <v>5.0</v>
+      </c>
+      <c r="M24" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="N24" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="O24" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="P24" s="2">
+        <v>4.0</v>
+      </c>
+      <c r="Q24" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="R24" s="2">
+        <v>2.0</v>
+      </c>
+      <c r="S24" s="2">
+        <v>5.0</v>
+      </c>
+      <c r="T24" s="2" t="s">
         <v>164</v>
       </c>
-      <c r="K24" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="L24" s="2">
-        <v>4.0</v>
-      </c>
-      <c r="M24" s="2">
-        <v>4.0</v>
-      </c>
-      <c r="N24" s="2">
-        <v>4.0</v>
-      </c>
-      <c r="O24" s="2">
-        <v>4.0</v>
-      </c>
-      <c r="P24" s="2">
-        <v>4.0</v>
-      </c>
-      <c r="Q24" s="2">
-        <v>5.0</v>
-      </c>
-      <c r="R24" s="2">
-        <v>5.0</v>
-      </c>
-      <c r="S24" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="T24" s="2"/>
       <c r="U24" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="V24" s="2" t="s">
-        <v>55</v>
-      </c>
+        <v>38</v>
+      </c>
+      <c r="V24" s="2"/>
       <c r="W24" s="2"/>
       <c r="X24" s="2"/>
       <c r="Y24" s="3"/>
@@ -3465,23 +3623,23 @@
       <c r="H25" s="2" t="s">
         <v>168</v>
       </c>
-      <c r="I25" s="2" t="s">
-        <v>35</v>
+      <c r="I25" s="2">
+        <v>8.0</v>
       </c>
       <c r="J25" s="2" t="s">
         <v>169</v>
       </c>
-      <c r="K25" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="L25" s="2" t="s">
-        <v>46</v>
+      <c r="K25" s="2">
+        <v>5.0</v>
+      </c>
+      <c r="L25" s="2">
+        <v>5.0</v>
       </c>
       <c r="M25" s="2">
-        <v>5.0</v>
-      </c>
-      <c r="N25" s="2" t="s">
-        <v>46</v>
+        <v>4.0</v>
+      </c>
+      <c r="N25" s="2">
+        <v>5.0</v>
       </c>
       <c r="O25" s="2">
         <v>5.0</v>
@@ -3490,21 +3648,21 @@
         <v>5.0</v>
       </c>
       <c r="Q25" s="2" t="s">
-        <v>46</v>
+        <v>98</v>
       </c>
       <c r="R25" s="2" t="s">
-        <v>46</v>
+        <v>98</v>
       </c>
       <c r="S25" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="T25" s="2"/>
+        <v>98</v>
+      </c>
+      <c r="T25" s="2" t="s">
+        <v>170</v>
+      </c>
       <c r="U25" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="V25" s="2" t="s">
-        <v>38</v>
-      </c>
+        <v>76</v>
+      </c>
+      <c r="V25" s="2"/>
       <c r="W25" s="2"/>
       <c r="X25" s="2"/>
       <c r="Y25" s="3"/>
@@ -3513,10 +3671,10 @@
     </row>
     <row r="26">
       <c r="A26" s="2" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>40</v>
+        <v>28</v>
       </c>
       <c r="C26" s="2" t="s">
         <v>29</v>
@@ -3525,59 +3683,57 @@
         <v>30</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="F26" s="2" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>43</v>
+        <v>33</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>173</v>
-      </c>
-      <c r="I26" s="2">
-        <v>7.0</v>
+        <v>174</v>
+      </c>
+      <c r="I26" s="2" t="s">
+        <v>49</v>
       </c>
       <c r="J26" s="2" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="K26" s="2" t="s">
-        <v>46</v>
+        <v>36</v>
       </c>
       <c r="L26" s="2" t="s">
-        <v>46</v>
+        <v>36</v>
       </c>
       <c r="M26" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="N26" s="2">
-        <v>4.0</v>
+        <v>36</v>
+      </c>
+      <c r="N26" s="2" t="s">
+        <v>36</v>
       </c>
       <c r="O26" s="2" t="s">
-        <v>53</v>
+        <v>36</v>
       </c>
       <c r="P26" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="Q26" s="2">
-        <v>5.0</v>
-      </c>
-      <c r="R26" s="2">
-        <v>5.0</v>
-      </c>
-      <c r="S26" s="2">
-        <v>5.0</v>
+        <v>36</v>
+      </c>
+      <c r="Q26" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="R26" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="S26" s="2" t="s">
+        <v>36</v>
       </c>
       <c r="T26" s="2" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="U26" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="V26" s="2" t="s">
-        <v>55</v>
-      </c>
+        <v>38</v>
+      </c>
+      <c r="V26" s="2"/>
       <c r="W26" s="2"/>
       <c r="X26" s="2"/>
       <c r="Y26" s="3"/>
@@ -3586,7 +3742,7 @@
     </row>
     <row r="27">
       <c r="A27" s="2" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="B27" s="2" t="s">
         <v>28</v>
@@ -3598,57 +3754,55 @@
         <v>30</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="F27" s="2" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="G27" s="2" t="s">
         <v>33</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="I27" s="2" t="s">
-        <v>35</v>
+        <v>49</v>
       </c>
       <c r="J27" s="2" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="K27" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="L27" s="2" t="s">
-        <v>46</v>
+        <v>36</v>
+      </c>
+      <c r="L27" s="2">
+        <v>5.0</v>
       </c>
       <c r="M27" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="N27" s="2">
-        <v>4.0</v>
-      </c>
-      <c r="O27" s="2">
-        <v>5.0</v>
-      </c>
-      <c r="P27" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="Q27" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="R27" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="S27" s="2" t="s">
-        <v>46</v>
+        <v>36</v>
+      </c>
+      <c r="N27" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="O27" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="P27" s="2">
+        <v>5.0</v>
+      </c>
+      <c r="Q27" s="2">
+        <v>5.0</v>
+      </c>
+      <c r="R27" s="2">
+        <v>5.0</v>
+      </c>
+      <c r="S27" s="2">
+        <v>5.0</v>
       </c>
       <c r="T27" s="2"/>
       <c r="U27" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="V27" s="2" t="s">
         <v>38</v>
       </c>
+      <c r="V27" s="2"/>
       <c r="W27" s="2"/>
       <c r="X27" s="2"/>
       <c r="Y27" s="3"/>
@@ -3657,10 +3811,10 @@
     </row>
     <row r="28">
       <c r="A28" s="2" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>40</v>
+        <v>28</v>
       </c>
       <c r="C28" s="2" t="s">
         <v>29</v>
@@ -3669,59 +3823,57 @@
         <v>30</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="F28" s="2" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>43</v>
+        <v>33</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>184</v>
-      </c>
-      <c r="I28" s="2">
-        <v>7.0</v>
+        <v>185</v>
+      </c>
+      <c r="I28" s="2" t="s">
+        <v>49</v>
       </c>
       <c r="J28" s="2" t="s">
-        <v>185</v>
-      </c>
-      <c r="K28" s="2">
-        <v>5.0</v>
-      </c>
-      <c r="L28" s="2">
-        <v>3.0</v>
-      </c>
-      <c r="M28" s="2">
-        <v>3.0</v>
-      </c>
-      <c r="N28" s="2">
-        <v>4.0</v>
-      </c>
-      <c r="O28" s="2">
-        <v>5.0</v>
-      </c>
-      <c r="P28" s="2">
-        <v>4.0</v>
+        <v>186</v>
+      </c>
+      <c r="K28" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="L28" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="M28" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="N28" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="O28" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="P28" s="2" t="s">
+        <v>36</v>
       </c>
       <c r="Q28" s="2" t="s">
-        <v>53</v>
+        <v>36</v>
       </c>
       <c r="R28" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="S28" s="2">
-        <v>5.0</v>
+        <v>36</v>
+      </c>
+      <c r="S28" s="2" t="s">
+        <v>36</v>
       </c>
       <c r="T28" s="2" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="U28" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="V28" s="2" t="s">
-        <v>55</v>
-      </c>
+        <v>38</v>
+      </c>
+      <c r="V28" s="2"/>
       <c r="W28" s="2"/>
       <c r="X28" s="2"/>
       <c r="Y28" s="3"/>
@@ -3730,7 +3882,7 @@
     </row>
     <row r="29">
       <c r="A29" s="2" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="B29" s="2" t="s">
         <v>28</v>
@@ -3742,57 +3894,55 @@
         <v>30</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="F29" s="2" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="G29" s="2" t="s">
         <v>33</v>
       </c>
       <c r="H29" s="2" t="s">
-        <v>190</v>
-      </c>
-      <c r="I29" s="2" t="s">
-        <v>35</v>
+        <v>191</v>
+      </c>
+      <c r="I29" s="2">
+        <v>6.0</v>
       </c>
       <c r="J29" s="2" t="s">
-        <v>191</v>
-      </c>
-      <c r="K29" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="L29" s="2">
-        <v>5.0</v>
-      </c>
-      <c r="M29" s="2" t="s">
-        <v>46</v>
+        <v>192</v>
+      </c>
+      <c r="K29" s="2">
+        <v>5.0</v>
+      </c>
+      <c r="L29" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="M29" s="2">
+        <v>3.0</v>
       </c>
       <c r="N29" s="2" t="s">
-        <v>46</v>
+        <v>98</v>
       </c>
       <c r="O29" s="2">
         <v>4.0</v>
       </c>
       <c r="P29" s="2">
-        <v>5.0</v>
+        <v>3.0</v>
       </c>
       <c r="Q29" s="2" t="s">
-        <v>46</v>
+        <v>98</v>
       </c>
       <c r="R29" s="2">
         <v>4.0</v>
       </c>
-      <c r="S29" s="2" t="s">
-        <v>46</v>
+      <c r="S29" s="2">
+        <v>4.0</v>
       </c>
       <c r="T29" s="2"/>
       <c r="U29" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="V29" s="2" t="s">
-        <v>38</v>
-      </c>
+        <v>67</v>
+      </c>
+      <c r="V29" s="2"/>
       <c r="W29" s="2"/>
       <c r="X29" s="2"/>
       <c r="Y29" s="3"/>
@@ -3801,10 +3951,10 @@
     </row>
     <row r="30">
       <c r="A30" s="2" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>28</v>
+        <v>69</v>
       </c>
       <c r="C30" s="2" t="s">
         <v>29</v>
@@ -3813,57 +3963,57 @@
         <v>30</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="F30" s="2" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>33</v>
+        <v>72</v>
       </c>
       <c r="H30" s="2" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="I30" s="2" t="s">
-        <v>35</v>
+        <v>49</v>
       </c>
       <c r="J30" s="2" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="K30" s="2" t="s">
-        <v>46</v>
+        <v>36</v>
       </c>
       <c r="L30" s="2" t="s">
-        <v>46</v>
+        <v>36</v>
       </c>
       <c r="M30" s="2" t="s">
-        <v>46</v>
+        <v>36</v>
       </c>
       <c r="N30" s="2" t="s">
-        <v>46</v>
+        <v>36</v>
       </c>
       <c r="O30" s="2" t="s">
-        <v>46</v>
+        <v>36</v>
       </c>
       <c r="P30" s="2" t="s">
-        <v>46</v>
+        <v>36</v>
       </c>
       <c r="Q30" s="2" t="s">
-        <v>46</v>
+        <v>36</v>
       </c>
       <c r="R30" s="2" t="s">
-        <v>46</v>
+        <v>36</v>
       </c>
       <c r="S30" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="T30" s="2"/>
+        <v>36</v>
+      </c>
+      <c r="T30" s="2" t="s">
+        <v>197</v>
+      </c>
       <c r="U30" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="V30" s="2" t="s">
         <v>38</v>
       </c>
+      <c r="V30" s="2"/>
       <c r="W30" s="2"/>
       <c r="X30" s="2"/>
       <c r="Y30" s="3"/>
@@ -3872,7 +4022,7 @@
     </row>
     <row r="31">
       <c r="A31" s="2" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="B31" s="2" t="s">
         <v>28</v>
@@ -3884,57 +4034,57 @@
         <v>30</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="F31" s="2" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="G31" s="2" t="s">
         <v>33</v>
       </c>
       <c r="H31" s="2" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="I31" s="2" t="s">
-        <v>35</v>
+        <v>49</v>
       </c>
       <c r="J31" s="2" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="K31" s="2" t="s">
-        <v>46</v>
+        <v>36</v>
       </c>
       <c r="L31" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="M31" s="2">
-        <v>5.0</v>
+        <v>36</v>
+      </c>
+      <c r="M31" s="2" t="s">
+        <v>36</v>
       </c>
       <c r="N31" s="2" t="s">
-        <v>46</v>
+        <v>36</v>
       </c>
       <c r="O31" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="P31" s="2">
-        <v>5.0</v>
-      </c>
-      <c r="Q31" s="2">
-        <v>5.0</v>
-      </c>
-      <c r="R31" s="2">
-        <v>3.0</v>
-      </c>
-      <c r="S31" s="2">
-        <v>5.0</v>
-      </c>
-      <c r="T31" s="2"/>
+        <v>36</v>
+      </c>
+      <c r="P31" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="Q31" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="R31" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="S31" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="T31" s="2" t="s">
+        <v>203</v>
+      </c>
       <c r="U31" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="V31" s="2" t="s">
         <v>38</v>
       </c>
+      <c r="V31" s="2"/>
       <c r="W31" s="2"/>
       <c r="X31" s="2"/>
       <c r="Y31" s="3"/>
@@ -3943,7 +4093,7 @@
     </row>
     <row r="32">
       <c r="A32" s="2" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="B32" s="2" t="s">
         <v>28</v>
@@ -3955,57 +4105,55 @@
         <v>30</v>
       </c>
       <c r="E32" s="2" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="F32" s="2" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="G32" s="2" t="s">
         <v>33</v>
       </c>
       <c r="H32" s="2" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="I32" s="2">
+        <v>8.0</v>
+      </c>
+      <c r="J32" s="2" t="s">
+        <v>208</v>
+      </c>
+      <c r="K32" s="2">
+        <v>5.0</v>
+      </c>
+      <c r="L32" s="2">
+        <v>5.0</v>
+      </c>
+      <c r="M32" s="2">
+        <v>5.0</v>
+      </c>
+      <c r="N32" s="2">
+        <v>5.0</v>
+      </c>
+      <c r="O32" s="2">
+        <v>5.0</v>
+      </c>
+      <c r="P32" s="2">
+        <v>4.0</v>
+      </c>
+      <c r="Q32" s="2">
+        <v>5.0</v>
+      </c>
+      <c r="R32" s="2">
         <v>3.0</v>
       </c>
-      <c r="J32" s="2" t="s">
-        <v>206</v>
-      </c>
-      <c r="K32" s="2">
-        <v>4.0</v>
-      </c>
-      <c r="L32" s="2">
-        <v>3.0</v>
-      </c>
-      <c r="M32" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="N32" s="2">
-        <v>4.0</v>
-      </c>
-      <c r="O32" s="2">
-        <v>4.0</v>
-      </c>
-      <c r="P32" s="2">
-        <v>4.0</v>
-      </c>
-      <c r="Q32" s="2">
-        <v>2.0</v>
-      </c>
-      <c r="R32" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="S32" s="2" t="s">
-        <v>46</v>
+      <c r="S32" s="2">
+        <v>4.0</v>
       </c>
       <c r="T32" s="2"/>
       <c r="U32" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="V32" s="2" t="s">
-        <v>61</v>
-      </c>
+        <v>76</v>
+      </c>
+      <c r="V32" s="2"/>
       <c r="W32" s="2"/>
       <c r="X32" s="2"/>
       <c r="Y32" s="3"/>
@@ -4014,10 +4162,10 @@
     </row>
     <row r="33">
       <c r="A33" s="2" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>28</v>
+        <v>69</v>
       </c>
       <c r="C33" s="2" t="s">
         <v>29</v>
@@ -4026,57 +4174,55 @@
         <v>30</v>
       </c>
       <c r="E33" s="2" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="F33" s="2" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="G33" s="2" t="s">
-        <v>33</v>
+        <v>72</v>
       </c>
       <c r="H33" s="2" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="I33" s="2" t="s">
-        <v>35</v>
+        <v>49</v>
       </c>
       <c r="J33" s="2" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="K33" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="L33" s="2">
-        <v>5.0</v>
-      </c>
-      <c r="M33" s="2">
-        <v>5.0</v>
-      </c>
-      <c r="N33" s="2">
-        <v>5.0</v>
-      </c>
-      <c r="O33" s="2">
-        <v>5.0</v>
-      </c>
-      <c r="P33" s="2">
-        <v>5.0</v>
-      </c>
-      <c r="Q33" s="2">
-        <v>5.0</v>
-      </c>
-      <c r="R33" s="2">
-        <v>4.0</v>
-      </c>
-      <c r="S33" s="2">
-        <v>5.0</v>
+        <v>36</v>
+      </c>
+      <c r="L33" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="M33" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="N33" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="O33" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="P33" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="Q33" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="R33" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="S33" s="2" t="s">
+        <v>36</v>
       </c>
       <c r="T33" s="2"/>
       <c r="U33" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="V33" s="2" t="s">
         <v>38</v>
       </c>
+      <c r="V33" s="2"/>
       <c r="W33" s="2"/>
       <c r="X33" s="2"/>
       <c r="Y33" s="3"/>
@@ -4085,10 +4231,10 @@
     </row>
     <row r="34">
       <c r="A34" s="5" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="B34" s="5" t="s">
-        <v>40</v>
+        <v>28</v>
       </c>
       <c r="C34" s="5" t="s">
         <v>29</v>
@@ -4097,59 +4243,55 @@
         <v>30</v>
       </c>
       <c r="E34" s="5" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="F34" s="5" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="G34" s="5" t="s">
-        <v>43</v>
+        <v>33</v>
       </c>
       <c r="H34" s="5" t="s">
-        <v>215</v>
-      </c>
-      <c r="I34" s="5">
-        <v>6.0</v>
+        <v>217</v>
+      </c>
+      <c r="I34" s="5" t="s">
+        <v>49</v>
       </c>
       <c r="J34" s="5" t="s">
-        <v>216</v>
-      </c>
-      <c r="K34" s="5">
-        <v>4.0</v>
+        <v>218</v>
+      </c>
+      <c r="K34" s="5" t="s">
+        <v>36</v>
       </c>
       <c r="L34" s="5">
         <v>4.0</v>
       </c>
-      <c r="M34" s="5">
-        <v>4.0</v>
+      <c r="M34" s="5" t="s">
+        <v>36</v>
       </c>
       <c r="N34" s="5">
-        <v>4.0</v>
-      </c>
-      <c r="O34" s="5">
         <v>3.0</v>
       </c>
+      <c r="O34" s="5" t="s">
+        <v>36</v>
+      </c>
       <c r="P34" s="5">
-        <v>3.0</v>
+        <v>4.0</v>
       </c>
       <c r="Q34" s="5">
-        <v>4.0</v>
+        <v>5.0</v>
       </c>
       <c r="R34" s="5">
-        <v>3.0</v>
-      </c>
-      <c r="S34" s="5">
-        <v>4.0</v>
-      </c>
-      <c r="T34" s="5" t="s">
-        <v>217</v>
-      </c>
+        <v>5.0</v>
+      </c>
+      <c r="S34" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="T34" s="5"/>
       <c r="U34" s="5" t="s">
-        <v>47</v>
-      </c>
-      <c r="V34" s="5" t="s">
-        <v>61</v>
-      </c>
+        <v>38</v>
+      </c>
+      <c r="V34" s="5"/>
       <c r="W34" s="5"/>
       <c r="X34" s="5"/>
       <c r="Y34" s="6"/>
@@ -4158,7 +4300,7 @@
     </row>
     <row r="35">
       <c r="A35" s="2" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="B35" s="2" t="s">
         <v>28</v>
@@ -4170,57 +4312,57 @@
         <v>30</v>
       </c>
       <c r="E35" s="2" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="F35" s="2" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="G35" s="2" t="s">
         <v>33</v>
       </c>
       <c r="H35" s="2" t="s">
-        <v>221</v>
-      </c>
-      <c r="I35" s="2">
-        <v>9.0</v>
+        <v>222</v>
+      </c>
+      <c r="I35" s="2" t="s">
+        <v>49</v>
       </c>
       <c r="J35" s="2" t="s">
-        <v>222</v>
-      </c>
-      <c r="K35" s="2">
-        <v>5.0</v>
+        <v>223</v>
+      </c>
+      <c r="K35" s="2" t="s">
+        <v>36</v>
       </c>
       <c r="L35" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="M35" s="2">
-        <v>5.0</v>
-      </c>
-      <c r="N35" s="2">
-        <v>5.0</v>
-      </c>
-      <c r="O35" s="2">
-        <v>5.0</v>
-      </c>
-      <c r="P35" s="2">
-        <v>5.0</v>
+        <v>36</v>
+      </c>
+      <c r="M35" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="N35" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="O35" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="P35" s="2" t="s">
+        <v>36</v>
       </c>
       <c r="Q35" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="R35" s="2">
-        <v>5.0</v>
-      </c>
-      <c r="S35" s="2">
-        <v>5.0</v>
-      </c>
-      <c r="T35" s="2"/>
+        <v>36</v>
+      </c>
+      <c r="R35" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="S35" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="T35" s="2" t="s">
+        <v>224</v>
+      </c>
       <c r="U35" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="V35" s="2" t="s">
         <v>38</v>
       </c>
+      <c r="V35" s="2"/>
       <c r="W35" s="2"/>
       <c r="X35" s="2"/>
       <c r="Y35" s="3"/>
@@ -4229,7 +4371,7 @@
     </row>
     <row r="36">
       <c r="A36" s="2" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="B36" s="2" t="s">
         <v>28</v>
@@ -4241,59 +4383,55 @@
         <v>30</v>
       </c>
       <c r="E36" s="2" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="F36" s="2" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="G36" s="2" t="s">
         <v>33</v>
       </c>
       <c r="H36" s="2" t="s">
-        <v>226</v>
-      </c>
-      <c r="I36" s="2" t="s">
-        <v>35</v>
+        <v>228</v>
+      </c>
+      <c r="I36" s="2">
+        <v>8.0</v>
       </c>
       <c r="J36" s="2" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="K36" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="L36" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="M36" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="N36" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="O36" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="P36" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="Q36" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="R36" s="2" t="s">
-        <v>46</v>
+        <v>36</v>
+      </c>
+      <c r="L36" s="2">
+        <v>4.0</v>
+      </c>
+      <c r="M36" s="2">
+        <v>4.0</v>
+      </c>
+      <c r="N36" s="2">
+        <v>4.0</v>
+      </c>
+      <c r="O36" s="2">
+        <v>4.0</v>
+      </c>
+      <c r="P36" s="2">
+        <v>4.0</v>
+      </c>
+      <c r="Q36" s="2">
+        <v>5.0</v>
+      </c>
+      <c r="R36" s="2">
+        <v>5.0</v>
       </c>
       <c r="S36" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="T36" s="2" t="s">
-        <v>228</v>
-      </c>
+        <v>36</v>
+      </c>
+      <c r="T36" s="2"/>
       <c r="U36" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="V36" s="2" t="s">
-        <v>38</v>
-      </c>
+        <v>76</v>
+      </c>
+      <c r="V36" s="2"/>
       <c r="W36" s="2"/>
       <c r="X36" s="2"/>
       <c r="Y36" s="3"/>
@@ -4302,7 +4440,7 @@
     </row>
     <row r="37">
       <c r="A37" s="2" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="B37" s="2" t="s">
         <v>28</v>
@@ -4314,59 +4452,55 @@
         <v>30</v>
       </c>
       <c r="E37" s="2" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="F37" s="2" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="G37" s="2" t="s">
         <v>33</v>
       </c>
       <c r="H37" s="2" t="s">
-        <v>232</v>
-      </c>
-      <c r="I37" s="2">
-        <v>4.0</v>
+        <v>233</v>
+      </c>
+      <c r="I37" s="2" t="s">
+        <v>49</v>
       </c>
       <c r="J37" s="2" t="s">
-        <v>233</v>
-      </c>
-      <c r="K37" s="2">
-        <v>3.0</v>
-      </c>
-      <c r="L37" s="2">
-        <v>3.0</v>
-      </c>
-      <c r="M37" s="2" t="s">
-        <v>53</v>
+        <v>234</v>
+      </c>
+      <c r="K37" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="L37" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="M37" s="2">
+        <v>5.0</v>
       </c>
       <c r="N37" s="2" t="s">
-        <v>53</v>
+        <v>36</v>
       </c>
       <c r="O37" s="2">
-        <v>2.0</v>
-      </c>
-      <c r="P37" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="Q37" s="2">
-        <v>3.0</v>
-      </c>
-      <c r="R37" s="2">
-        <v>3.0</v>
-      </c>
-      <c r="S37" s="2">
-        <v>5.0</v>
-      </c>
-      <c r="T37" s="2" t="s">
-        <v>234</v>
-      </c>
+        <v>5.0</v>
+      </c>
+      <c r="P37" s="2">
+        <v>5.0</v>
+      </c>
+      <c r="Q37" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="R37" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="S37" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="T37" s="2"/>
       <c r="U37" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="V37" s="2" t="s">
-        <v>61</v>
-      </c>
+        <v>38</v>
+      </c>
+      <c r="V37" s="2"/>
       <c r="W37" s="2"/>
       <c r="X37" s="2"/>
       <c r="Y37" s="3"/>
@@ -4378,7 +4512,7 @@
         <v>235</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>40</v>
+        <v>69</v>
       </c>
       <c r="C38" s="2" t="s">
         <v>29</v>
@@ -4393,53 +4527,51 @@
         <v>237</v>
       </c>
       <c r="G38" s="2" t="s">
-        <v>43</v>
+        <v>72</v>
       </c>
       <c r="H38" s="2" t="s">
         <v>238</v>
       </c>
       <c r="I38" s="2">
-        <v>8.0</v>
+        <v>7.0</v>
       </c>
       <c r="J38" s="2" t="s">
         <v>239</v>
       </c>
-      <c r="K38" s="2">
-        <v>5.0</v>
-      </c>
-      <c r="L38" s="2">
-        <v>5.0</v>
-      </c>
-      <c r="M38" s="2">
-        <v>4.0</v>
+      <c r="K38" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="L38" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="M38" s="2" t="s">
+        <v>36</v>
       </c>
       <c r="N38" s="2">
-        <v>3.0</v>
-      </c>
-      <c r="O38" s="2">
-        <v>5.0</v>
-      </c>
-      <c r="P38" s="2">
-        <v>5.0</v>
+        <v>4.0</v>
+      </c>
+      <c r="O38" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="P38" s="2" t="s">
+        <v>36</v>
       </c>
       <c r="Q38" s="2">
-        <v>4.0</v>
+        <v>5.0</v>
       </c>
       <c r="R38" s="2">
-        <v>3.0</v>
+        <v>5.0</v>
       </c>
       <c r="S38" s="2">
-        <v>2.0</v>
+        <v>5.0</v>
       </c>
       <c r="T38" s="2" t="s">
         <v>240</v>
       </c>
       <c r="U38" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="V38" s="2" t="s">
-        <v>55</v>
-      </c>
+        <v>76</v>
+      </c>
+      <c r="V38" s="2"/>
       <c r="W38" s="2"/>
       <c r="X38" s="2"/>
       <c r="Y38" s="3"/>
@@ -4451,7 +4583,7 @@
         <v>241</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>40</v>
+        <v>28</v>
       </c>
       <c r="C39" s="2" t="s">
         <v>29</v>
@@ -4466,53 +4598,49 @@
         <v>243</v>
       </c>
       <c r="G39" s="2" t="s">
-        <v>43</v>
+        <v>33</v>
       </c>
       <c r="H39" s="2" t="s">
         <v>244</v>
       </c>
       <c r="I39" s="2" t="s">
-        <v>35</v>
+        <v>49</v>
       </c>
       <c r="J39" s="2" t="s">
         <v>245</v>
       </c>
       <c r="K39" s="2" t="s">
-        <v>46</v>
+        <v>36</v>
       </c>
       <c r="L39" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="M39" s="2">
-        <v>5.0</v>
+        <v>36</v>
+      </c>
+      <c r="M39" s="2" t="s">
+        <v>36</v>
       </c>
       <c r="N39" s="2">
-        <v>5.0</v>
-      </c>
-      <c r="O39" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="P39" s="2">
-        <v>5.0</v>
-      </c>
-      <c r="Q39" s="2">
-        <v>5.0</v>
+        <v>4.0</v>
+      </c>
+      <c r="O39" s="2">
+        <v>5.0</v>
+      </c>
+      <c r="P39" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="Q39" s="2" t="s">
+        <v>36</v>
       </c>
       <c r="R39" s="2" t="s">
-        <v>46</v>
+        <v>36</v>
       </c>
       <c r="S39" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="T39" s="2" t="s">
-        <v>246</v>
-      </c>
+        <v>36</v>
+      </c>
+      <c r="T39" s="2"/>
       <c r="U39" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="V39" s="2" t="s">
         <v>38</v>
       </c>
+      <c r="V39" s="2"/>
       <c r="W39" s="2"/>
       <c r="X39" s="2"/>
       <c r="Y39" s="3"/>
@@ -4521,69 +4649,69 @@
     </row>
     <row r="40">
       <c r="A40" s="2" t="s">
+        <v>246</v>
+      </c>
+      <c r="B40" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="C40" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="D40" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="E40" s="2" t="s">
         <v>247</v>
       </c>
-      <c r="B40" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="C40" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="D40" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="E40" s="2" t="s">
+      <c r="F40" s="2" t="s">
         <v>248</v>
       </c>
-      <c r="F40" s="2" t="s">
+      <c r="G40" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="H40" s="2" t="s">
         <v>249</v>
       </c>
-      <c r="G40" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="H40" s="2" t="s">
+      <c r="I40" s="2">
+        <v>7.0</v>
+      </c>
+      <c r="J40" s="2" t="s">
         <v>250</v>
       </c>
-      <c r="I40" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="J40" s="2" t="s">
+      <c r="K40" s="2">
+        <v>5.0</v>
+      </c>
+      <c r="L40" s="2">
+        <v>3.0</v>
+      </c>
+      <c r="M40" s="2">
+        <v>3.0</v>
+      </c>
+      <c r="N40" s="2">
+        <v>4.0</v>
+      </c>
+      <c r="O40" s="2">
+        <v>5.0</v>
+      </c>
+      <c r="P40" s="2">
+        <v>4.0</v>
+      </c>
+      <c r="Q40" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="R40" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="S40" s="2">
+        <v>5.0</v>
+      </c>
+      <c r="T40" s="2" t="s">
         <v>251</v>
       </c>
-      <c r="K40" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="L40" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="M40" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="N40" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="O40" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="P40" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="Q40" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="R40" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="S40" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="T40" s="2"/>
       <c r="U40" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="V40" s="2" t="s">
-        <v>38</v>
-      </c>
+        <v>76</v>
+      </c>
+      <c r="V40" s="2"/>
       <c r="W40" s="2"/>
       <c r="X40" s="2"/>
       <c r="Y40" s="3"/>
@@ -4595,7 +4723,7 @@
         <v>252</v>
       </c>
       <c r="B41" s="2" t="s">
-        <v>40</v>
+        <v>28</v>
       </c>
       <c r="C41" s="2" t="s">
         <v>29</v>
@@ -4610,53 +4738,49 @@
         <v>254</v>
       </c>
       <c r="G41" s="2" t="s">
-        <v>43</v>
+        <v>33</v>
       </c>
       <c r="H41" s="2" t="s">
         <v>255</v>
       </c>
       <c r="I41" s="2" t="s">
-        <v>35</v>
+        <v>49</v>
       </c>
       <c r="J41" s="2" t="s">
         <v>256</v>
       </c>
       <c r="K41" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="L41" s="2" t="s">
-        <v>46</v>
+        <v>36</v>
+      </c>
+      <c r="L41" s="2">
+        <v>5.0</v>
       </c>
       <c r="M41" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="N41" s="2">
-        <v>5.0</v>
+        <v>36</v>
+      </c>
+      <c r="N41" s="2" t="s">
+        <v>36</v>
       </c>
       <c r="O41" s="2">
-        <v>5.0</v>
+        <v>4.0</v>
       </c>
       <c r="P41" s="2">
         <v>5.0</v>
       </c>
       <c r="Q41" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="R41" s="2" t="s">
-        <v>46</v>
+        <v>36</v>
+      </c>
+      <c r="R41" s="2">
+        <v>4.0</v>
       </c>
       <c r="S41" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="T41" s="2" t="s">
-        <v>256</v>
-      </c>
+        <v>36</v>
+      </c>
+      <c r="T41" s="2"/>
       <c r="U41" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="V41" s="2" t="s">
         <v>38</v>
       </c>
+      <c r="V41" s="2"/>
       <c r="W41" s="2"/>
       <c r="X41" s="2"/>
       <c r="Y41" s="3"/>
@@ -4689,45 +4813,43 @@
         <v>260</v>
       </c>
       <c r="I42" s="2" t="s">
-        <v>35</v>
+        <v>49</v>
       </c>
       <c r="J42" s="2" t="s">
         <v>261</v>
       </c>
-      <c r="K42" s="2">
-        <v>5.0</v>
-      </c>
-      <c r="L42" s="2">
-        <v>5.0</v>
-      </c>
-      <c r="M42" s="2">
-        <v>5.0</v>
-      </c>
-      <c r="N42" s="2">
-        <v>4.0</v>
-      </c>
-      <c r="O42" s="2">
-        <v>4.0</v>
-      </c>
-      <c r="P42" s="2">
-        <v>5.0</v>
-      </c>
-      <c r="Q42" s="2">
-        <v>5.0</v>
-      </c>
-      <c r="R42" s="2">
-        <v>5.0</v>
-      </c>
-      <c r="S42" s="2">
-        <v>5.0</v>
+      <c r="K42" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="L42" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="M42" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="N42" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="O42" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="P42" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="Q42" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="R42" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="S42" s="2" t="s">
+        <v>36</v>
       </c>
       <c r="T42" s="2"/>
       <c r="U42" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="V42" s="2" t="s">
         <v>38</v>
       </c>
+      <c r="V42" s="2"/>
       <c r="W42" s="2"/>
       <c r="X42" s="2"/>
       <c r="Y42" s="3"/>
@@ -4760,45 +4882,43 @@
         <v>265</v>
       </c>
       <c r="I43" s="2" t="s">
-        <v>35</v>
+        <v>49</v>
       </c>
       <c r="J43" s="2" t="s">
         <v>266</v>
       </c>
-      <c r="K43" s="2">
-        <v>5.0</v>
+      <c r="K43" s="2" t="s">
+        <v>36</v>
       </c>
       <c r="L43" s="2" t="s">
-        <v>46</v>
+        <v>36</v>
       </c>
       <c r="M43" s="2">
         <v>5.0</v>
       </c>
       <c r="N43" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="O43" s="2">
-        <v>5.0</v>
+        <v>36</v>
+      </c>
+      <c r="O43" s="2" t="s">
+        <v>36</v>
       </c>
       <c r="P43" s="2">
         <v>5.0</v>
       </c>
-      <c r="Q43" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="R43" s="2" t="s">
-        <v>46</v>
+      <c r="Q43" s="2">
+        <v>5.0</v>
+      </c>
+      <c r="R43" s="2">
+        <v>3.0</v>
       </c>
       <c r="S43" s="2">
         <v>5.0</v>
       </c>
       <c r="T43" s="2"/>
       <c r="U43" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="V43" s="2" t="s">
         <v>38</v>
       </c>
+      <c r="V43" s="2"/>
       <c r="W43" s="2"/>
       <c r="X43" s="2"/>
       <c r="Y43" s="3"/>
@@ -4830,48 +4950,44 @@
       <c r="H44" s="2" t="s">
         <v>270</v>
       </c>
-      <c r="I44" s="2" t="s">
-        <v>35</v>
+      <c r="I44" s="2">
+        <v>3.0</v>
       </c>
       <c r="J44" s="2" t="s">
         <v>271</v>
       </c>
       <c r="K44" s="2">
-        <v>5.0</v>
-      </c>
-      <c r="L44" s="2" t="s">
-        <v>46</v>
+        <v>4.0</v>
+      </c>
+      <c r="L44" s="2">
+        <v>3.0</v>
       </c>
       <c r="M44" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="N44" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="O44" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="P44" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="Q44" s="2" t="s">
-        <v>46</v>
+        <v>36</v>
+      </c>
+      <c r="N44" s="2">
+        <v>4.0</v>
+      </c>
+      <c r="O44" s="2">
+        <v>4.0</v>
+      </c>
+      <c r="P44" s="2">
+        <v>4.0</v>
+      </c>
+      <c r="Q44" s="2">
+        <v>2.0</v>
       </c>
       <c r="R44" s="2" t="s">
-        <v>46</v>
+        <v>36</v>
       </c>
       <c r="S44" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="T44" s="2" t="s">
-        <v>272</v>
-      </c>
+        <v>36</v>
+      </c>
+      <c r="T44" s="2"/>
       <c r="U44" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="V44" s="2" t="s">
-        <v>38</v>
-      </c>
+        <v>67</v>
+      </c>
+      <c r="V44" s="2"/>
       <c r="W44" s="2"/>
       <c r="X44" s="2"/>
       <c r="Y44" s="3"/>
@@ -4880,7 +4996,7 @@
     </row>
     <row r="45">
       <c r="A45" s="2" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="B45" s="2" t="s">
         <v>28</v>
@@ -4892,59 +5008,55 @@
         <v>30</v>
       </c>
       <c r="E45" s="2" t="s">
+        <v>273</v>
+      </c>
+      <c r="F45" s="2" t="s">
         <v>274</v>
-      </c>
-      <c r="F45" s="2" t="s">
-        <v>275</v>
       </c>
       <c r="G45" s="2" t="s">
         <v>33</v>
       </c>
       <c r="H45" s="2" t="s">
+        <v>275</v>
+      </c>
+      <c r="I45" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="J45" s="2" t="s">
         <v>276</v>
       </c>
-      <c r="I45" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="J45" s="2" t="s">
-        <v>277</v>
-      </c>
       <c r="K45" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="L45" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="M45" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="N45" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="O45" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="P45" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="Q45" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="R45" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="S45" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="T45" s="2" t="s">
-        <v>278</v>
-      </c>
+        <v>36</v>
+      </c>
+      <c r="L45" s="2">
+        <v>5.0</v>
+      </c>
+      <c r="M45" s="2">
+        <v>5.0</v>
+      </c>
+      <c r="N45" s="2">
+        <v>5.0</v>
+      </c>
+      <c r="O45" s="2">
+        <v>5.0</v>
+      </c>
+      <c r="P45" s="2">
+        <v>5.0</v>
+      </c>
+      <c r="Q45" s="2">
+        <v>5.0</v>
+      </c>
+      <c r="R45" s="2">
+        <v>4.0</v>
+      </c>
+      <c r="S45" s="2">
+        <v>5.0</v>
+      </c>
+      <c r="T45" s="2"/>
       <c r="U45" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="V45" s="2" t="s">
         <v>38</v>
       </c>
+      <c r="V45" s="2"/>
       <c r="W45" s="2"/>
       <c r="X45" s="2"/>
       <c r="Y45" s="3"/>
@@ -4953,69 +5065,69 @@
     </row>
     <row r="46">
       <c r="A46" s="2" t="s">
+        <v>277</v>
+      </c>
+      <c r="B46" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="C46" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="D46" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="E46" s="2" t="s">
+        <v>278</v>
+      </c>
+      <c r="F46" s="2" t="s">
         <v>279</v>
       </c>
-      <c r="B46" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="C46" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="D46" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="E46" s="2" t="s">
+      <c r="G46" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="H46" s="2" t="s">
         <v>280</v>
-      </c>
-      <c r="F46" s="2" t="s">
-        <v>281</v>
-      </c>
-      <c r="G46" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="H46" s="2" t="s">
-        <v>282</v>
       </c>
       <c r="I46" s="2">
         <v>6.0</v>
       </c>
       <c r="J46" s="2" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="K46" s="2">
-        <v>5.0</v>
+        <v>4.0</v>
       </c>
       <c r="L46" s="2">
-        <v>5.0</v>
+        <v>4.0</v>
       </c>
       <c r="M46" s="2">
-        <v>5.0</v>
+        <v>4.0</v>
       </c>
       <c r="N46" s="2">
-        <v>5.0</v>
+        <v>4.0</v>
       </c>
       <c r="O46" s="2">
-        <v>5.0</v>
+        <v>3.0</v>
       </c>
       <c r="P46" s="2">
-        <v>5.0</v>
-      </c>
-      <c r="Q46" s="2" t="s">
-        <v>46</v>
+        <v>3.0</v>
+      </c>
+      <c r="Q46" s="2">
+        <v>4.0</v>
       </c>
       <c r="R46" s="2">
-        <v>5.0</v>
-      </c>
-      <c r="S46" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="T46" s="2"/>
+        <v>3.0</v>
+      </c>
+      <c r="S46" s="2">
+        <v>4.0</v>
+      </c>
+      <c r="T46" s="2" t="s">
+        <v>282</v>
+      </c>
       <c r="U46" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="V46" s="2" t="s">
-        <v>61</v>
-      </c>
+        <v>67</v>
+      </c>
+      <c r="V46" s="2"/>
       <c r="W46" s="2"/>
       <c r="X46" s="2"/>
       <c r="Y46" s="3"/>
@@ -5024,7 +5136,7 @@
     </row>
     <row r="47">
       <c r="A47" s="2" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="B47" s="2" t="s">
         <v>28</v>
@@ -5036,28 +5148,28 @@
         <v>30</v>
       </c>
       <c r="E47" s="2" t="s">
+        <v>284</v>
+      </c>
+      <c r="F47" s="2" t="s">
         <v>285</v>
-      </c>
-      <c r="F47" s="2" t="s">
-        <v>286</v>
       </c>
       <c r="G47" s="2" t="s">
         <v>33</v>
       </c>
       <c r="H47" s="2" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="I47" s="2">
         <v>9.0</v>
       </c>
       <c r="J47" s="2" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="K47" s="2">
         <v>5.0</v>
       </c>
-      <c r="L47" s="2">
-        <v>5.0</v>
+      <c r="L47" s="2" t="s">
+        <v>36</v>
       </c>
       <c r="M47" s="2">
         <v>5.0</v>
@@ -5071,8 +5183,8 @@
       <c r="P47" s="2">
         <v>5.0</v>
       </c>
-      <c r="Q47" s="2">
-        <v>5.0</v>
+      <c r="Q47" s="2" t="s">
+        <v>36</v>
       </c>
       <c r="R47" s="2">
         <v>5.0</v>
@@ -5082,11 +5194,9 @@
       </c>
       <c r="T47" s="2"/>
       <c r="U47" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="V47" s="2" t="s">
         <v>38</v>
       </c>
+      <c r="V47" s="2"/>
       <c r="W47" s="2"/>
       <c r="X47" s="2"/>
       <c r="Y47" s="3"/>
@@ -5095,7 +5205,7 @@
     </row>
     <row r="48">
       <c r="A48" s="2" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="B48" s="2" t="s">
         <v>28</v>
@@ -5107,57 +5217,57 @@
         <v>30</v>
       </c>
       <c r="E48" s="2" t="s">
+        <v>289</v>
+      </c>
+      <c r="F48" s="2" t="s">
         <v>290</v>
-      </c>
-      <c r="F48" s="2" t="s">
-        <v>291</v>
       </c>
       <c r="G48" s="2" t="s">
         <v>33</v>
       </c>
       <c r="H48" s="2" t="s">
+        <v>291</v>
+      </c>
+      <c r="I48" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="J48" s="2" t="s">
         <v>292</v>
       </c>
-      <c r="I48" s="2">
-        <v>9.0</v>
-      </c>
-      <c r="J48" s="2" t="s">
+      <c r="K48" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="L48" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="M48" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="N48" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="O48" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="P48" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="Q48" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="R48" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="S48" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="T48" s="2" t="s">
         <v>293</v>
       </c>
-      <c r="K48" s="2">
-        <v>5.0</v>
-      </c>
-      <c r="L48" s="2">
-        <v>5.0</v>
-      </c>
-      <c r="M48" s="2">
-        <v>5.0</v>
-      </c>
-      <c r="N48" s="2">
-        <v>5.0</v>
-      </c>
-      <c r="O48" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="P48" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="Q48" s="2">
-        <v>5.0</v>
-      </c>
-      <c r="R48" s="2">
-        <v>5.0</v>
-      </c>
-      <c r="S48" s="2">
-        <v>5.0</v>
-      </c>
-      <c r="T48" s="2"/>
       <c r="U48" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="V48" s="2" t="s">
         <v>38</v>
       </c>
+      <c r="V48" s="2"/>
       <c r="W48" s="2"/>
       <c r="X48" s="2"/>
       <c r="Y48" s="3"/>
@@ -5189,48 +5299,46 @@
       <c r="H49" s="2" t="s">
         <v>297</v>
       </c>
-      <c r="I49" s="2" t="s">
+      <c r="I49" s="2">
+        <v>4.0</v>
+      </c>
+      <c r="J49" s="2" t="s">
         <v>298</v>
       </c>
-      <c r="J49" s="2" t="s">
-        <v>299</v>
-      </c>
       <c r="K49" s="2">
-        <v>4.0</v>
-      </c>
-      <c r="L49" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="M49" s="2">
         <v>3.0</v>
       </c>
+      <c r="L49" s="2">
+        <v>3.0</v>
+      </c>
+      <c r="M49" s="2" t="s">
+        <v>98</v>
+      </c>
       <c r="N49" s="2" t="s">
-        <v>53</v>
+        <v>98</v>
       </c>
       <c r="O49" s="2">
         <v>2.0</v>
       </c>
       <c r="P49" s="2" t="s">
-        <v>53</v>
+        <v>98</v>
       </c>
       <c r="Q49" s="2">
-        <v>4.0</v>
+        <v>3.0</v>
       </c>
       <c r="R49" s="2">
-        <v>4.0</v>
+        <v>3.0</v>
       </c>
       <c r="S49" s="2">
-        <v>3.0</v>
+        <v>5.0</v>
       </c>
       <c r="T49" s="2" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="U49" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="V49" s="2" t="s">
-        <v>61</v>
-      </c>
+        <v>67</v>
+      </c>
+      <c r="V49" s="2"/>
       <c r="W49" s="2"/>
       <c r="X49" s="2"/>
       <c r="Y49" s="3"/>
@@ -5239,69 +5347,69 @@
     </row>
     <row r="50">
       <c r="A50" s="2" t="s">
+        <v>300</v>
+      </c>
+      <c r="B50" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="C50" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="D50" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="E50" s="2" t="s">
         <v>301</v>
       </c>
-      <c r="B50" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="C50" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="D50" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="E50" s="2" t="s">
+      <c r="F50" s="2" t="s">
         <v>302</v>
       </c>
-      <c r="F50" s="2" t="s">
+      <c r="G50" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="H50" s="2" t="s">
         <v>303</v>
       </c>
-      <c r="G50" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="H50" s="2" t="s">
+      <c r="I50" s="2">
+        <v>8.0</v>
+      </c>
+      <c r="J50" s="2" t="s">
         <v>304</v>
       </c>
-      <c r="I50" s="2">
-        <v>9.0</v>
-      </c>
-      <c r="J50" s="2" t="s">
+      <c r="K50" s="2">
+        <v>5.0</v>
+      </c>
+      <c r="L50" s="2">
+        <v>5.0</v>
+      </c>
+      <c r="M50" s="2">
+        <v>4.0</v>
+      </c>
+      <c r="N50" s="2">
+        <v>3.0</v>
+      </c>
+      <c r="O50" s="2">
+        <v>5.0</v>
+      </c>
+      <c r="P50" s="2">
+        <v>5.0</v>
+      </c>
+      <c r="Q50" s="2">
+        <v>4.0</v>
+      </c>
+      <c r="R50" s="2">
+        <v>3.0</v>
+      </c>
+      <c r="S50" s="2">
+        <v>2.0</v>
+      </c>
+      <c r="T50" s="2" t="s">
         <v>305</v>
       </c>
-      <c r="K50" s="2">
-        <v>5.0</v>
-      </c>
-      <c r="L50" s="2">
-        <v>4.0</v>
-      </c>
-      <c r="M50" s="2">
-        <v>5.0</v>
-      </c>
-      <c r="N50" s="2">
-        <v>5.0</v>
-      </c>
-      <c r="O50" s="2">
-        <v>5.0</v>
-      </c>
-      <c r="P50" s="2">
-        <v>5.0</v>
-      </c>
-      <c r="Q50" s="2">
-        <v>5.0</v>
-      </c>
-      <c r="R50" s="2">
-        <v>5.0</v>
-      </c>
-      <c r="S50" s="2">
-        <v>5.0</v>
-      </c>
-      <c r="T50" s="2"/>
       <c r="U50" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="V50" s="2" t="s">
-        <v>38</v>
-      </c>
+        <v>76</v>
+      </c>
+      <c r="V50" s="2"/>
       <c r="W50" s="2"/>
       <c r="X50" s="2"/>
       <c r="Y50" s="3"/>
@@ -5313,7 +5421,7 @@
         <v>306</v>
       </c>
       <c r="B51" s="2" t="s">
-        <v>40</v>
+        <v>69</v>
       </c>
       <c r="C51" s="2" t="s">
         <v>29</v>
@@ -5328,51 +5436,51 @@
         <v>308</v>
       </c>
       <c r="G51" s="2" t="s">
-        <v>43</v>
+        <v>72</v>
       </c>
       <c r="H51" s="2" t="s">
         <v>309</v>
       </c>
       <c r="I51" s="2" t="s">
-        <v>35</v>
+        <v>49</v>
       </c>
       <c r="J51" s="2" t="s">
         <v>310</v>
       </c>
       <c r="K51" s="2" t="s">
-        <v>46</v>
+        <v>36</v>
       </c>
       <c r="L51" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="M51" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="N51" s="2" t="s">
-        <v>46</v>
+        <v>36</v>
+      </c>
+      <c r="M51" s="2">
+        <v>5.0</v>
+      </c>
+      <c r="N51" s="2">
+        <v>5.0</v>
       </c>
       <c r="O51" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="P51" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="Q51" s="2" t="s">
-        <v>46</v>
+        <v>36</v>
+      </c>
+      <c r="P51" s="2">
+        <v>5.0</v>
+      </c>
+      <c r="Q51" s="2">
+        <v>5.0</v>
       </c>
       <c r="R51" s="2" t="s">
-        <v>46</v>
+        <v>36</v>
       </c>
       <c r="S51" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="T51" s="2"/>
+        <v>36</v>
+      </c>
+      <c r="T51" s="2" t="s">
+        <v>311</v>
+      </c>
       <c r="U51" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="V51" s="2" t="s">
         <v>38</v>
       </c>
+      <c r="V51" s="2"/>
       <c r="W51" s="2"/>
       <c r="X51" s="2"/>
       <c r="Y51" s="3"/>
@@ -5381,10 +5489,10 @@
     </row>
     <row r="52">
       <c r="A52" s="2" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="B52" s="2" t="s">
-        <v>40</v>
+        <v>69</v>
       </c>
       <c r="C52" s="2" t="s">
         <v>29</v>
@@ -5393,59 +5501,55 @@
         <v>30</v>
       </c>
       <c r="E52" s="2" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="F52" s="2" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="G52" s="2" t="s">
-        <v>43</v>
+        <v>72</v>
       </c>
       <c r="H52" s="2" t="s">
-        <v>314</v>
-      </c>
-      <c r="I52" s="2">
-        <v>8.0</v>
+        <v>315</v>
+      </c>
+      <c r="I52" s="2" t="s">
+        <v>49</v>
       </c>
       <c r="J52" s="2" t="s">
-        <v>315</v>
-      </c>
-      <c r="K52" s="2">
-        <v>5.0</v>
+        <v>316</v>
+      </c>
+      <c r="K52" s="2" t="s">
+        <v>36</v>
       </c>
       <c r="L52" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="M52" s="2">
-        <v>5.0</v>
-      </c>
-      <c r="N52" s="2">
-        <v>3.0</v>
-      </c>
-      <c r="O52" s="2">
-        <v>4.0</v>
+        <v>36</v>
+      </c>
+      <c r="M52" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="N52" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="O52" s="2" t="s">
+        <v>36</v>
       </c>
       <c r="P52" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="Q52" s="2">
-        <v>5.0</v>
+        <v>36</v>
+      </c>
+      <c r="Q52" s="2" t="s">
+        <v>36</v>
       </c>
       <c r="R52" s="2" t="s">
-        <v>53</v>
+        <v>36</v>
       </c>
       <c r="S52" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="T52" s="2" t="s">
-        <v>316</v>
-      </c>
+        <v>36</v>
+      </c>
+      <c r="T52" s="2"/>
       <c r="U52" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="V52" s="2" t="s">
-        <v>55</v>
-      </c>
+        <v>38</v>
+      </c>
+      <c r="V52" s="2"/>
       <c r="W52" s="2"/>
       <c r="X52" s="2"/>
       <c r="Y52" s="3"/>
@@ -5457,7 +5561,7 @@
         <v>317</v>
       </c>
       <c r="B53" s="2" t="s">
-        <v>40</v>
+        <v>69</v>
       </c>
       <c r="C53" s="2" t="s">
         <v>29</v>
@@ -5472,25 +5576,25 @@
         <v>319</v>
       </c>
       <c r="G53" s="2" t="s">
-        <v>43</v>
+        <v>72</v>
       </c>
       <c r="H53" s="2" t="s">
         <v>320</v>
       </c>
-      <c r="I53" s="2">
-        <v>5.0</v>
+      <c r="I53" s="2" t="s">
+        <v>49</v>
       </c>
       <c r="J53" s="2" t="s">
         <v>321</v>
       </c>
-      <c r="K53" s="2">
-        <v>5.0</v>
-      </c>
-      <c r="L53" s="2">
-        <v>5.0</v>
-      </c>
-      <c r="M53" s="2">
-        <v>4.0</v>
+      <c r="K53" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="L53" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="M53" s="2" t="s">
+        <v>36</v>
       </c>
       <c r="N53" s="2">
         <v>5.0</v>
@@ -5499,26 +5603,24 @@
         <v>5.0</v>
       </c>
       <c r="P53" s="2">
-        <v>4.0</v>
+        <v>5.0</v>
       </c>
       <c r="Q53" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="R53" s="2">
-        <v>3.0</v>
-      </c>
-      <c r="S53" s="2">
-        <v>5.0</v>
+        <v>36</v>
+      </c>
+      <c r="R53" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="S53" s="2" t="s">
+        <v>36</v>
       </c>
       <c r="T53" s="2" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="U53" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="V53" s="2" t="s">
-        <v>61</v>
-      </c>
+        <v>38</v>
+      </c>
+      <c r="V53" s="2"/>
       <c r="W53" s="2"/>
       <c r="X53" s="2"/>
       <c r="Y53" s="3"/>
@@ -5527,69 +5629,67 @@
     </row>
     <row r="54">
       <c r="A54" s="2" t="s">
+        <v>322</v>
+      </c>
+      <c r="B54" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="C54" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="D54" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="E54" s="2" t="s">
         <v>323</v>
       </c>
-      <c r="B54" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="C54" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="D54" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="E54" s="2" t="s">
+      <c r="F54" s="2" t="s">
         <v>324</v>
       </c>
-      <c r="F54" s="2" t="s">
+      <c r="G54" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="H54" s="2" t="s">
         <v>325</v>
       </c>
-      <c r="G54" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="H54" s="2" t="s">
+      <c r="I54" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="J54" s="2" t="s">
         <v>326</v>
       </c>
-      <c r="I54" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="J54" s="2" t="s">
-        <v>327</v>
-      </c>
-      <c r="K54" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="L54" s="2" t="s">
-        <v>46</v>
+      <c r="K54" s="2">
+        <v>5.0</v>
+      </c>
+      <c r="L54" s="2">
+        <v>5.0</v>
       </c>
       <c r="M54" s="2">
-        <v>4.0</v>
-      </c>
-      <c r="N54" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="O54" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="P54" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="Q54" s="2" t="s">
-        <v>46</v>
+        <v>5.0</v>
+      </c>
+      <c r="N54" s="2">
+        <v>4.0</v>
+      </c>
+      <c r="O54" s="2">
+        <v>4.0</v>
+      </c>
+      <c r="P54" s="2">
+        <v>5.0</v>
+      </c>
+      <c r="Q54" s="2">
+        <v>5.0</v>
       </c>
       <c r="R54" s="2">
-        <v>4.0</v>
-      </c>
-      <c r="S54" s="2" t="s">
-        <v>46</v>
+        <v>5.0</v>
+      </c>
+      <c r="S54" s="2">
+        <v>5.0</v>
       </c>
       <c r="T54" s="2"/>
       <c r="U54" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="V54" s="2" t="s">
         <v>38</v>
       </c>
+      <c r="V54" s="2"/>
       <c r="W54" s="2"/>
       <c r="X54" s="2"/>
       <c r="Y54" s="3"/>
@@ -5598,71 +5698,67 @@
     </row>
     <row r="55">
       <c r="A55" s="2" t="s">
+        <v>327</v>
+      </c>
+      <c r="B55" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="C55" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="D55" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="E55" s="2" t="s">
         <v>328</v>
       </c>
-      <c r="B55" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="C55" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="D55" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="E55" s="2" t="s">
+      <c r="F55" s="2" t="s">
         <v>329</v>
       </c>
-      <c r="F55" s="2" t="s">
+      <c r="G55" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="H55" s="2" t="s">
         <v>330</v>
       </c>
-      <c r="G55" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="H55" s="2" t="s">
+      <c r="I55" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="J55" s="2" t="s">
         <v>331</v>
       </c>
-      <c r="I55" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="J55" s="2" t="s">
-        <v>332</v>
-      </c>
-      <c r="K55" s="2" t="s">
-        <v>46</v>
+      <c r="K55" s="2">
+        <v>5.0</v>
       </c>
       <c r="L55" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="M55" s="2" t="s">
-        <v>46</v>
+        <v>36</v>
+      </c>
+      <c r="M55" s="2">
+        <v>5.0</v>
       </c>
       <c r="N55" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="O55" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="P55" s="2" t="s">
-        <v>46</v>
+        <v>36</v>
+      </c>
+      <c r="O55" s="2">
+        <v>5.0</v>
+      </c>
+      <c r="P55" s="2">
+        <v>5.0</v>
       </c>
       <c r="Q55" s="2" t="s">
-        <v>46</v>
+        <v>36</v>
       </c>
       <c r="R55" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="S55" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="T55" s="2" t="s">
-        <v>333</v>
-      </c>
+        <v>36</v>
+      </c>
+      <c r="S55" s="2">
+        <v>5.0</v>
+      </c>
+      <c r="T55" s="2"/>
       <c r="U55" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="V55" s="2" t="s">
         <v>38</v>
       </c>
+      <c r="V55" s="2"/>
       <c r="W55" s="2"/>
       <c r="X55" s="2"/>
       <c r="Y55" s="3"/>
@@ -5671,71 +5767,69 @@
     </row>
     <row r="56">
       <c r="A56" s="2" t="s">
+        <v>332</v>
+      </c>
+      <c r="B56" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="C56" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="D56" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="E56" s="2" t="s">
+        <v>333</v>
+      </c>
+      <c r="F56" s="2" t="s">
         <v>334</v>
       </c>
-      <c r="B56" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="C56" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="D56" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="E56" s="2" t="s">
+      <c r="G56" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="H56" s="2" t="s">
         <v>335</v>
       </c>
-      <c r="F56" s="2" t="s">
+      <c r="I56" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="J56" s="2" t="s">
         <v>336</v>
       </c>
-      <c r="G56" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="H56" s="2" t="s">
+      <c r="K56" s="2">
+        <v>5.0</v>
+      </c>
+      <c r="L56" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="M56" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="N56" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="O56" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="P56" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="Q56" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="R56" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="S56" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="T56" s="2" t="s">
         <v>337</v>
       </c>
-      <c r="I56" s="2">
-        <v>9.0</v>
-      </c>
-      <c r="J56" s="2" t="s">
-        <v>338</v>
-      </c>
-      <c r="K56" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="L56" s="2">
-        <v>5.0</v>
-      </c>
-      <c r="M56" s="2">
-        <v>5.0</v>
-      </c>
-      <c r="N56" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="O56" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="P56" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="Q56" s="2">
-        <v>5.0</v>
-      </c>
-      <c r="R56" s="2">
-        <v>5.0</v>
-      </c>
-      <c r="S56" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="T56" s="2" t="s">
-        <v>339</v>
-      </c>
       <c r="U56" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="V56" s="2" t="s">
         <v>38</v>
       </c>
+      <c r="V56" s="2"/>
       <c r="W56" s="3"/>
       <c r="X56" s="3"/>
       <c r="Y56" s="3"/>
@@ -5744,71 +5838,69 @@
     </row>
     <row r="57">
       <c r="A57" s="2" t="s">
+        <v>338</v>
+      </c>
+      <c r="B57" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="C57" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="D57" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="E57" s="2" t="s">
+        <v>339</v>
+      </c>
+      <c r="F57" s="2" t="s">
         <v>340</v>
       </c>
-      <c r="B57" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="C57" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="D57" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="E57" s="2" t="s">
+      <c r="G57" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="H57" s="2" t="s">
         <v>341</v>
       </c>
-      <c r="F57" s="2" t="s">
+      <c r="I57" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="J57" s="2" t="s">
         <v>342</v>
       </c>
-      <c r="G57" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="H57" s="2" t="s">
+      <c r="K57" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="L57" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="M57" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="N57" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="O57" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="P57" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="Q57" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="R57" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="S57" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="T57" s="2" t="s">
         <v>343</v>
       </c>
-      <c r="I57" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="J57" s="2" t="s">
-        <v>344</v>
-      </c>
-      <c r="K57" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="L57" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="M57" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="N57" s="2">
-        <v>4.0</v>
-      </c>
-      <c r="O57" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="P57" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="Q57" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="R57" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="S57" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="T57" s="2" t="s">
-        <v>345</v>
-      </c>
       <c r="U57" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="V57" s="2" t="s">
         <v>38</v>
       </c>
+      <c r="V57" s="2"/>
       <c r="W57" s="3"/>
       <c r="X57" s="3"/>
       <c r="Y57" s="3"/>
@@ -5817,69 +5909,67 @@
     </row>
     <row r="58">
       <c r="A58" s="2" t="s">
+        <v>344</v>
+      </c>
+      <c r="B58" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="C58" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="D58" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="E58" s="2" t="s">
+        <v>345</v>
+      </c>
+      <c r="F58" s="2" t="s">
         <v>346</v>
       </c>
-      <c r="B58" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="C58" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="D58" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="E58" s="2" t="s">
+      <c r="G58" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="H58" s="2" t="s">
         <v>347</v>
       </c>
-      <c r="F58" s="2" t="s">
+      <c r="I58" s="2">
+        <v>6.0</v>
+      </c>
+      <c r="J58" s="2" t="s">
         <v>348</v>
       </c>
-      <c r="G58" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="H58" s="2" t="s">
-        <v>349</v>
-      </c>
-      <c r="I58" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="J58" s="2" t="s">
-        <v>350</v>
-      </c>
-      <c r="K58" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="L58" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="M58" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="N58" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="O58" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="P58" s="2" t="s">
-        <v>46</v>
+      <c r="K58" s="2">
+        <v>5.0</v>
+      </c>
+      <c r="L58" s="2">
+        <v>5.0</v>
+      </c>
+      <c r="M58" s="2">
+        <v>5.0</v>
+      </c>
+      <c r="N58" s="2">
+        <v>5.0</v>
+      </c>
+      <c r="O58" s="2">
+        <v>5.0</v>
+      </c>
+      <c r="P58" s="2">
+        <v>5.0</v>
       </c>
       <c r="Q58" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="R58" s="2" t="s">
-        <v>46</v>
+        <v>36</v>
+      </c>
+      <c r="R58" s="2">
+        <v>5.0</v>
       </c>
       <c r="S58" s="2" t="s">
-        <v>46</v>
+        <v>36</v>
       </c>
       <c r="T58" s="2"/>
       <c r="U58" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="V58" s="2" t="s">
-        <v>38</v>
-      </c>
+        <v>67</v>
+      </c>
+      <c r="V58" s="2"/>
       <c r="W58" s="3"/>
       <c r="X58" s="3"/>
       <c r="Y58" s="3"/>
@@ -5888,40 +5978,40 @@
     </row>
     <row r="59">
       <c r="A59" s="2" t="s">
+        <v>349</v>
+      </c>
+      <c r="B59" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="C59" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="D59" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="E59" s="2" t="s">
+        <v>350</v>
+      </c>
+      <c r="F59" s="2" t="s">
         <v>351</v>
       </c>
-      <c r="B59" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="C59" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="D59" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="E59" s="2" t="s">
+      <c r="G59" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="H59" s="2" t="s">
         <v>352</v>
       </c>
-      <c r="F59" s="2" t="s">
+      <c r="I59" s="2">
+        <v>9.0</v>
+      </c>
+      <c r="J59" s="2" t="s">
         <v>353</v>
       </c>
-      <c r="G59" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="H59" s="2" t="s">
-        <v>354</v>
-      </c>
-      <c r="I59" s="2">
-        <v>8.0</v>
-      </c>
-      <c r="J59" s="2" t="s">
-        <v>355</v>
-      </c>
       <c r="K59" s="2">
         <v>5.0</v>
       </c>
       <c r="L59" s="2">
-        <v>4.0</v>
+        <v>5.0</v>
       </c>
       <c r="M59" s="2">
         <v>5.0</v>
@@ -5929,28 +6019,26 @@
       <c r="N59" s="2">
         <v>5.0</v>
       </c>
-      <c r="O59" s="2" t="s">
-        <v>46</v>
+      <c r="O59" s="2">
+        <v>5.0</v>
       </c>
       <c r="P59" s="2">
         <v>5.0</v>
       </c>
-      <c r="Q59" s="2" t="s">
-        <v>46</v>
+      <c r="Q59" s="2">
+        <v>5.0</v>
       </c>
       <c r="R59" s="2">
         <v>5.0</v>
       </c>
-      <c r="S59" s="2" t="s">
-        <v>46</v>
+      <c r="S59" s="2">
+        <v>5.0</v>
       </c>
       <c r="T59" s="2"/>
       <c r="U59" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="V59" s="2" t="s">
-        <v>55</v>
-      </c>
+        <v>38</v>
+      </c>
+      <c r="V59" s="2"/>
       <c r="W59" s="3"/>
       <c r="X59" s="3"/>
       <c r="Y59" s="3"/>
@@ -5959,7 +6047,7 @@
     </row>
     <row r="60">
       <c r="A60" s="2" t="s">
-        <v>356</v>
+        <v>354</v>
       </c>
       <c r="B60" s="2" t="s">
         <v>28</v>
@@ -5971,59 +6059,55 @@
         <v>30</v>
       </c>
       <c r="E60" s="2" t="s">
-        <v>357</v>
+        <v>355</v>
       </c>
       <c r="F60" s="2" t="s">
-        <v>358</v>
+        <v>356</v>
       </c>
       <c r="G60" s="2" t="s">
         <v>33</v>
       </c>
       <c r="H60" s="2" t="s">
-        <v>359</v>
-      </c>
-      <c r="I60" s="2" t="s">
-        <v>35</v>
+        <v>357</v>
+      </c>
+      <c r="I60" s="2">
+        <v>9.0</v>
       </c>
       <c r="J60" s="2" t="s">
-        <v>360</v>
-      </c>
-      <c r="K60" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="L60" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="M60" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="N60" s="2" t="s">
-        <v>46</v>
+        <v>358</v>
+      </c>
+      <c r="K60" s="2">
+        <v>5.0</v>
+      </c>
+      <c r="L60" s="2">
+        <v>5.0</v>
+      </c>
+      <c r="M60" s="2">
+        <v>5.0</v>
+      </c>
+      <c r="N60" s="2">
+        <v>5.0</v>
       </c>
       <c r="O60" s="2" t="s">
-        <v>46</v>
+        <v>36</v>
       </c>
       <c r="P60" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="Q60" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="R60" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="S60" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="T60" s="2" t="s">
-        <v>361</v>
-      </c>
+        <v>36</v>
+      </c>
+      <c r="Q60" s="2">
+        <v>5.0</v>
+      </c>
+      <c r="R60" s="2">
+        <v>5.0</v>
+      </c>
+      <c r="S60" s="2">
+        <v>5.0</v>
+      </c>
+      <c r="T60" s="2"/>
       <c r="U60" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="V60" s="2" t="s">
         <v>38</v>
       </c>
+      <c r="V60" s="2"/>
       <c r="W60" s="3"/>
       <c r="X60" s="3"/>
       <c r="Y60" s="3"/>
@@ -6032,7 +6116,7 @@
     </row>
     <row r="61">
       <c r="A61" s="2" t="s">
-        <v>362</v>
+        <v>359</v>
       </c>
       <c r="B61" s="2" t="s">
         <v>28</v>
@@ -6044,57 +6128,57 @@
         <v>30</v>
       </c>
       <c r="E61" s="2" t="s">
-        <v>363</v>
+        <v>360</v>
       </c>
       <c r="F61" s="2" t="s">
-        <v>364</v>
+        <v>361</v>
       </c>
       <c r="G61" s="2" t="s">
         <v>33</v>
       </c>
       <c r="H61" s="2" t="s">
+        <v>362</v>
+      </c>
+      <c r="I61" s="2" t="s">
+        <v>363</v>
+      </c>
+      <c r="J61" s="2" t="s">
+        <v>364</v>
+      </c>
+      <c r="K61" s="2">
+        <v>4.0</v>
+      </c>
+      <c r="L61" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="M61" s="2">
+        <v>3.0</v>
+      </c>
+      <c r="N61" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="O61" s="2">
+        <v>2.0</v>
+      </c>
+      <c r="P61" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="Q61" s="2">
+        <v>4.0</v>
+      </c>
+      <c r="R61" s="2">
+        <v>4.0</v>
+      </c>
+      <c r="S61" s="2">
+        <v>3.0</v>
+      </c>
+      <c r="T61" s="2" t="s">
         <v>365</v>
       </c>
-      <c r="I61" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="J61" s="2" t="s">
-        <v>132</v>
-      </c>
-      <c r="K61" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="L61" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="M61" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="N61" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="O61" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="P61" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="Q61" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="R61" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="S61" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="T61" s="2"/>
       <c r="U61" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="V61" s="2" t="s">
-        <v>38</v>
-      </c>
+        <v>67</v>
+      </c>
+      <c r="V61" s="2"/>
       <c r="W61" s="3"/>
       <c r="X61" s="3"/>
       <c r="Y61" s="3"/>
@@ -6127,47 +6211,43 @@
         <v>369</v>
       </c>
       <c r="I62" s="2">
-        <v>5.0</v>
+        <v>9.0</v>
       </c>
       <c r="J62" s="2" t="s">
         <v>370</v>
       </c>
       <c r="K62" s="2">
-        <v>3.0</v>
+        <v>5.0</v>
       </c>
       <c r="L62" s="2">
         <v>4.0</v>
       </c>
-      <c r="M62" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="N62" s="2" t="s">
-        <v>53</v>
+      <c r="M62" s="2">
+        <v>5.0</v>
+      </c>
+      <c r="N62" s="2">
+        <v>5.0</v>
       </c>
       <c r="O62" s="2">
         <v>5.0</v>
       </c>
       <c r="P62" s="2">
-        <v>3.0</v>
-      </c>
-      <c r="Q62" s="2" t="s">
-        <v>53</v>
+        <v>5.0</v>
+      </c>
+      <c r="Q62" s="2">
+        <v>5.0</v>
       </c>
       <c r="R62" s="2">
-        <v>2.0</v>
+        <v>5.0</v>
       </c>
       <c r="S62" s="2">
-        <v>2.0</v>
-      </c>
-      <c r="T62" s="2" t="s">
-        <v>371</v>
-      </c>
+        <v>5.0</v>
+      </c>
+      <c r="T62" s="2"/>
       <c r="U62" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="V62" s="2" t="s">
-        <v>61</v>
-      </c>
+        <v>38</v>
+      </c>
+      <c r="V62" s="2"/>
       <c r="W62" s="3"/>
       <c r="X62" s="3"/>
       <c r="Y62" s="3"/>
@@ -6176,71 +6256,67 @@
     </row>
     <row r="63">
       <c r="A63" s="2" t="s">
+        <v>371</v>
+      </c>
+      <c r="B63" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="C63" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="D63" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="E63" s="2" t="s">
         <v>372</v>
       </c>
-      <c r="B63" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="C63" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="D63" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="E63" s="2" t="s">
+      <c r="F63" s="2" t="s">
         <v>373</v>
       </c>
-      <c r="F63" s="2" t="s">
+      <c r="G63" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="H63" s="2" t="s">
         <v>374</v>
       </c>
-      <c r="G63" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="H63" s="2" t="s">
+      <c r="I63" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="J63" s="2" t="s">
         <v>375</v>
       </c>
-      <c r="I63" s="2">
-        <v>8.0</v>
-      </c>
-      <c r="J63" s="2" t="s">
-        <v>376</v>
-      </c>
       <c r="K63" s="2" t="s">
-        <v>46</v>
+        <v>36</v>
       </c>
       <c r="L63" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="M63" s="2">
-        <v>5.0</v>
-      </c>
-      <c r="N63" s="2">
-        <v>5.0</v>
-      </c>
-      <c r="O63" s="2">
-        <v>4.0</v>
+        <v>36</v>
+      </c>
+      <c r="M63" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="N63" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="O63" s="2" t="s">
+        <v>36</v>
       </c>
       <c r="P63" s="2" t="s">
-        <v>46</v>
+        <v>36</v>
       </c>
       <c r="Q63" s="2" t="s">
-        <v>46</v>
+        <v>36</v>
       </c>
       <c r="R63" s="2" t="s">
-        <v>46</v>
+        <v>36</v>
       </c>
       <c r="S63" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="T63" s="2" t="s">
-        <v>377</v>
-      </c>
+        <v>36</v>
+      </c>
+      <c r="T63" s="2"/>
       <c r="U63" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="V63" s="2" t="s">
-        <v>55</v>
-      </c>
+        <v>38</v>
+      </c>
+      <c r="V63" s="2"/>
       <c r="W63" s="3"/>
       <c r="X63" s="3"/>
       <c r="Y63" s="3"/>
@@ -6249,71 +6325,69 @@
     </row>
     <row r="64">
       <c r="A64" s="2" t="s">
+        <v>376</v>
+      </c>
+      <c r="B64" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="C64" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="D64" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="E64" s="2" t="s">
+        <v>377</v>
+      </c>
+      <c r="F64" s="2" t="s">
         <v>378</v>
       </c>
-      <c r="B64" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="C64" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="D64" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="E64" s="2" t="s">
+      <c r="G64" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="H64" s="2" t="s">
         <v>379</v>
       </c>
-      <c r="F64" s="2" t="s">
+      <c r="I64" s="2">
+        <v>8.0</v>
+      </c>
+      <c r="J64" s="2" t="s">
         <v>380</v>
       </c>
-      <c r="G64" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="H64" s="2" t="s">
+      <c r="K64" s="2">
+        <v>5.0</v>
+      </c>
+      <c r="L64" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="M64" s="2">
+        <v>5.0</v>
+      </c>
+      <c r="N64" s="2">
+        <v>3.0</v>
+      </c>
+      <c r="O64" s="2">
+        <v>4.0</v>
+      </c>
+      <c r="P64" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="Q64" s="2">
+        <v>5.0</v>
+      </c>
+      <c r="R64" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="S64" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="T64" s="2" t="s">
         <v>381</v>
       </c>
-      <c r="I64" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="J64" s="2" t="s">
-        <v>382</v>
-      </c>
-      <c r="K64" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="L64" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="M64" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="N64" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="O64" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="P64" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="Q64" s="2">
-        <v>4.0</v>
-      </c>
-      <c r="R64" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="S64" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="T64" s="2" t="s">
-        <v>383</v>
-      </c>
       <c r="U64" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="V64" s="2" t="s">
-        <v>38</v>
-      </c>
+        <v>76</v>
+      </c>
+      <c r="V64" s="2"/>
       <c r="W64" s="3"/>
       <c r="X64" s="3"/>
       <c r="Y64" s="3"/>
@@ -6322,69 +6396,69 @@
     </row>
     <row r="65">
       <c r="A65" s="2" t="s">
+        <v>382</v>
+      </c>
+      <c r="B65" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="C65" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="D65" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="E65" s="2" t="s">
+        <v>383</v>
+      </c>
+      <c r="F65" s="2" t="s">
         <v>384</v>
       </c>
-      <c r="B65" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="C65" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="D65" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="E65" s="2" t="s">
+      <c r="G65" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="H65" s="2" t="s">
         <v>385</v>
       </c>
-      <c r="F65" s="2" t="s">
+      <c r="I65" s="2">
+        <v>5.0</v>
+      </c>
+      <c r="J65" s="2" t="s">
         <v>386</v>
       </c>
-      <c r="G65" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="H65" s="2" t="s">
+      <c r="K65" s="2">
+        <v>5.0</v>
+      </c>
+      <c r="L65" s="2">
+        <v>5.0</v>
+      </c>
+      <c r="M65" s="2">
+        <v>4.0</v>
+      </c>
+      <c r="N65" s="2">
+        <v>5.0</v>
+      </c>
+      <c r="O65" s="2">
+        <v>5.0</v>
+      </c>
+      <c r="P65" s="2">
+        <v>4.0</v>
+      </c>
+      <c r="Q65" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="R65" s="2">
+        <v>3.0</v>
+      </c>
+      <c r="S65" s="2">
+        <v>5.0</v>
+      </c>
+      <c r="T65" s="2" t="s">
         <v>387</v>
       </c>
-      <c r="I65" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="J65" s="2" t="s">
-        <v>388</v>
-      </c>
-      <c r="K65" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="L65" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="M65" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="N65" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="O65" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="P65" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="Q65" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="R65" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="S65" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="T65" s="2"/>
       <c r="U65" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="V65" s="2" t="s">
-        <v>38</v>
-      </c>
+        <v>67</v>
+      </c>
+      <c r="V65" s="2"/>
       <c r="W65" s="3"/>
       <c r="X65" s="3"/>
       <c r="Y65" s="3"/>
@@ -6393,71 +6467,67 @@
     </row>
     <row r="66">
       <c r="A66" s="2" t="s">
+        <v>388</v>
+      </c>
+      <c r="B66" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="C66" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="D66" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="E66" s="2" t="s">
         <v>389</v>
       </c>
-      <c r="B66" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="C66" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="D66" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="E66" s="2" t="s">
+      <c r="F66" s="2" t="s">
         <v>390</v>
       </c>
-      <c r="F66" s="2" t="s">
+      <c r="G66" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="H66" s="2" t="s">
         <v>391</v>
       </c>
-      <c r="G66" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="H66" s="2" t="s">
+      <c r="I66" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="J66" s="2" t="s">
         <v>392</v>
       </c>
-      <c r="I66" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="J66" s="2" t="s">
-        <v>132</v>
-      </c>
       <c r="K66" s="2" t="s">
-        <v>46</v>
+        <v>36</v>
       </c>
       <c r="L66" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="M66" s="2" t="s">
-        <v>46</v>
+        <v>36</v>
+      </c>
+      <c r="M66" s="2">
+        <v>4.0</v>
       </c>
       <c r="N66" s="2" t="s">
-        <v>46</v>
+        <v>36</v>
       </c>
       <c r="O66" s="2" t="s">
-        <v>46</v>
+        <v>36</v>
       </c>
       <c r="P66" s="2" t="s">
-        <v>46</v>
+        <v>36</v>
       </c>
       <c r="Q66" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="R66" s="2" t="s">
-        <v>46</v>
+        <v>36</v>
+      </c>
+      <c r="R66" s="2">
+        <v>4.0</v>
       </c>
       <c r="S66" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="T66" s="2" t="s">
-        <v>132</v>
-      </c>
+        <v>36</v>
+      </c>
+      <c r="T66" s="2"/>
       <c r="U66" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="V66" s="2" t="s">
         <v>38</v>
       </c>
+      <c r="V66" s="2"/>
       <c r="W66" s="3"/>
       <c r="X66" s="3"/>
       <c r="Y66" s="3"/>
@@ -6469,7 +6539,7 @@
         <v>393</v>
       </c>
       <c r="B67" s="2" t="s">
-        <v>28</v>
+        <v>69</v>
       </c>
       <c r="C67" s="2" t="s">
         <v>29</v>
@@ -6484,53 +6554,51 @@
         <v>395</v>
       </c>
       <c r="G67" s="2" t="s">
-        <v>33</v>
+        <v>72</v>
       </c>
       <c r="H67" s="2" t="s">
         <v>396</v>
       </c>
-      <c r="I67" s="2">
-        <v>9.0</v>
+      <c r="I67" s="2" t="s">
+        <v>49</v>
       </c>
       <c r="J67" s="2" t="s">
         <v>397</v>
       </c>
       <c r="K67" s="2" t="s">
-        <v>46</v>
+        <v>36</v>
       </c>
       <c r="L67" s="2" t="s">
-        <v>46</v>
+        <v>36</v>
       </c>
       <c r="M67" s="2" t="s">
-        <v>46</v>
+        <v>36</v>
       </c>
       <c r="N67" s="2" t="s">
-        <v>46</v>
+        <v>36</v>
       </c>
       <c r="O67" s="2" t="s">
-        <v>53</v>
+        <v>36</v>
       </c>
       <c r="P67" s="2" t="s">
-        <v>46</v>
+        <v>36</v>
       </c>
       <c r="Q67" s="2" t="s">
-        <v>46</v>
+        <v>36</v>
       </c>
       <c r="R67" s="2" t="s">
-        <v>53</v>
+        <v>36</v>
       </c>
       <c r="S67" s="2" t="s">
-        <v>46</v>
+        <v>36</v>
       </c>
       <c r="T67" s="2" t="s">
         <v>398</v>
       </c>
       <c r="U67" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="V67" s="2" t="s">
         <v>38</v>
       </c>
+      <c r="V67" s="2"/>
       <c r="W67" s="3"/>
       <c r="X67" s="3"/>
       <c r="Y67" s="3"/>
@@ -6542,7 +6610,7 @@
         <v>399</v>
       </c>
       <c r="B68" s="2" t="s">
-        <v>28</v>
+        <v>69</v>
       </c>
       <c r="C68" s="2" t="s">
         <v>29</v>
@@ -6557,34 +6625,34 @@
         <v>401</v>
       </c>
       <c r="G68" s="2" t="s">
-        <v>33</v>
+        <v>72</v>
       </c>
       <c r="H68" s="2" t="s">
         <v>402</v>
       </c>
-      <c r="I68" s="2" t="s">
-        <v>35</v>
+      <c r="I68" s="2">
+        <v>9.0</v>
       </c>
       <c r="J68" s="2" t="s">
         <v>403</v>
       </c>
       <c r="K68" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="L68" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="M68" s="2" t="s">
-        <v>46</v>
+        <v>36</v>
+      </c>
+      <c r="L68" s="2">
+        <v>5.0</v>
+      </c>
+      <c r="M68" s="2">
+        <v>5.0</v>
       </c>
       <c r="N68" s="2" t="s">
-        <v>46</v>
+        <v>36</v>
       </c>
       <c r="O68" s="2" t="s">
-        <v>46</v>
+        <v>36</v>
       </c>
       <c r="P68" s="2" t="s">
-        <v>46</v>
+        <v>36</v>
       </c>
       <c r="Q68" s="2">
         <v>5.0</v>
@@ -6593,17 +6661,15 @@
         <v>5.0</v>
       </c>
       <c r="S68" s="2" t="s">
-        <v>46</v>
+        <v>36</v>
       </c>
       <c r="T68" s="2" t="s">
         <v>404</v>
       </c>
       <c r="U68" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="V68" s="2" t="s">
         <v>38</v>
       </c>
+      <c r="V68" s="2"/>
       <c r="W68" s="3"/>
       <c r="X68" s="3"/>
       <c r="Y68" s="3"/>
@@ -6615,7 +6681,7 @@
         <v>405</v>
       </c>
       <c r="B69" s="2" t="s">
-        <v>28</v>
+        <v>69</v>
       </c>
       <c r="C69" s="2" t="s">
         <v>29</v>
@@ -6630,51 +6696,51 @@
         <v>407</v>
       </c>
       <c r="G69" s="2" t="s">
-        <v>33</v>
+        <v>72</v>
       </c>
       <c r="H69" s="2" t="s">
         <v>408</v>
       </c>
       <c r="I69" s="2" t="s">
-        <v>35</v>
+        <v>49</v>
       </c>
       <c r="J69" s="2" t="s">
         <v>409</v>
       </c>
       <c r="K69" s="2" t="s">
-        <v>46</v>
+        <v>36</v>
       </c>
       <c r="L69" s="2" t="s">
-        <v>46</v>
+        <v>36</v>
       </c>
       <c r="M69" s="2" t="s">
-        <v>46</v>
+        <v>36</v>
       </c>
       <c r="N69" s="2">
-        <v>5.0</v>
+        <v>4.0</v>
       </c>
       <c r="O69" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="P69" s="2">
-        <v>4.0</v>
+        <v>36</v>
+      </c>
+      <c r="P69" s="2" t="s">
+        <v>36</v>
       </c>
       <c r="Q69" s="2" t="s">
-        <v>46</v>
+        <v>36</v>
       </c>
       <c r="R69" s="2" t="s">
-        <v>46</v>
+        <v>36</v>
       </c>
       <c r="S69" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="T69" s="3"/>
+        <v>36</v>
+      </c>
+      <c r="T69" s="2" t="s">
+        <v>410</v>
+      </c>
       <c r="U69" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="V69" s="2" t="s">
         <v>38</v>
       </c>
+      <c r="V69" s="2"/>
       <c r="W69" s="3"/>
       <c r="X69" s="3"/>
       <c r="Y69" s="3"/>
@@ -6683,10 +6749,10 @@
     </row>
     <row r="70">
       <c r="A70" s="2" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="B70" s="2" t="s">
-        <v>28</v>
+        <v>69</v>
       </c>
       <c r="C70" s="2" t="s">
         <v>29</v>
@@ -6695,57 +6761,55 @@
         <v>30</v>
       </c>
       <c r="E70" s="2" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="F70" s="2" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="G70" s="2" t="s">
-        <v>33</v>
+        <v>72</v>
       </c>
       <c r="H70" s="2" t="s">
-        <v>413</v>
-      </c>
-      <c r="I70" s="2">
-        <v>9.0</v>
+        <v>414</v>
+      </c>
+      <c r="I70" s="2" t="s">
+        <v>49</v>
       </c>
       <c r="J70" s="2" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="K70" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="L70" s="2">
-        <v>5.0</v>
-      </c>
-      <c r="M70" s="2">
-        <v>5.0</v>
-      </c>
-      <c r="N70" s="2">
-        <v>5.0</v>
-      </c>
-      <c r="O70" s="2">
-        <v>5.0</v>
-      </c>
-      <c r="P70" s="2">
-        <v>5.0</v>
+        <v>36</v>
+      </c>
+      <c r="L70" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="M70" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="N70" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="O70" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="P70" s="2" t="s">
+        <v>36</v>
       </c>
       <c r="Q70" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="R70" s="2">
-        <v>5.0</v>
-      </c>
-      <c r="S70" s="2">
-        <v>5.0</v>
-      </c>
-      <c r="T70" s="3"/>
+        <v>36</v>
+      </c>
+      <c r="R70" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="S70" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="T70" s="2"/>
       <c r="U70" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="V70" s="2" t="s">
         <v>38</v>
       </c>
+      <c r="V70" s="2"/>
       <c r="W70" s="3"/>
       <c r="X70" s="3"/>
       <c r="Y70" s="3"/>
@@ -6754,10 +6818,10 @@
     </row>
     <row r="71">
       <c r="A71" s="2" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="B71" s="2" t="s">
-        <v>28</v>
+        <v>69</v>
       </c>
       <c r="C71" s="2" t="s">
         <v>29</v>
@@ -6766,59 +6830,55 @@
         <v>30</v>
       </c>
       <c r="E71" s="2" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="F71" s="2" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="G71" s="2" t="s">
-        <v>33</v>
+        <v>72</v>
       </c>
       <c r="H71" s="2" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="I71" s="2">
-        <v>9.0</v>
+        <v>8.0</v>
       </c>
       <c r="J71" s="2" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="K71" s="2">
         <v>5.0</v>
       </c>
       <c r="L71" s="2">
-        <v>5.0</v>
+        <v>4.0</v>
       </c>
       <c r="M71" s="2">
         <v>5.0</v>
       </c>
       <c r="N71" s="2">
-        <v>4.0</v>
-      </c>
-      <c r="O71" s="2">
-        <v>5.0</v>
+        <v>5.0</v>
+      </c>
+      <c r="O71" s="2" t="s">
+        <v>36</v>
       </c>
       <c r="P71" s="2">
         <v>5.0</v>
       </c>
-      <c r="Q71" s="2">
-        <v>5.0</v>
+      <c r="Q71" s="2" t="s">
+        <v>36</v>
       </c>
       <c r="R71" s="2">
-        <v>4.0</v>
-      </c>
-      <c r="S71" s="2">
-        <v>5.0</v>
-      </c>
-      <c r="T71" s="2" t="s">
-        <v>420</v>
-      </c>
+        <v>5.0</v>
+      </c>
+      <c r="S71" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="T71" s="2"/>
       <c r="U71" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="V71" s="2" t="s">
-        <v>38</v>
-      </c>
+        <v>76</v>
+      </c>
+      <c r="V71" s="2"/>
       <c r="W71" s="3"/>
       <c r="X71" s="3"/>
       <c r="Y71" s="3"/>
@@ -6851,45 +6911,45 @@
         <v>424</v>
       </c>
       <c r="I72" s="2" t="s">
-        <v>35</v>
+        <v>49</v>
       </c>
       <c r="J72" s="2" t="s">
         <v>425</v>
       </c>
       <c r="K72" s="2" t="s">
-        <v>46</v>
+        <v>36</v>
       </c>
       <c r="L72" s="2" t="s">
-        <v>46</v>
+        <v>36</v>
       </c>
       <c r="M72" s="2" t="s">
-        <v>46</v>
+        <v>36</v>
       </c>
       <c r="N72" s="2" t="s">
-        <v>46</v>
+        <v>36</v>
       </c>
       <c r="O72" s="2" t="s">
-        <v>46</v>
+        <v>36</v>
       </c>
       <c r="P72" s="2" t="s">
-        <v>46</v>
+        <v>36</v>
       </c>
       <c r="Q72" s="2" t="s">
-        <v>46</v>
+        <v>36</v>
       </c>
       <c r="R72" s="2" t="s">
-        <v>46</v>
+        <v>36</v>
       </c>
       <c r="S72" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="T72" s="3"/>
+        <v>36</v>
+      </c>
+      <c r="T72" s="2" t="s">
+        <v>426</v>
+      </c>
       <c r="U72" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="V72" s="2" t="s">
         <v>38</v>
       </c>
+      <c r="V72" s="2"/>
       <c r="W72" s="3"/>
       <c r="X72" s="3"/>
       <c r="Y72" s="3"/>
@@ -6898,7 +6958,7 @@
     </row>
     <row r="73">
       <c r="A73" s="2" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="B73" s="2" t="s">
         <v>28</v>
@@ -6910,59 +6970,55 @@
         <v>30</v>
       </c>
       <c r="E73" s="2" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="F73" s="2" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="G73" s="2" t="s">
         <v>33</v>
       </c>
       <c r="H73" s="2" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="I73" s="2" t="s">
-        <v>35</v>
+        <v>49</v>
       </c>
       <c r="J73" s="2" t="s">
-        <v>430</v>
+        <v>197</v>
       </c>
       <c r="K73" s="2" t="s">
-        <v>46</v>
+        <v>36</v>
       </c>
       <c r="L73" s="2" t="s">
-        <v>46</v>
+        <v>36</v>
       </c>
       <c r="M73" s="2" t="s">
-        <v>46</v>
+        <v>36</v>
       </c>
       <c r="N73" s="2" t="s">
-        <v>46</v>
+        <v>36</v>
       </c>
       <c r="O73" s="2" t="s">
-        <v>46</v>
+        <v>36</v>
       </c>
       <c r="P73" s="2" t="s">
-        <v>46</v>
+        <v>36</v>
       </c>
       <c r="Q73" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="R73" s="2">
-        <v>5.0</v>
+        <v>36</v>
+      </c>
+      <c r="R73" s="2" t="s">
+        <v>36</v>
       </c>
       <c r="S73" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="T73" s="2" t="s">
-        <v>431</v>
-      </c>
+        <v>36</v>
+      </c>
+      <c r="T73" s="2"/>
       <c r="U73" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="V73" s="2" t="s">
         <v>38</v>
       </c>
+      <c r="V73" s="2"/>
       <c r="W73" s="3"/>
       <c r="X73" s="3"/>
       <c r="Y73" s="3"/>
@@ -6971,7 +7027,7 @@
     </row>
     <row r="74">
       <c r="A74" s="2" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="B74" s="2" t="s">
         <v>28</v>
@@ -6983,57 +7039,57 @@
         <v>30</v>
       </c>
       <c r="E74" s="2" t="s">
+        <v>432</v>
+      </c>
+      <c r="F74" s="2" t="s">
         <v>433</v>
-      </c>
-      <c r="F74" s="2" t="s">
-        <v>434</v>
       </c>
       <c r="G74" s="2" t="s">
         <v>33</v>
       </c>
       <c r="H74" s="2" t="s">
+        <v>434</v>
+      </c>
+      <c r="I74" s="2">
+        <v>5.0</v>
+      </c>
+      <c r="J74" s="2" t="s">
         <v>435</v>
       </c>
-      <c r="I74" s="2">
-        <v>7.0</v>
-      </c>
-      <c r="J74" s="2" t="s">
+      <c r="K74" s="2">
+        <v>3.0</v>
+      </c>
+      <c r="L74" s="2">
+        <v>4.0</v>
+      </c>
+      <c r="M74" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="N74" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="O74" s="2">
+        <v>5.0</v>
+      </c>
+      <c r="P74" s="2">
+        <v>3.0</v>
+      </c>
+      <c r="Q74" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="R74" s="2">
+        <v>2.0</v>
+      </c>
+      <c r="S74" s="2">
+        <v>2.0</v>
+      </c>
+      <c r="T74" s="2" t="s">
         <v>436</v>
       </c>
-      <c r="K74" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="L74" s="2">
-        <v>5.0</v>
-      </c>
-      <c r="M74" s="2">
-        <v>4.0</v>
-      </c>
-      <c r="N74" s="2">
-        <v>3.0</v>
-      </c>
-      <c r="O74" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="P74" s="2">
-        <v>5.0</v>
-      </c>
-      <c r="Q74" s="2">
-        <v>5.0</v>
-      </c>
-      <c r="R74" s="2">
-        <v>5.0</v>
-      </c>
-      <c r="S74" s="2">
-        <v>5.0</v>
-      </c>
-      <c r="T74" s="3"/>
       <c r="U74" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="V74" s="2" t="s">
-        <v>55</v>
-      </c>
+        <v>67</v>
+      </c>
+      <c r="V74" s="2"/>
       <c r="W74" s="3"/>
       <c r="X74" s="3"/>
       <c r="Y74" s="3"/>
@@ -7066,47 +7122,45 @@
         <v>440</v>
       </c>
       <c r="I75" s="2">
-        <v>9.0</v>
+        <v>8.0</v>
       </c>
       <c r="J75" s="2" t="s">
         <v>441</v>
       </c>
-      <c r="K75" s="2">
-        <v>5.0</v>
-      </c>
-      <c r="L75" s="2">
-        <v>5.0</v>
+      <c r="K75" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="L75" s="2" t="s">
+        <v>36</v>
       </c>
       <c r="M75" s="2">
         <v>5.0</v>
       </c>
       <c r="N75" s="2">
-        <v>4.0</v>
+        <v>5.0</v>
       </c>
       <c r="O75" s="2">
         <v>4.0</v>
       </c>
-      <c r="P75" s="2">
-        <v>4.0</v>
-      </c>
-      <c r="Q75" s="2">
-        <v>5.0</v>
-      </c>
-      <c r="R75" s="2">
-        <v>4.0</v>
-      </c>
-      <c r="S75" s="2">
-        <v>4.0</v>
+      <c r="P75" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="Q75" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="R75" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="S75" s="2" t="s">
+        <v>36</v>
       </c>
       <c r="T75" s="2" t="s">
         <v>442</v>
       </c>
       <c r="U75" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="V75" s="2" t="s">
-        <v>38</v>
-      </c>
+        <v>76</v>
+      </c>
+      <c r="V75" s="2"/>
       <c r="W75" s="3"/>
       <c r="X75" s="3"/>
       <c r="Y75" s="3"/>
@@ -7139,53 +7193,885 @@
         <v>446</v>
       </c>
       <c r="I76" s="2" t="s">
-        <v>35</v>
+        <v>49</v>
       </c>
       <c r="J76" s="2" t="s">
         <v>447</v>
       </c>
       <c r="K76" s="2" t="s">
-        <v>46</v>
+        <v>36</v>
       </c>
       <c r="L76" s="2" t="s">
-        <v>46</v>
+        <v>36</v>
       </c>
       <c r="M76" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="N76" s="2">
-        <v>2.0</v>
+        <v>36</v>
+      </c>
+      <c r="N76" s="2" t="s">
+        <v>36</v>
       </c>
       <c r="O76" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="P76" s="2">
-        <v>3.0</v>
-      </c>
-      <c r="Q76" s="2" t="s">
-        <v>46</v>
+        <v>36</v>
+      </c>
+      <c r="P76" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="Q76" s="2">
+        <v>4.0</v>
       </c>
       <c r="R76" s="2" t="s">
-        <v>46</v>
+        <v>36</v>
       </c>
       <c r="S76" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="T76" s="3"/>
+        <v>36</v>
+      </c>
+      <c r="T76" s="2" t="s">
+        <v>448</v>
+      </c>
       <c r="U76" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="V76" s="2" t="s">
         <v>38</v>
       </c>
+      <c r="V76" s="2"/>
       <c r="W76" s="3"/>
       <c r="X76" s="3"/>
       <c r="Y76" s="3"/>
       <c r="Z76" s="3"/>
       <c r="AA76" s="3"/>
     </row>
+    <row r="77">
+      <c r="A77" s="2" t="s">
+        <v>449</v>
+      </c>
+      <c r="B77" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="C77" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="D77" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="E77" s="2" t="s">
+        <v>450</v>
+      </c>
+      <c r="F77" s="2" t="s">
+        <v>451</v>
+      </c>
+      <c r="G77" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="H77" s="2" t="s">
+        <v>452</v>
+      </c>
+      <c r="I77" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="J77" s="2" t="s">
+        <v>453</v>
+      </c>
+      <c r="K77" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="L77" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="M77" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="N77" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="O77" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="P77" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="Q77" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="R77" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="S77" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="T77" s="2"/>
+      <c r="U77" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="V77" s="2"/>
+      <c r="W77" s="3"/>
+      <c r="X77" s="3"/>
+      <c r="Y77" s="3"/>
+      <c r="Z77" s="3"/>
+      <c r="AA77" s="3"/>
+    </row>
+    <row r="78">
+      <c r="A78" s="2" t="s">
+        <v>454</v>
+      </c>
+      <c r="B78" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="C78" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="D78" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="E78" s="2" t="s">
+        <v>455</v>
+      </c>
+      <c r="F78" s="2" t="s">
+        <v>456</v>
+      </c>
+      <c r="G78" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="H78" s="2" t="s">
+        <v>457</v>
+      </c>
+      <c r="I78" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="J78" s="2" t="s">
+        <v>197</v>
+      </c>
+      <c r="K78" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="L78" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="M78" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="N78" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="O78" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="P78" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="Q78" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="R78" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="S78" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="T78" s="2" t="s">
+        <v>197</v>
+      </c>
+      <c r="U78" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="V78" s="2"/>
+      <c r="W78" s="3"/>
+      <c r="X78" s="3"/>
+      <c r="Y78" s="3"/>
+      <c r="Z78" s="3"/>
+      <c r="AA78" s="3"/>
+    </row>
+    <row r="79">
+      <c r="A79" s="2" t="s">
+        <v>458</v>
+      </c>
+      <c r="B79" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="C79" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="D79" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="E79" s="2" t="s">
+        <v>459</v>
+      </c>
+      <c r="F79" s="2" t="s">
+        <v>460</v>
+      </c>
+      <c r="G79" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="H79" s="2" t="s">
+        <v>461</v>
+      </c>
+      <c r="I79" s="2">
+        <v>9.0</v>
+      </c>
+      <c r="J79" s="2" t="s">
+        <v>462</v>
+      </c>
+      <c r="K79" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="L79" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="M79" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="N79" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="O79" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="P79" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="Q79" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="R79" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="S79" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="T79" s="2" t="s">
+        <v>463</v>
+      </c>
+      <c r="U79" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="V79" s="2"/>
+      <c r="W79" s="3"/>
+      <c r="X79" s="3"/>
+      <c r="Y79" s="3"/>
+      <c r="Z79" s="3"/>
+      <c r="AA79" s="3"/>
+    </row>
+    <row r="80">
+      <c r="A80" s="2" t="s">
+        <v>464</v>
+      </c>
+      <c r="B80" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="C80" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="D80" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="E80" s="2" t="s">
+        <v>465</v>
+      </c>
+      <c r="F80" s="2" t="s">
+        <v>466</v>
+      </c>
+      <c r="G80" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="H80" s="2" t="s">
+        <v>467</v>
+      </c>
+      <c r="I80" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="J80" s="2" t="s">
+        <v>468</v>
+      </c>
+      <c r="K80" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="L80" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="M80" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="N80" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="O80" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="P80" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="Q80" s="2">
+        <v>5.0</v>
+      </c>
+      <c r="R80" s="2">
+        <v>5.0</v>
+      </c>
+      <c r="S80" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="T80" s="2" t="s">
+        <v>469</v>
+      </c>
+      <c r="U80" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="V80" s="2"/>
+      <c r="W80" s="3"/>
+      <c r="X80" s="3"/>
+      <c r="Y80" s="3"/>
+      <c r="Z80" s="3"/>
+      <c r="AA80" s="3"/>
+    </row>
+    <row r="81">
+      <c r="A81" s="2" t="s">
+        <v>470</v>
+      </c>
+      <c r="B81" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="C81" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="D81" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="E81" s="2" t="s">
+        <v>471</v>
+      </c>
+      <c r="F81" s="2" t="s">
+        <v>472</v>
+      </c>
+      <c r="G81" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="H81" s="2" t="s">
+        <v>473</v>
+      </c>
+      <c r="I81" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="J81" s="2" t="s">
+        <v>474</v>
+      </c>
+      <c r="K81" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="L81" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="M81" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="N81" s="2">
+        <v>5.0</v>
+      </c>
+      <c r="O81" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="P81" s="2">
+        <v>4.0</v>
+      </c>
+      <c r="Q81" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="R81" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="S81" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="T81" s="2"/>
+      <c r="U81" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="V81" s="3"/>
+      <c r="W81" s="3"/>
+      <c r="X81" s="3"/>
+      <c r="Y81" s="3"/>
+      <c r="Z81" s="3"/>
+    </row>
+    <row r="82">
+      <c r="A82" s="2" t="s">
+        <v>475</v>
+      </c>
+      <c r="B82" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="C82" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="D82" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="E82" s="2" t="s">
+        <v>476</v>
+      </c>
+      <c r="F82" s="2" t="s">
+        <v>477</v>
+      </c>
+      <c r="G82" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="H82" s="2" t="s">
+        <v>478</v>
+      </c>
+      <c r="I82" s="2">
+        <v>9.0</v>
+      </c>
+      <c r="J82" s="2" t="s">
+        <v>479</v>
+      </c>
+      <c r="K82" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="L82" s="2">
+        <v>5.0</v>
+      </c>
+      <c r="M82" s="2">
+        <v>5.0</v>
+      </c>
+      <c r="N82" s="2">
+        <v>5.0</v>
+      </c>
+      <c r="O82" s="2">
+        <v>5.0</v>
+      </c>
+      <c r="P82" s="2">
+        <v>5.0</v>
+      </c>
+      <c r="Q82" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="R82" s="2">
+        <v>5.0</v>
+      </c>
+      <c r="S82" s="2">
+        <v>5.0</v>
+      </c>
+      <c r="T82" s="2"/>
+      <c r="U82" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="V82" s="3"/>
+      <c r="W82" s="3"/>
+      <c r="X82" s="3"/>
+      <c r="Y82" s="3"/>
+      <c r="Z82" s="3"/>
+    </row>
+    <row r="83">
+      <c r="A83" s="2" t="s">
+        <v>480</v>
+      </c>
+      <c r="B83" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="C83" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="D83" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="E83" s="2" t="s">
+        <v>481</v>
+      </c>
+      <c r="F83" s="2" t="s">
+        <v>482</v>
+      </c>
+      <c r="G83" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="H83" s="2" t="s">
+        <v>483</v>
+      </c>
+      <c r="I83" s="2">
+        <v>9.0</v>
+      </c>
+      <c r="J83" s="2" t="s">
+        <v>484</v>
+      </c>
+      <c r="K83" s="2">
+        <v>5.0</v>
+      </c>
+      <c r="L83" s="2">
+        <v>5.0</v>
+      </c>
+      <c r="M83" s="2">
+        <v>5.0</v>
+      </c>
+      <c r="N83" s="2">
+        <v>4.0</v>
+      </c>
+      <c r="O83" s="2">
+        <v>5.0</v>
+      </c>
+      <c r="P83" s="2">
+        <v>5.0</v>
+      </c>
+      <c r="Q83" s="2">
+        <v>5.0</v>
+      </c>
+      <c r="R83" s="2">
+        <v>4.0</v>
+      </c>
+      <c r="S83" s="2">
+        <v>5.0</v>
+      </c>
+      <c r="T83" s="2" t="s">
+        <v>485</v>
+      </c>
+      <c r="U83" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="V83" s="3"/>
+      <c r="W83" s="3"/>
+      <c r="X83" s="3"/>
+      <c r="Y83" s="3"/>
+      <c r="Z83" s="3"/>
+    </row>
+    <row r="84">
+      <c r="A84" s="2" t="s">
+        <v>486</v>
+      </c>
+      <c r="B84" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="C84" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="D84" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="E84" s="2" t="s">
+        <v>487</v>
+      </c>
+      <c r="F84" s="2" t="s">
+        <v>488</v>
+      </c>
+      <c r="G84" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="H84" s="2" t="s">
+        <v>489</v>
+      </c>
+      <c r="I84" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="J84" s="2" t="s">
+        <v>490</v>
+      </c>
+      <c r="K84" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="L84" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="M84" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="N84" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="O84" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="P84" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="Q84" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="R84" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="S84" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="T84" s="2"/>
+      <c r="U84" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="V84" s="3"/>
+      <c r="W84" s="3"/>
+      <c r="X84" s="3"/>
+      <c r="Y84" s="3"/>
+      <c r="Z84" s="3"/>
+    </row>
+    <row r="85">
+      <c r="A85" s="2" t="s">
+        <v>491</v>
+      </c>
+      <c r="B85" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="C85" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="D85" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="E85" s="2" t="s">
+        <v>492</v>
+      </c>
+      <c r="F85" s="2" t="s">
+        <v>493</v>
+      </c>
+      <c r="G85" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="H85" s="2" t="s">
+        <v>494</v>
+      </c>
+      <c r="I85" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="J85" s="2" t="s">
+        <v>495</v>
+      </c>
+      <c r="K85" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="L85" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="M85" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="N85" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="O85" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="P85" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="Q85" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="R85" s="2">
+        <v>5.0</v>
+      </c>
+      <c r="S85" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="T85" s="2" t="s">
+        <v>496</v>
+      </c>
+      <c r="U85" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="V85" s="3"/>
+      <c r="W85" s="3"/>
+      <c r="X85" s="3"/>
+      <c r="Y85" s="3"/>
+      <c r="Z85" s="3"/>
+    </row>
+    <row r="86">
+      <c r="A86" s="2" t="s">
+        <v>497</v>
+      </c>
+      <c r="B86" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="C86" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="D86" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="E86" s="2" t="s">
+        <v>498</v>
+      </c>
+      <c r="F86" s="2" t="s">
+        <v>499</v>
+      </c>
+      <c r="G86" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="H86" s="2" t="s">
+        <v>500</v>
+      </c>
+      <c r="I86" s="2">
+        <v>7.0</v>
+      </c>
+      <c r="J86" s="2" t="s">
+        <v>501</v>
+      </c>
+      <c r="K86" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="L86" s="2">
+        <v>5.0</v>
+      </c>
+      <c r="M86" s="2">
+        <v>4.0</v>
+      </c>
+      <c r="N86" s="2">
+        <v>3.0</v>
+      </c>
+      <c r="O86" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="P86" s="2">
+        <v>5.0</v>
+      </c>
+      <c r="Q86" s="2">
+        <v>5.0</v>
+      </c>
+      <c r="R86" s="2">
+        <v>5.0</v>
+      </c>
+      <c r="S86" s="2">
+        <v>5.0</v>
+      </c>
+      <c r="T86" s="2"/>
+      <c r="U86" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="V86" s="3"/>
+      <c r="W86" s="3"/>
+      <c r="X86" s="3"/>
+      <c r="Y86" s="3"/>
+      <c r="Z86" s="3"/>
+    </row>
+    <row r="87">
+      <c r="A87" s="2" t="s">
+        <v>502</v>
+      </c>
+      <c r="B87" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="C87" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="D87" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="E87" s="2" t="s">
+        <v>503</v>
+      </c>
+      <c r="F87" s="2" t="s">
+        <v>504</v>
+      </c>
+      <c r="G87" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="H87" s="2" t="s">
+        <v>505</v>
+      </c>
+      <c r="I87" s="2">
+        <v>9.0</v>
+      </c>
+      <c r="J87" s="2" t="s">
+        <v>506</v>
+      </c>
+      <c r="K87" s="2">
+        <v>5.0</v>
+      </c>
+      <c r="L87" s="2">
+        <v>5.0</v>
+      </c>
+      <c r="M87" s="2">
+        <v>5.0</v>
+      </c>
+      <c r="N87" s="2">
+        <v>4.0</v>
+      </c>
+      <c r="O87" s="2">
+        <v>4.0</v>
+      </c>
+      <c r="P87" s="2">
+        <v>4.0</v>
+      </c>
+      <c r="Q87" s="2">
+        <v>5.0</v>
+      </c>
+      <c r="R87" s="2">
+        <v>4.0</v>
+      </c>
+      <c r="S87" s="2">
+        <v>4.0</v>
+      </c>
+      <c r="T87" s="2" t="s">
+        <v>507</v>
+      </c>
+      <c r="U87" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="V87" s="3"/>
+      <c r="W87" s="3"/>
+      <c r="X87" s="3"/>
+      <c r="Y87" s="3"/>
+      <c r="Z87" s="3"/>
+    </row>
+    <row r="88">
+      <c r="A88" s="2" t="s">
+        <v>508</v>
+      </c>
+      <c r="B88" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="C88" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="D88" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="E88" s="2" t="s">
+        <v>509</v>
+      </c>
+      <c r="F88" s="2" t="s">
+        <v>510</v>
+      </c>
+      <c r="G88" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="H88" s="2" t="s">
+        <v>511</v>
+      </c>
+      <c r="I88" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="J88" s="2" t="s">
+        <v>512</v>
+      </c>
+      <c r="K88" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="L88" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="M88" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="N88" s="2">
+        <v>2.0</v>
+      </c>
+      <c r="O88" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="P88" s="2">
+        <v>3.0</v>
+      </c>
+      <c r="Q88" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="R88" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="S88" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="T88" s="3"/>
+      <c r="U88" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="V88" s="3"/>
+      <c r="W88" s="3"/>
+      <c r="X88" s="3"/>
+      <c r="Y88" s="3"/>
+      <c r="Z88" s="3"/>
+    </row>
   </sheetData>
-  <autoFilter ref="$A$1:$Z$76"/>
+  <autoFilter ref="$A$1:$Z$88"/>
   <drawing r:id="rId1"/>
 </worksheet>
 </file>